--- a/outputs/coded_findings.xlsx
+++ b/outputs/coded_findings.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="581">
   <si>
     <t>snippet_id</t>
   </si>
@@ -193,9 +193,6 @@
     <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0040</t>
   </si>
   <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0041</t>
-  </si>
-  <si>
     <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0042</t>
   </si>
   <si>
@@ -214,6 +211,63 @@
     <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0047</t>
   </si>
   <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0048</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0049</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0050</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0051</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0052</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0053</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0054</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0055</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0056</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0057</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0058</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0059</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0060</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0061</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0062</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0063</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0064</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0065</t>
+  </si>
+  <si>
+    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_EFFECTIVENESS__0066</t>
+  </si>
+  <si>
     <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_EFFECTIVENESS__0001</t>
   </si>
   <si>
@@ -286,18 +340,6 @@
     <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_EFFECTIVENESS__0024</t>
   </si>
   <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_EFFECTIVENESS__0025</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_EFFECTIVENESS__0026</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_EFFECTIVENESS__0027</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_EFFECTIVENESS__0028</t>
-  </si>
-  <si>
     <t>Glastuinbouw_position_paper_on_the_CPVO__CPVR_EFFECTIVENESS__0001</t>
   </si>
   <si>
@@ -340,6 +382,9 @@
     <t>Glastuinbouw_position_paper_on_the_CPVO__CPVR_EFFECTIVENESS__0014</t>
   </si>
   <si>
+    <t>Glastuinbouw_position_paper_on_the_CPVO__CPVR_EFFECTIVENESS__0015</t>
+  </si>
+  <si>
     <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0001</t>
   </si>
   <si>
@@ -364,105 +409,6 @@
     <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0008</t>
   </si>
   <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0001</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0002</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0003</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0004</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0005</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0006</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0007</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0008</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0009</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0010</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0011</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0012</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0013</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0014</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0015</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0016</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0017</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0018</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0019</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0020</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0021</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0022</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0023</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0024</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0025</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0026</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0027</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0028</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0029</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0030</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0031</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0032</t>
-  </si>
-  <si>
-    <t>APBREBES__2020__Focus_on_Plant_Variety_P__CPVR_LEGAL__0033</t>
-  </si>
-  <si>
     <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0001</t>
   </si>
   <si>
@@ -490,6 +436,27 @@
     <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0009</t>
   </si>
   <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0010</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0011</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0012</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0013</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0014</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0015</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0016</t>
+  </si>
+  <si>
     <t>Glastuinbouw_position_paper_on_the_CPVO__CPVR_LEGAL__0001</t>
   </si>
   <si>
@@ -502,9 +469,6 @@
     <t>Glastuinbouw_position_paper_on_the_CPVO__CPVR_LEGAL__0004</t>
   </si>
   <si>
-    <t>Glastuinbouw_position_paper_on_the_CPVO__CPVR_LEGAL__0005</t>
-  </si>
-  <si>
     <t>AIPPI position paper on the CPVO.CPVR Call for Evidence March 2025.pdf</t>
   </si>
   <si>
@@ -541,16 +505,19 @@
     <t>Plant variety right protection is the most relevant form of intellectual property protection for plant varieties. To foster innovation in the field of plant breeding, the Basic Regulation should provide for strong and balanced IP protection for all stakeholders that invest in plant innovations, irrespective of how new plant varieties are developed, either by way of classic breeding and/or the use of new breeding technologies.</t>
   </si>
   <si>
-    <t>The interpretation given by the CJEU in its judgement of 19 December 2019 in the Nadorcott case (C-176 / 18) on unauthorized use of variety constituents in the context of provisional protection has a negative impact on the plant breeding industry in practice, especially in the field of ornamentals and fruit species. The approach of the Court, that there is no unauthorized use of variety constituents if no authorization is required to propagate the material, limits the right to act against harvested material beyond the intentions of the UPOV legislator and has a chilling effect on the release of new plant varieties before the expiry of the provisional protection.</t>
+    <t>The interpretation given by the CJEU in its judgement of 19 December 2019 in the Nadorcott case (C-176 / 18) on unauthorized use of variety constituents in the context of provisional protection has a negative impact on the plant breeding industry in practice, especially in the field of ornamentals and fruit species.</t>
+  </si>
+  <si>
+    <t>The approach of the Court, that there is no unauthorized use of variety constituents if no authorization is required to propagate the material, limits the right to act against harvested material beyond the intentions of the UPOV legislator and has a chilling effect on the release of new plant varieties before the expiry of the provisional protection.</t>
   </si>
   <si>
     <t>Holders of CPVR should have the same rights and remedies granted to other IP holders under the EU enforcement directive. To this end, the relation between the Basic Regulation and the EU enforcement directive should be clarified.</t>
   </si>
   <si>
-    <t>Provisional protection (Article 95, Basic Regulation). Article 95 provides that "Prior to the grant of Community plant variety rights, the holder may require reasonable compensation from any person who has, in the time between publication of the application for a Community plant variety right and grant thereof, effected an act that he would be prohibited from performing subsequent thereto". However, the concept of reasonable compensation is extremely vague and lends itself to different interpretations at the national level in the case of enforcement. For provisional protection to be effective, it would be advisable to delineate the concept of "reasonable compensation" in its conceivable amount so as to provide reliable reference elements for (prospective) rights holders to prevent acts potentially adversely affecting their PVRs, where subsequently granted.</t>
-  </si>
-  <si>
-    <t>To ensure breeders can benefit from the full scope of protection provided for under UPOV 1991 and to make the system future-proof in view of technical progress in plant breeding, the Basic Regulation and related regulations should be improved and clarified, including without limitation:</t>
+    <t>Article 95 provides that "Prior to the grant of Community plant variety rights, the holder may require reasonable compensation from any person who has, in the time between publication of the application for a Community plant variety right and grant thereof, effected an act that he would be prohibited from performing subsequent thereto". However, the concept of reasonable compensation is extremely vague and lends itself to different interpretations at the national level in the case of enforcement. For provisional protection to be effective, it would be advisable to delineate the concept of "reasonable compensation" in its conceivable amount so as to provide reliable reference elements for (prospective) rights holders to prevent acts potentially adversely affecting their PVRs, where subsequently granted.</t>
+  </si>
+  <si>
+    <t>Article 95 provides that "Prior to the grant of Community plant variety rights, the holder may require reasonable compensation from any person who has, in the time between publication of the application for a Community plant variety right and grant thereof, effected an act that he would be prohibited from performing subsequent thereto". However, the concept of reasonable compensation is extremely vague and lends itself to different interpretations at the national level in the case of enforcement.</t>
   </si>
   <si>
     <t>Secondly, various nation states have opted for sui generis PVP laws, oftentimes taking some elements of UPOV provisions that protect plant breeders’ rights and combining these with other provisions that attempt to, inter alia, balance or reconcile with Farmers’ Rights, conserve plant genetic resources for food and agriculture and implement fair and equitable sharing of benefits arising from the use of such genetic resources.</t>
@@ -559,49 +526,74 @@
     <t>The final aspect of the compilation is on the issue of development of PVP laws; this includes literature on what a sui generis PVP regime that attempts to balance Farmers’ Rights and breeders’ rights could look like, what factors may influence policy and legal developments, and what options are available for countries given their international obligations.</t>
   </si>
   <si>
-    <t>While it is argued that IPRs may foster investment in research and development (R&amp;D) and innovation, robust seed sectors have often thrived in the absence of IPRs (Louwaars et al., 2005). Further, IPR protection can restrict access to knowledge, which might hinder future innovation, production and productivity (Campi and Nuvolari, 2020).</t>
-  </si>
-  <si>
-    <t>The UPOV system has not been found to deliver a significant increase in plant breeding activities in developing countries nor has it necessarily led to the development of the seed industry, but instead there are concerns over the misappropriation of local and farmers’ varieties (Coulibaly and Brac de la Perrière, 2019). PVP does not incentivize breeding in crops for which there is no commercial market, implying that in many developing countries a PVP system will only serve a minor share of existing seed systems, and that for many crops and farming areas, public and farmer breeding will continue to be the mainstay.</t>
+    <t>While it is argued that IPRs may foster investment in re­search and development (R&amp;D) and innovation, robust seed sec­tors have often thrived in the absence of IPRs (Louwaars et al., 2005). Further, IPR protection can restrict access to knowledge, which might hinder future innovation, production and produc­tivity (Campi and Nuvolari, 2020).</t>
+  </si>
+  <si>
+    <t>There are indications that developing countries are not bene­fiting from PVP applications, and that IPRs do not appear to be the best tool for fostering pro-poor agricultural R&amp;D (Oberth et al., 2012). The UPOV system has not been found to deliver a signif­icant increase in plant breeding activities in developing coun­tries nor has it necessarily led to the development of the seed industry, but instead there are concerns over the misappropria­tion of local and farmers’ varieties (Coulibaly and Brac de la Per­rière, 2019).</t>
   </si>
   <si>
     <t>Countries need to be able to devise PVP systems that balance the interests of both breeders and farmers, as well as to protect Farmers’ Rights.</t>
   </si>
   <si>
-    <t>PVP remains an area of tension between creating incentives for plant breeding through PBRs and ensuring seed sovereignty, agricultural biodiversity and encouraging farmer innovation through Farmers’ Rights. Many sui generis PVP laws attempt to balance both breeders’ rights and Farmers’ Rights to various extents, by conferring IP protection in plant breeding while protecting the rights of farming communities</t>
-  </si>
-  <si>
-    <t>Where food production relies on widespread practices of saving, exchange and local sale of seeds and other planting materials, the national PVP law should recognize exceptions and protections for farmers to limit the reach of otherwise exclusive PBRs. In particular, given the crucial role that small farmers play in the production of food in developing countries, PVP regimes should exempt them from any obligation in connection with plant varieties, thereby fully safeguarding their right to freely save, use, exchange and sell seeds/propagating material (Correa, 2015).</t>
-  </si>
-  <si>
-    <t>the recommendations include: (1) Governments of developing countries should clarify the objectives of their national PVP law and carefully consider how different PVP laws could help address these; ensuring how all farmers can access seed of protected varieties, and how scientific breeding progress can be directed towards the needs of vulnerable groups;</t>
-  </si>
-  <si>
-    <t>The report concludes by stating that states should promote innovation in both commercial and farmers’ seed systems, ensuring that such innovation works for the benefit of the poorest and most marginalized farmers, particularly in developing countries.</t>
-  </si>
-  <si>
-    <t>There is still an open debate on the effect of IP protection and on the role of IPRs in encouraging innovation and agricultural development. While IPRs can foster investment in R&amp;D and innovation, with potential positive impact for agricultural production, they also restrict access to knowledge, which might hinder future innovation, production and productivity, especially affecting poor countries.</t>
+    <t>GETTING THE BALANCE RIGHT IN SUI GENERIS PVP SYSTEMS
+PVP remains an area of tension between creating incentives for plant breeding through PBRs and ensuring seed sovereignty, ag-ricultural biodiversity and encouraging farmer innovation through Farmers’ Rights.</t>
+  </si>
+  <si>
+    <t>Many sui generis PVP laws attempt to balance both breeders’ rights and Farmers’ Rights to various ex­tents, by conferring IP protection in plant breeding while pro­tecting the rights of farming communities (e.g., Adebola, 2019; Hindeya, 2011; Kamble, 2013; Moonka and Mukherjee, 2018).</t>
+  </si>
+  <si>
+    <t>Where food pro­duction relies on widespread practices of saving, exchange and local sale of seeds and other planting materials, the national PVP law should recognize exceptions and protections for farmers to limit the reach of otherwise exclusive PBRs.</t>
+  </si>
+  <si>
+    <t>In particular, given the crucial role that small farmers play in the production of food in developing countries, PVP regimes should exempt them from any obligation in connection with plant varieties, thereby fully safeguarding their right to freely save, use, exchange and sell seeds/propagating material (Correa, 2015).</t>
+  </si>
+  <si>
+    <t>As such, the recommendations include: (1) Govern­ments of developing countries should clarify the objectives of their national PVP law and carefully consider how different PVP laws could help address these; ensuring how all farmers can ac­cess seed of protected varieties, and how scientific breeding progress can be directed towards the needs of vulnerable groups;</t>
+  </si>
+  <si>
+    <t>The paper finds that all countries, regardless of their development level, have been tightening their IPR systems, driven by exogenous processes derived from TRIPS obligations and adoption of TRIPS-plus provisions, rather than a response to domestic needs. In do­ing so, these countries risk implementing IPR regimes that are not appropriate to contexts in which traditional knowledge and collective invention are important components of farming prac­tices. In addition, regardless of the type of country, the effect of IPRs on agricultural performance is ambiguous.</t>
+  </si>
+  <si>
+    <t>This is because IPRs have a trade-off: they are adopted with the aim of fostering innovation but as they provide a monopoly power on the use of innovations, they can lead to a decrease in the number of new products and to an increase in their price.</t>
+  </si>
+  <si>
+    <t>The article finds that IPRs do not affect developed and developing countries in the same way. For example, it finds a positive and significant correlation between the strengthening of IP protection and agricultural value added for developed countries, but it was not able to establish any sig­nificant correlation for developing countries.</t>
+  </si>
+  <si>
+    <t>The paper argues that the establishment of IPR schemes, particularly patents and PBRs, has created power asymmetry in the seed value chain and has therefore been a major driver of consolidation in Sweden and internationally. In particular, the tightening of IPR laws created market power in the upper part of the chain and in­creased the concentration in the industry, spurring waves of mergers and acquisitions, which provided a way to aggregate and control the relevant IPRs.</t>
   </si>
   <si>
     <t>The system has not delivered any significant increase in plant breeding activities nor led to the development of the seed industry across the region, but instead raises a major concern of misappropriation of local and farmer varieties.</t>
   </si>
   <si>
-    <t>The note concludes that for IPRs to support agricultural development, they need to be tailored to a country’s circumstances. Developing countries, with their diversity of farmers and seed systems, present special challenges, where the goal should be to provide incentives for seed sector development without limiting the practices and livelihoods of small farmers.</t>
-  </si>
-  <si>
-    <t>The note concludes that for IPRs to support agricultural development, they need to be tailored to a country’s circumstances. Developing countries, with their diversity of farmers and seed systems, present special challenges, where the goal should be to provide incentives for seed sector development without limiting the practices and livelihoods of small farmers. Meeting this goal requires a careful balancing of rights and obligations, which may imply adapting, as opposed to simply adopting, the standard models available.</t>
-  </si>
-  <si>
-    <t>The study finds that the emergence of the private seed sector in the case study countries owes relatively little to national IP regimes; the most dynamic private seed sector in the sample (India) has grown and diversified without benefit of any IPRs.</t>
-  </si>
-  <si>
-    <t>The study concludes by pointing to significant lessons, including: (1) IPR regimes should be consistent with developing countries’ priorities and capacities instead of being externally imposed; (2) IPRs in plant breeding should be seen in the context of a wider range of agricultural policies, but IPR regimes themselves must be carefully tailored to specific situations;</t>
-  </si>
-  <si>
-    <t>The study finds that a window for synergistic and mutually reinforcing implementation of the three regimes to serve or advance the objectives of ABS lies at the national level, where countries are free to craft balanced and detailed provisions on Farmers’ Rights. Furthermore, states can support the development of rules on ABS that accommodate the rights of breeders, TK holders, farmers and even patent holders in as fair and balanced a way as possible</t>
-  </si>
-  <si>
-    <t>The evidence suggests that increased investments are targeted primarily at a limited set of commercial crop types.</t>
+    <t>The results point to a dysfunctional PVP system that does not fit the socio-economic and agricultural conditions in the region. Only seven of the current 17 OAPI member states have made use of the system, at great cost and at the expense of public funds. Only 51 PVP Cer­tificates are in force after 10 years and the private sector’s use of the system is negligible.</t>
+  </si>
+  <si>
+    <t>The note concludes that for IPRs to support ag­ricultural development, they need to be tailored to a country’s circumstances. Developing countries, with their diversity of farmers and seed systems, present special challenges, where the goal should be to provide incentives for seed sector develop­ment without limiting the practices and livelihoods of small farmers.</t>
+  </si>
+  <si>
+    <t>The note concludes that for IPRs to support ag­ricultural development, they need to be tailored to a country’s circumstances. Developing countries, with their diversity of farmers and seed systems, present special challenges, where the goal should be to provide incentives for seed sector develop­ment without limiting the practices and livelihoods of small farmers. Meeting this goal requires a careful balancing of rights and obligations, which may imply adapting, as opposed to sim­ply adopting, the standard models available.</t>
+  </si>
+  <si>
+    <t>The study finds that the emergence of the private seed sector in the case study countries owes relatively little to national IP re­gimes; the most dynamic private seed sector in the sample (In­dia) has grown and diversified without benefit of any IPRs.</t>
+  </si>
+  <si>
+    <t>Instead, the focus of national agricultural re­search institutes on revenue generation may divert attention from the needs of marginal farmers in favour of breeding ob­jectives and methodologies directed at large-scale commercial production, and may affect the conduct of participatory meth­ods in breeding and variety selection.</t>
+  </si>
+  <si>
+    <t>Important parameters that require careful consideration for PVP are: (1) the designation of which species are to be covered; (2) fee structures (and possible subsidies or differentiation by crop); (3) the nature of the breeder’s exemption for use of protected vari­eties; and (4) implications for farmers’ abilities to save, ex­change and sell seed.</t>
+  </si>
+  <si>
+    <t>The study finds that a window for synergistic and mu­tually reinforcing implementation of the three regimes to serve or advance the objectives of ABS lies at the national level, where countries are free to craft balanced and detailed provisions on Farmers’ Rights.</t>
+  </si>
+  <si>
+    <t>Furthermore, states can support the develop­ment of rules on ABS that accommodate the rights of breeders, TK holders, farmers and even patent holders in as fair and bal­anced a way as possible, with the ultimate aim of advancing bio­diversity conservation, protecting and conserving PGRFA, and supporting PVP in fairness to Farmers’ Rights.</t>
+  </si>
+  <si>
+    <t>The evidence suggests that increased investments are targeted primarily at a limited set of commer­cial crop types.</t>
+  </si>
+  <si>
+    <t>PVP laws as per UPOV may have disrup­tive effects if they narrow or eliminate farmers’ rights to replant and exchange saved seed.</t>
   </si>
   <si>
     <t>It is apparent from this data that there is no causal link between UPOV membership or implementation of UPOV legislation, and the presence and engagement of seed companies and their breeding activities.</t>
@@ -610,85 +602,112 @@
     <t>The paper finds no significant effect from UPOV membership, as an indicator of the scope and strength of IPRs affecting the plant breeding sector, on seed imports, i.e., there is no evidence that the adoption of a UPOV system of PBRs positively influences seed imports.</t>
   </si>
   <si>
-    <t>This paper does not engage with the question of whether PVP supports or undermines food security and biological diversity but instead seeks to assess the extent to which the UPOV system permits consideration of its interaction with, and impact on, these public policy objectives.</t>
-  </si>
-  <si>
-    <t>According to UPOV, the reviews demonstrate positive responses. These include an increase in the occurrence of protected varieties in a range of crops; improved quality in protected varieties; and an increase in variety applications by foreign (non-resident) breeders, which was seen to enhance global competitiveness for producers.</t>
-  </si>
-  <si>
-    <t>The Commission finds that the evidence suggests that PVP systems have not been particularly effective at stimulating research on crops in general, and particularly for the kind of crops grown by poor farmers.</t>
-  </si>
-  <si>
-    <t>There may be a need to differentiate standards of protection between different kinds of crop, in particular, for food crops grown by farmers, to protect their practices of saving, trading and exchanging seeds, and informal systems of innovation.</t>
+    <t>The paper does not engage with the question of whether PVP supports or undermines food secu­rity and biological diversity but instead seeks to assess the ex­tent to which the UPOV system permits consideration of its in­teraction with, and impact on, these public policy objectives.</t>
+  </si>
+  <si>
+    <t>a PVP regime should be for the benefit of society, and that while PVP may stimulate private investment in research where an industry already exists, or in varieties that have a high market value, there is a lack of evidence that PVP alone will stimulate these elements.</t>
+  </si>
+  <si>
+    <t>According to UPOV, the reviews demonstrate positive responses. These include an increase in the occurrence of protected variet­ies in a range of crops; improved quality in protected varieties; and an increase in variety applications by foreign (non-resident) breeders, which was seen to enhance global competitiveness for producers.</t>
+  </si>
+  <si>
+    <t>These include an increase in the occurrence of protected variet­ies in a range of crops; improved quality in protected varieties; and an increase in variety applications by foreign (non-resident) breeders, which was seen to enhance global competitiveness for producers.</t>
+  </si>
+  <si>
+    <t>The critique concludes that UP­OV’s impact study leaves unanswered the question whether the UPOV Conventions do or do not have positive impacts – in a broader sense – on the countries that have adopted them.</t>
+  </si>
+  <si>
+    <t>The Commission finds that the evidence suggests that PVP sys­tems have not been particularly effective at stimulating research on crops in general, and particularly for the kind of crops grown by poor farmers.</t>
+  </si>
+  <si>
+    <t>The chapter concludes that in developing sui generis regimes for the protection of plant varieties that suit their agri­cultural systems, countries should permit access to the protect­ed varieties for further research and breeding, and provide at least for the right of farmers to save and plant-back seed, in­cluding the possibility of informal sale and exchange.</t>
+  </si>
+  <si>
+    <t>The article describes Ethiopian access legislations, which are unique in Africa in that they aim to harmonize regulation and implementation of breed­ers’, farmers’ and community rights by combining elements of the CBD and ITPGRFA.</t>
+  </si>
+  <si>
+    <t>Its laws make protected varieties accessible for smallholder farmers, conceptualize Farmers’ Rights as an important protection for smallholder agricultural production and food security, and promote pluralistic seed sys­tems to ensure complementarity of formal and farmers’ seed systems.</t>
+  </si>
+  <si>
+    <t>It finds that attaining food security requires a balancing of all interests, making it essential to also limit IPRs, particularly as they impact on Farmers’ Rights.</t>
   </si>
   <si>
     <t>The African Model Law is a framework mechanism that remains relevant because its core principles promote the balance of small-scale farmers’, farming communities’ and commercial breeders’ interests.</t>
   </si>
   <si>
-    <t>The protection of three categories of varieties – community varieties, farmers’ varieties and new breeders’ varieties – alongside ABS principles and Farmers’ Rights provisions, demonstrate this balance.</t>
-  </si>
-  <si>
-    <t>The article concludes that the introduction of a creatively designed sui generis system in Nigeria can be an alternative guide for the continent to recognize Farmers’ Rights and breeders’ rights while ensuring ABS.</t>
-  </si>
-  <si>
-    <t>The Arusha Protocol, which is to enter into force after the requisite ratifications, reaffirms UPOV 1991 in its extensive limitation of farmers’ rights to freely save, replant and exchange seeds of protected plant varieties, while liberally conceptualizing PBRs.</t>
-  </si>
-  <si>
-    <t>the article argues that the legal regime for PVP established under the Arusha Protocol is inappropriate for ARIPO members as it fails to balance breeders’ rights and Farmers’ Rights in a manner that promotes food security.</t>
-  </si>
-  <si>
-    <t>The article highlights the imbalance presented by the Act, between the interests of plant breeders who are the ultimate beneficiaries of PVP, and the rights of indigenous farmers, who are seemingly unsuspecting losers.</t>
-  </si>
-  <si>
-    <t>The article finds that within the process and outcome of the ARIPO Arusha PVP Protocol, the interests of breeders prevailed, while farmers’ organizations and organizations promoting the public interest were to a large extent sidelined from the negotiations.</t>
-  </si>
-  <si>
-    <t>The article concludes that the goal of the PVP legislation to enable access by local farmers to high-value, higher-yielding foreign varieties, has not been fully met.</t>
-  </si>
-  <si>
-    <t>The paper concludes that the sui generis system adopted by Ethiopia strikes the necessary balance between the interests of right holders and the public interest in general and Farmers’ Rights in particular.</t>
-  </si>
-  <si>
-    <t>The fundamental ideology of the PPVFRA is thus to protect the rights of small and marginal farming communities, while promoting plant breeding by vesting adequate IP protection.</t>
-  </si>
-  <si>
-    <t>The PPVFRA protects farmers’ rights to save, use, exchange and share all farm produce, including non-branded seed, even of a protected variety. It protects biodiversity through a fund which recognizes and rewards the contributions made by indigenous farmers; prescribes community rights; provides for benefit sharing, public interest exceptions and compulsory licensing.</t>
-  </si>
-  <si>
-    <t>The paper concludes that the PPVFRA showcases that Farmers’ Rights and breeders’ rights can be adequately and concurrently protected under a single piece of legislation, despite its significant difference from the UPOV model.</t>
-  </si>
-  <si>
-    <t>The article concludes that countries can both promote food sovereignty and protect plant varieties. In some instances, the concept of food sovereignty can counterbalance the exclusivity associated with standard forms of IP, as when laws move beyond the provision of exclusive ownership rights for plants and seeds to recognize new protections for farmers, in a way that provides benefits for diverse social actors.</t>
-  </si>
-  <si>
-    <t>Where food production relies on widespread practices of saving, exchange and local sale of seeds and other planting materials, the national PVP law should recognize exceptions and protections for farmers. The new frameworks in Ecuador and Nepal contain such provisions, limiting the reach of the otherwise exclusive proprietary rights granted to plant breeders.</t>
-  </si>
-  <si>
-    <t>The paper finds that countries that are not bound to comply with or that do not follow the UPOV 1991 model may provide for Farmers’ Rights relating to seeds with a broad scope; for example, in countries that still adhere to UPOV 1978 (such as Argentina, Brazil, China), the use and exchange by farmers of farm-saved seeds is legal, since those acts are outside the scope of the breeder’s rights.</t>
-  </si>
-  <si>
-    <t>Moreover, the policy space is even broader in countries that have adopted sui generis PVP regimes that do not follow the UPOV Convention (whether the 1978 or 1991 Acts), particularly with regard to the right to sell farm-saved seed.</t>
-  </si>
-  <si>
-    <t>The paper finds that on all these counts, UPOV fails to support the implementation of Farmers’ Rights. It notes in particular the major differences between the UPOV Acts of 1978 and 1991 regarding the right to save, use, exchange and sell farm-saved seeds and propagating materials: UPOV 1978 offers greater leeway to implement Farmers’ Rights, but there are still limitations, while UPOV 1991 greatly expands the scope of breeders’ rights and severely limits Farmers’ Rights.</t>
+    <t>The article finds that a sui generis system that incorpo­rates Farmers’ Rights, as well as ABS principles, is best suited to Nigeria’s socio-economic realities.</t>
+  </si>
+  <si>
+    <t>Thus, the article argues that the legal regime for PVP established under the Arusha Protocol is inappropriate for ARIPO members as it fails to balance breeders’ rights and Farmers’ Rights in a man­ner that promotes food security.</t>
+  </si>
+  <si>
+    <t>Giving the example of Kenya, the article finds that the role of PBRs as the core driver of greater foreign investment in agricultural activities is overrated.</t>
+  </si>
+  <si>
+    <t>The legislative bias in favour of the formal (corporate seed) sector is at the root of the contest between Farmers’ Rights enshrining practices of seed sovereignty, and a proprietorial PBR paradigm.</t>
+  </si>
+  <si>
+    <t>The article highlights the imbal­ance presented by the Act, between the interests of plant breed­ers who are the ultimate beneficiaries of PVP, and the rights of indigenous farmers, who are seemingly unsuspecting losers.</t>
+  </si>
+  <si>
+    <t>The article analyzes the content of the Arusha PVP Protocol, noting that several provisions go beyond UPOV 1991 require­ments, resulting in a Protocol that does not adequately ensure balance between private and public interests, the latter of which would include benefit sharing with the providers of ge­netic resources or associated traditional knowledge.</t>
+  </si>
+  <si>
+    <t>The article concludes that the goal of the PVP legislation to enable access by local farmers to high-value, higher-yielding foreign variet­ies, has not been fully met.</t>
+  </si>
+  <si>
+    <t>With regard to UPOV, the paper notes that it seems to confer excessive rights on breeders whilst Farmers’ Rights are marginalized, which could have serious repercussions on the realization of the right to food as farmers in these countries are the major food producers and suppliers.</t>
+  </si>
+  <si>
+    <t>The paper concludes that the sui generis system adopted by Ethiopia strikes the neces­sary balance between the interests of right holders and the pub­lic interest in general and Farmers’ Rights in particular.</t>
+  </si>
+  <si>
+    <t>The purpose is to encourage farmers to make full use of their plant genetic resources while encouraging the private sector to release new plant varieties suitable for the Malaysian agricultural sector.</t>
+  </si>
+  <si>
+    <t>This paper describes how India has enacted the Protection of Plant Varieties and Farmers’ Rights Act (PPVFRA), a sui generis struc­ture to protect plant varieties with a view to balancing both breeders’ rights and Farmers’ Rights, without becoming a mem­ber of UPOV or enacting a PVP law based on the UPOV model.</t>
+  </si>
+  <si>
+    <t>The PPVFRA protects farmers’ rights to save, use, exchange and share all farm produce, including non-branded seed, even of a protected variety. It protects biodiversity through a fund which recognizes and rewards the contributions made by indig­enous farmers; prescribes community rights; provides for ben­efit sharing, public interest exceptions and compulsory licens­ing.</t>
+  </si>
+  <si>
+    <t>The aim of the PVP Act is twofold: to protect PBRs in order to promote innovative plant breeding ac­tivities; and to recognize the rights of farmers in respect of their role in improving, conserving and using plant genetic resources (PGR).</t>
+  </si>
+  <si>
+    <t>The Act further allows protected plant varieties to be sold and exchanged without the breeder’s authorization when such use is consistent with ancestral agricultural practic­es or occurs in a traditional communitarian environment.</t>
+  </si>
+  <si>
+    <t>Where food production relies on wide­spread practices of saving, exchange and local sale of seeds and other planting materials, the national PVP law should recognize exceptions and protections for farmers.</t>
+  </si>
+  <si>
+    <t>The concept of Farmers’ Rights recog­nizes the role of farmers as custodians of biodiversity and draws attention to the need to preserve practices that are essential for sustainable agriculture.</t>
+  </si>
+  <si>
+    <t>Although some elements of the right to save, use, exchange and sell seeds have traditionally been regarded as part of what is known as the ‘farmers’ privilege’ under plant variety legislation, the evolution of the UPOV Convention and of national and regional laws that follow its model has been towards the narrowing down of the space left to farmers to dispose of the farm-saved seeds.</t>
+  </si>
+  <si>
+    <t>The paper finds that on all these counts, UPOV fails to support the implementation of Farmers’ Rights. It notes in par­ticular the major differences between the UPOV Acts of 1978 and 1991 regarding the right to save, use, exchange and sell farm-saved seeds and propagating materials: UPOV 1978 offers greater leeway to implement Farmers’ Rights, but there are still limitations, while UPOV 1991 greatly expands the scope of breeders’ rights and severely limits Farmers’ Rights.</t>
+  </si>
+  <si>
+    <t>The 1991 revision gives governments discretion on wheth­er to uphold Farmers’ Rights, which includes only the use of saved seed on the same farm (and thus excludes any type of ex­change or sale of such seed).</t>
   </si>
   <si>
     <t>The paper concludes that it is crucial for the countries to devise such measures that balance the interests of both breeders and farmers, and to protect the rights of farmers.</t>
   </si>
   <si>
-    <t>The proposed sui generis regime is articulated on the basis of: (1) new uniform plant varieties; (2) new farmer and other heterogeneous varieties; and (3) traditional farmers varieties.</t>
-  </si>
-  <si>
-    <t>In recognition of the crucial role that small farmers play in the production of food in developing countries, the proposed regime exempts them from any obligation in connection with the various categories of plant varieties, thereby fully safeguarding their right to freely save, use, exchange and sell seeds/propagating material. The proposed regime attempts to attain a right balance between breeders’ rights and those of farmers and society at large;</t>
-  </si>
-  <si>
-    <t>The proposed regime attempts to attain a right balance between breeders’ rights and those of farmers and society at large; ensure that farmers varieties and those developed by public research are not misappropriated; allow breeders to recoup investments in the development of new varieties; expand the use of new varieties suitable to the conditions in the country, taking into account the needs of small-scale farmers; support national policies of conservation and sustainable use of PGRFA, as well as compliance with the CBD, Nagoya Protocol and ITPGRFA; preserve associated TK and ensure the permanent adaptation of seeds to the evolution of agricultural ecosystems and food security; and respect, protect and fulfil human rights.</t>
-  </si>
-  <si>
-    <t>allow breeders to recoup investments in the development of new varieties; expand the use of new varieties suitable to the conditions in the country, taking into account the needs of small-scale farmers;</t>
-  </si>
-  <si>
-    <t>The paper recommends that any successful model put forward must be rooted in the development objectives of the particular country, and the objective must be to establish a PVP regime that includes and supports the interests of all affected.</t>
+    <t>This is evidenced, for example, by the formulation of seed laws, in particular PVP, seed certification and marketing laws that restrict and in some cases criminalize farmers’ right to free­ly use, save, exchange and sell farm-saved seed/propagating material.</t>
+  </si>
+  <si>
+    <t>The proposed regime exempts them from any obligation in connection with the vari­ous categories of plant varieties, thereby fully safeguarding their right to freely save, use, exchange and sell seeds/propagating material.</t>
+  </si>
+  <si>
+    <t>The proposed regime attempts to attain a right balance between breeders’ rights and those of farmers and society at large; ensure that farmers varieties and those developed by pub­lic research are not misappropriated; allow breeders to recoup investments in the development of new varieties;</t>
+  </si>
+  <si>
+    <t>This working paper is a tool to assist developing countries in de­signing a sui generis PVP system that is consistent with the re­quirements of the TRIPS Agreement, is suitable for their seed and agricultural systems, and promotes the objectives of the CBD, the Nagoya Protocol and the ITPGRFA.</t>
+  </si>
+  <si>
+    <t>It recommends that any successful model put forward must be rooted in the development objectives of the particular country, and the objective must be to establish a PVP regime that includes and supports the interests of all affected.</t>
   </si>
   <si>
     <t>Plant variety preservation and intellectual 
@@ -710,25 +729,6 @@
 preservation of genetic variation.</t>
   </si>
   <si>
-    <t>PVR regimes 
-encourage the generation of new varieties 
-that are suited to address changing market 
-needs and environmental issues by 
-providing incentives for research and 
-development.</t>
-  </si>
-  <si>
-    <t>However, the implementation of PVR 
-regulations raises complex ethical, legal and 
-socioeconomic considerations. Concerns 
-about farmers' rights, benefit-sharing 
-arrangements, and access to genetic 
-resources are major problems that highlight 
-the necessity of a comprehensive and 
-inclusive approach to plant variety 
-sustainability.</t>
-  </si>
-  <si>
     <t>This 
 research work evaluates agricultural 
 progress prior to the implementation of PVP 
@@ -737,6 +737,13 @@
 some of the provisions of the Act in relation 
 to innovation, attracting foreign 
 investments, and boost economic growth.</t>
+  </si>
+  <si>
+    <t>With food 
+security and economic growth depending 
+more and more on agricultural innovation, it 
+became clear that plant breeders' intellectual 
+property needed to be protected.</t>
   </si>
   <si>
     <t>Recognizing the importance of 
@@ -791,7 +798,11 @@
 plants.</t>
   </si>
   <si>
-    <t>This system encourages 
+    <t>PVRs 
+grant exclusive rights to breeders of new 
+plant varieties, allowing them to control the 
+propagation and commercialization of their 
+varieties. This system encourages 
 investment in plant breeding and crop 
 variety development, aiming to boost 
 agricultural productivity and innovation.</t>
@@ -811,46 +822,10 @@
 and investments are adequately rewarded.</t>
   </si>
   <si>
-    <t>The Nigeria Agricultural Quarantine 
-Service (NAQS) prevents the introduction, 
-establishment and spread of exotic pests and 
-diseases of plants and planting material into 
-and outside the country in order to 
-safeguard the nation's agricultural 
-economy.</t>
-  </si>
-  <si>
-    <t>The service control the 
-regional and international movement of 
-plant variety in order to prevent the 
-introduction and spread of diseases; control 
-of the production and registration of agro 
-pesticides and preventing pesticides or 
-mycotoxin contamination of agricultural 
-commodities; increasing agricultural 
-productivity, by contributing to wealth 
-creation and employment generation, in 
-order to ensure food security and rural 
-development.</t>
-  </si>
-  <si>
-    <t>The National Agricultural Seed Council 
-NASC (2007) is instrumental in Nigeria's 
-seed sector regulation, overseeing the Plant 
-Breeders' Rights Act implementation, 
-promote and stimulate the development of 
-dependable seed industry, facilitating the 
-registration of new plant varieties, protect 
-farmers from the sales of poor quality seeds, 
-facilitate the production and marketing of 
-high quality seeds in Nigeria</t>
-  </si>
-  <si>
-    <t>This 
-includes monitoring the market for potential 
-infringements and taking legal action 
-against unauthorized use of protected 
-varieties.</t>
+    <t>These rights 
+may include the right to prevent others from 
+making, using, selling, or importing the 
+protected variety.</t>
   </si>
   <si>
     <t>The Plant Variety Protection Act (2021) 
@@ -871,9 +846,17 @@
 functions.</t>
   </si>
   <si>
-    <t>Any authorization given by the plant 
-breeder may be subject to conditions and 
-limitations. However, such exclusive rights 
+    <t>A plant breeder has exclusive rights to 
+propagate materials of a protected variety. 
+Authorization must be obtained from such a 
+breeder for the production and 
+reproduction, conditioning for propagation; 
+offering for sale; selling or marketing; 
+exporting; importing and stocking in 
+relation to any of the mentioned purposes.</t>
+  </si>
+  <si>
+    <t>However, such exclusive rights 
 of a plant breeder cannot impede the doing 
 of the following acts by a third party without 
 authorization: Private and non-commercial 
@@ -881,13 +864,6 @@
 the purpose of breeding any other variety, 
 except it is essentially derived from an 
 initially protected variety.</t>
-  </si>
-  <si>
-    <t>The Plant Variety 
-Protection Act 2021 makes provision for the 
-holder of a plant breeder’s right to assign or 
-authorize any activity in relation to a 
-registered plant variety.</t>
   </si>
   <si>
     <t>The PVP Act grants 
@@ -934,9 +910,7 @@
 relation to any registered plant variety. This 
 also opens investment opportunities for 
 investors seeking to explore this aspect of 
-agriculture and further creates job 
-opportunities for people skilled in 
-agriculture.</t>
+agriculture</t>
   </si>
   <si>
     <t>The National Agricultural 
@@ -958,7 +932,7 @@
     <t>Al dertig jaar beschermt het systeem van het Communautair Bureau voor plantenrassen (CBP) effectief dit intellectueel eigendom om innovatie aan te jagen. De voorgaande evaluatie in 2011 en de gezamenlijke studie van het CBP en EUIPO uit 2022 bekrachtigden dit. Om een doeltreffend CBP-systeem te behouden is het de hoogste tijd deze EU-wetgeving te moderniseren, menen Glastuinbouw Nederland en LTO Nederland.</t>
   </si>
   <si>
-    <t>Kwekersrecht kan worden aangevraagd door veredelaars en ontdekkers van plantenrassen. Dit eigendomsrecht geeft de kweker 25 à 30 jaar het exclusieve recht om die plant te verhandelen en te vermeerderen. Alle plantensoorten vallen hieronder. Daarmee is deze wetgeving ook van groot belang voor Europese boeren en tuinders, omdat het veredelaars beschermt, hen een verdienmodel geeft en hen stimuleert om te blijven innoveren en weerbaardere rassen te ontwikkelen.</t>
+    <t>Daarmee is deze wetgeving ook van groot belang voor Europese boeren en tuinders, omdat het veredelaars beschermt, hen een verdienmodel geeft en hen stimuleert om te blijven innoveren en weerbaardere rassen te ontwikkelen. Dat komt de verduurzaming van de algehele land- en tuinbouw in de Unie ten goede.</t>
   </si>
   <si>
     <t>Diverse rechtszaken hebben de vrijstelling voor eigen vermeerdering (FSS) in Europa moeilijk handhaafbaar gemaakt, terwijl FSS al een aanzienlijke beperking is van het kwekersrecht. Beperkt beschikbare informatie over het gebruik van eigen vermeerdering door boeren en tuinders en beperkte naleving van de vereisten zetten FSS verder onder druk.</t>
@@ -967,628 +941,535 @@
     <t>Bovendien zijn Glastuinbouw Nederland en LTO Nederland van mening dat de lijsten onder artikel 14 van de onderhavige Verordening (EU) 94/2100 op lidstaatniveau moeten worden geanalyseerd. Veredelingsprogramma’s voor diverse plantensoorten zijn afgenomen, hetgeen de beschikbaarheid van nieuwe variëteiten voor boeren en tuinders in de toekomst beteugelt.</t>
   </si>
   <si>
-    <t>Daarmee rijst de vraag in hoeverre het kwekersrecht daadwerkelijk effectief en van meerwaarde is voor het beschermen van deze meerjarige rassen.</t>
+    <t>Als gevolg van de Nadorcott-zaak vallen producten die zijn geoogst van planten die zijn aangeplant vóór de verlening van het kwekersrecht niet langer onder dit recht. Zelfs niet wanneer oogst na verlening plaatsvindt. Dit schaadt de Europese fruit- en sierteeltsector ernstig, die traditioneel met meerjarige gewassen werkt. Daarmee rijst de vraag in hoeverre het kwekersrecht daadwerkelijk effectief en van meerwaarde is voor het beschermen van deze meerjarige rassen.</t>
+  </si>
+  <si>
+    <t>De definitie van een EDV is overgelaten aan nationale jurisdicties. Dit leidt tot wereldwijd een lappendeken van verschillende interpretaties. Juist met het CBP heeft de EU een belangrijke troef in handen om EDV te harmoniseren in haar lidstaten om zo een voorbeeld te vormen voor derde landen.</t>
   </si>
   <si>
     <t>Harmonisatie van de EDV-definitie zal in de toekomst alleen maar belangrijker worden door de technologische en juridische ontwikkelingen op gebied van biotechnologie en nieuwe veredelingstechnieken. Het is cruciaal dat onze boeren en tuinders zoveel mogelijk van deze innovaties kunnen profiteren.</t>
   </si>
   <si>
+    <t>Gecentraliseerde en gespecialiseerde rechtbanken voor plantenrassenbescherming (PVP) op landelijk en EU-niveau - conform het Nederlandse model - kunnen helpen om hier meer juridische ervaring en kennis over op te doen. Voorts draagt dit bij aan de harmonisatie van het kwekersrecht in de verschillende EU-lidstaten.</t>
+  </si>
+  <si>
+    <t>Glastuinbouw Nederland en LTO Nederland zien unieke kansen om met NGTs, zoals CRISPR-Cas, de plantaardige sectoren in Europe verder te verduurzamen en weerbaarder te maken. Dit mag echter noch tot financiële lasten voor boeren en tuinders noch tot verdere consolidatie in de zaadveredelingsbranche leiden. NGTs zijn bij uitstek toegankelijk voor grote en kleine veredelingsbedrijven. Het kwekersrecht is nodig voor de borging van verdere veredeling en eerlijke concurrentie, zodat een brede variatie van gewasgroepen en rassen beschikbaar blijft voor onze boeren en tuinders.</t>
+  </si>
+  <si>
+    <t>Dit mag echter noch tot financiële lasten voor boeren en tuinders noch tot verdere consolidatie in de zaadveredelingsbranche leiden. NGTs zijn bij uitstek toegankelijk voor grote en kleine veredelingsbedrijven. Het kwekersrecht is nodig voor de borging van verdere veredeling en eerlijke concurrentie, zodat een brede variatie van gewasgroepen en rassen beschikbaar blijft voor onze boeren en tuinders.</t>
+  </si>
+  <si>
+    <t>Het huidige systeem van kwekersrecht, geborgd door het CPB, waarin als intrinsiek onderdeel van het recht nieuwe rassen mogen worden gebruikt en verder ontwikkeld door concurrent-veredelaars zolang er maar een nieuw, onderscheidbaar ras uit voortkomt, zorgt voor meer beschikbare genetische variëteiten met de beste innovaties voor alle veredelaars en daardoor uiteindelijk tot meer en betere rassen voor onze boeren en tuinders.</t>
+  </si>
+  <si>
+    <t>Vooral in het licht van voedselsoevereiniteit en verduurzaming van onze teelten is het noodzakelijk dat veredelaars kunnen putten uit een grote, internationale genenpool voor breed onderzoek en ontwikkeling en dat zij beschikken over een eerlijk verdienmodel, inclusief het mechanisme dat borgt dat belangrijke innovaties niet exclusief bij een enkel veredelingsbedrijf blijven liggen. Het zou een sterke afhankelijkheid van boeren en tuinders aan veredelaars kunnen creëren in het geval er licentiebetalingen aan patenthouders gedaan moeten worden om hun innovaties te kunnen inzetten voor verdere veredeling.</t>
+  </si>
+  <si>
+    <t>Glastuinbouw Nederland en LTO Nederland geloven daarom dat een sterk en effectief CBP-systeem kwekersrechten beter kan beschermen, hetgeen een diverse, duurzame en weerbare land- en tuinbouw in Europa bevordert.</t>
+  </si>
+  <si>
+    <t>De afgelopen 30 jaar is het CBP-systeem veredelaars, boeren, tuinders en de maatschappij als geheel van dienst geweest. Na drie decennia is het de hoogste tijd om dit systeem te moderniseren, opdat het ook geschikt blijft voor de toekomst.</t>
+  </si>
+  <si>
+    <t>To ensure breeders can benefit from the full scope of protection provided for under UPOV 1991 and to make the system future-proof in view of technical progress in plant breeding, the Basic Regulation and related regulations should be improved and clarified, including without limitation:</t>
+  </si>
+  <si>
+    <t>Furthermore, cost-efficient enforcement measures should be available for breeders to act against unauthorized use of protected plant material and harvested material.</t>
+  </si>
+  <si>
+    <t>The trigger for exhaustion in Article 16 Basic Regulation (disposed of to others) deviates from the wording used in Article 16 UPOV 1991 (sold or otherwise marketed). The trigger for exhaustion should be clarified.</t>
+  </si>
+  <si>
+    <t>Enforcement. Holders of CPVR should have the same rights and remedies granted to other IP holders under the EU enforcement directive. To this end, the relation between the Basic Regulation and the EU enforcement directive should be clarified.</t>
+  </si>
+  <si>
+    <t>The definition of EDVs under Article 13(6), especially as regards the concepts of "predominantly derived" under Article 13(6)(a) and "conforms essentially to the initial variety in the expression of the characteristics …." under Article 13(6)(c), should be updated taking into account the guidance provided by the Explanatory Notes on Essentially Derived Varieties under the 1991 Act of the UPOV Convention, adopted by the Council at its fifty-seventh ordinary session on 27 October 2023</t>
+  </si>
+  <si>
+    <t>However, the concept of reasonable compensation is extremely vague and lends itself to different interpretations at the national level in the case of enforcement. For provisional protection to be effective, it would be advisable to delineate the concept of "reasonable compensation" in its conceivable amount so as to provide reliable reference elements for (prospective) rights holders to prevent acts potentially adversely affecting their PVRs, where subsequently granted.</t>
+  </si>
+  <si>
+    <t>A harmonization of terminology with the UPOV Convention might be advisable as well as the inclusion of a specific article providing for basic definitions.</t>
+  </si>
+  <si>
+    <t>However, the implementation of PVR regulations raises complex ethical, legal and socioeconomic considerations. Concerns about farmers' rights, benefit-sharing arrangements, and access to genetic resources are major problems that highlight the necessity of a comprehensive and inclusive approach to plant variety sustainability.</t>
+  </si>
+  <si>
+    <t>One of the most significant developments was the adoption of the International Union for the Protection of New Plant Varieties Convention (UPOV Convention) in 1961. The UPOV system of plant variety protection came into being with the adoption of the International Convention for the Protection of New Varieties of Plants by a Diplomatic Conference in Paris on December 2, 1961.</t>
+  </si>
+  <si>
+    <t>Nigeria was not a signatory to the International Union for the Protection of New Varieties of Plants (UPOV) Convention (Okonkwo, et al 2021) which to a large extent impeded the exploitation of such rights. It even deprived plant breeders in Nigeria access to high-quality new varieties of plant from foreign countries and also discourages foreign plant breeders since their new plant variety cannot be protected.</t>
+  </si>
+  <si>
+    <t>Meanwhile, the Trade-Related Aspects of Intellectual Property Rights Agreement (TRIPS), which Nigeria is a signatory to, recognizes and provides for the patentability of inventions in all fields of technology and specifically calls for the protection of plant varieties either by patent or by an effective sui generis system or by any combination thereof in line with the provisions of Article 27 of the TRIPS Agreement.</t>
+  </si>
+  <si>
+    <t>The Act aligns with international standards, such as those set by the International Union for the Protection of New Varieties of Plants (UPOV).</t>
+  </si>
+  <si>
+    <t>In some jurisdictions like the United State and Australia, the subject matter of protection covered by a Traditional IP and by a plant breeder’s right might be the same, namely a plant variety while in several other jurisdictions like European Union and India, the subject matter of protection is different, and, in general, plant varieties are excluded from patentability.</t>
+  </si>
+  <si>
+    <t>As far as the International Union for the Protection of New Plant Varieties Convention (UPOV) is concerned, a member is free to protect plant varieties, in addition to the grant of a breeder’s right, by the grant of other titles, particularly patents.</t>
+  </si>
+  <si>
+    <t>The International Union for the Protection of New Varieties of Plants (UPOV) is an intergovernmental organization based in Geneva, Switzerland established in 1961. UPOV provides a sui generis system for the protection of plant varieties and the rights of plant breeders by ensuring that their effort and investments are adequately rewarded.</t>
+  </si>
+  <si>
+    <t>The Agreement on Trade-Related Aspects of Intellectual Property Rights (TRIPS) is administered by the World Trade Organization (WTO). According to the Agreement on Trade-Related Aspect of Intellectual Property Right (1994), the treaty covers a broader range of intellectual property rights, including patents, trademarks, copyrights, and trade secrets, in addition to PVP. TRIPS do not specify detailed criteria for plant variety protection but requires member countries to establish effective systems for the protection of plant varieties.</t>
+  </si>
+  <si>
+    <t>The Service also set a defined standards on agricultural quarantine procedure; ensuring compliance with International agreements, protocols, conventions and treaties on agricultural quarantine, including forestry, endangered species, plants variety and planting materials; monitoring the agricultural quarantine Regulations and standards; ensuring that agricultural quarantine projects are carried out in compliance with plant variety and public health regulations;</t>
+  </si>
+  <si>
+    <t>NASC is responsible for enforcing PVP rights in Nigeria. This includes monitoring the market for potential infringements and taking legal action against unauthorized use of protected varieties.</t>
+  </si>
+  <si>
+    <t>A breeder right can be protected by both civil and criminal measures stipulated in any written law. An action can also be instituted in court against any person who infringes the breeder right (Section 33 (2) Plant Variety Protection Act 2021).</t>
+  </si>
+  <si>
+    <t>The Registrar should make effective guidelines for the effective implementation of the Act.</t>
+  </si>
+  <si>
+    <t>The National Agricultural Seeds Council (NASC) should be given adequate resources and trained personnel to effectively manage the PVP system. This will endeavour that NASC can handle applications, conduct examinations and enforce rights where necessary.</t>
+  </si>
+  <si>
+    <t>A well structured awareness program could be implemented at all level of the society to sensitize farmers, breeders, legislators and the general public on the intellectual property rights and plant variety rights and how they support innovation and food security.</t>
+  </si>
+  <si>
+    <t>Regular monitoring of the market for unauthorized use or infringement on plant varieties. Prompt action should be taken to enforce intellectual property rights through legal means such as sending cease-and-desist letters or pursuing litigation.</t>
+  </si>
+  <si>
+    <t>Gecentraliseerde en gespecialiseerde rechtbanken voor plantenrassenbescherming (PVP) op landelijk en EU-niveau – conform het Nederlandse model – kunnen helpen om hier meer juridische ervaring en kennis over op te doen.</t>
+  </si>
+  <si>
     <t>Voorts draagt dit bij aan de harmonisatie van het kwekersrecht in de verschillende EU-lidstaten.</t>
   </si>
   <si>
-    <t>Glastuinbouw Nederland en LTO Nederland zien unieke kansen om met NGTs, zoals CRISPR-Cas, de plantaardige sectoren in Europe verder te verduurzamen en weerbaarder te maken. Dit mag echter noch tot financiële lasten voor boeren en tuinders noch tot verdere consolidatie in de zaadveredelingsbranche leiden. NGTs zijn bij uitstek toegankelijk voor grote en kleine veredelingsbedrijven. Het kwekersrecht is nodig voor de borging van verdere veredeling en eerlijke concurrentie, zodat een brede variatie van gewasgroepen en rassen beschikbaar blijft voor onze boeren en tuinders.</t>
-  </si>
-  <si>
-    <t>Het kwekersrecht is nodig voor de borging van verdere veredeling en eerlijke concurrentie, zodat een brede variatie van gewasgroepen en rassen beschikbaar blijft voor onze boeren en tuinders.</t>
-  </si>
-  <si>
-    <t>Het huidige systeem van kwekersrecht, geborgd door het CPB, waarin als intrinsiek onderdeel van het recht nieuwe rassen mogen worden gebruikt en verder ontwikkeld door concurrent-veredelaars zolang er maar een nieuw, onderscheidbaar ras uit voortkomt, zorgt voor meer beschikbare genetische variëteiten met de beste innovaties voor alle veredelaars en daardoor uiteindelijk tot meer en betere rassen voor onze boeren en tuinders.</t>
-  </si>
-  <si>
-    <t>Vooral in het licht van voedselsoevereiniteit en verduurzaming van onze teelten is het noodzakelijk dat veredelaars kunnen putten uit een grote, internationale genenpool voor breed onderzoek en ontwikkeling en dat zij beschikken over een eerlijk verdienmodel, inclusief het mechanisme dat borgt dat belangrijke innovaties niet exclusief bij een enkel veredelingsbedrijf blijven liggen. Het zou een sterke afhankelijkheid van boeren en tuinders aan veredelaars kunnen creëren in het geval er licentiebetalingen aan patenthouders gedaan moeten worden om hun innovaties te kunnen inzetten voor verdere veredeling.</t>
-  </si>
-  <si>
-    <t>Glastuinbouw Nederland en LTO Nederland geloven daarom dat een sterk en effectief CBP-systeem kwekersrechten beter kan beschermen, hetgeen een diverse, duurzame en weerbare land- en tuinbouw in Europa bevordert.</t>
-  </si>
-  <si>
-    <t>De afgelopen 30 jaar is het CBP-systeem veredelaars, boeren, tuinders en de maatschappij als geheel van dienst geweest. Na drie decennia is het de hoogste tijd om dit systeem te moderniseren, opdat het ook geschikt blijft voor de toekomst.</t>
-  </si>
-  <si>
-    <t>Furthermore, cost-efficient enforcement measures should be available for breeders to act against unauthorized use of protected plant material and harvested material.</t>
-  </si>
-  <si>
-    <t>The trigger for exhaustion in Article 16 Basic Regulation (disposed of to others) deviates from the wording used in Article 16 UPOV 1991 (sold or otherwise marketed). The trigger for exhaustion should be clarified.</t>
-  </si>
-  <si>
-    <t>- Enforcement. Holders of CPVR should have the same rights and remedies granted to other IP holders under the EU enforcement directive. To this end, the relation between the Basic Regulation and the EU enforcement directive should be clarified.</t>
-  </si>
-  <si>
-    <t>The definition of EDVs under Article 13(6), especially as regards the concepts of "predominantly derived" under Article 13(6)(a) and "conforms essentially to the initial variety in the expression of the characteristics …." under Article 13(6)(c), should be updated taking into account the guidance provided by the Explanatory Notes on Essentially Derived Varieties under the 1991 Act of the UPOV Convention, adopted by the Council at its fifty-seventh ordinary session on 27 October 2023</t>
-  </si>
-  <si>
-    <t>However, the concept of reasonable compensation is extremely vague and lends itself to different interpretations at the national level in the case of enforcement. For provisional protection to be effective, it would be advisable to delineate the concept of "reasonable compensation" in its conceivable amount so as to provide reliable reference elements for (prospective) rights holders to prevent acts potentially adversely affecting their PVRs, where subsequently granted.</t>
-  </si>
-  <si>
-    <t>A harmonization of terminology with the UPOV Convention might be advisable as well as the inclusion of a specific article providing for basic definitions.</t>
-  </si>
-  <si>
-    <t>All countries, regardless of their development level, have been progressively strengthening their intellectual property rights (IPR) systems (Campi and Nuvolari, 2015; 2020). The move towards stronger intellectual property (IP) protection has been largely driven by external processes, derived from obligations under the World Trade Organization’s (WTO) Agreement on Trade-Related Aspects of Intellectual Property Rights (TRIPS) and the adoption of TRIPS-plus provisions, the latter often mediated via North-South free trade agreements (FTAs).</t>
-  </si>
-  <si>
-    <t>The WTO’s TRIPS Agreement only requires that WTO members provide for the protection of plant varieties either by patents or by an effective sui generis system or by any combination thereof, without specifying further what a sui generis system should be. No country should be forced to establish an IPR regime that goes beyond the minimum requirements of the TRIPS Agreement, including through FTAs obliging countries to join UPOV 1991 or to adopt UPOV-compliant legislation (De Schutter, 2009).</t>
-  </si>
-  <si>
-    <t>UPOV 1991 requirements can also undermine implementation of the Convention on Biological Diversity (CBD), its Nagoya Protocol on Access to Genetic Resources and the Fair and Equitable Sharing of Benefits Arising from their Utilization, and the International Treaty on Plant Genetic Resources for Food and Agriculture (ITPGRFA) (Correa, 2015).</t>
-  </si>
-  <si>
-    <t>One conclusion is that the TRIPS Agreement leaves sufficient discretion to governments to design PVP laws in such a way that the obligations of other treaties are addressed, but that the possibilities for developing countries to implement Farmers’ Rights in their national PVP laws are very restricted once they join UPOV 1991.</t>
-  </si>
-  <si>
-    <t>(5) There is a lack of information and participation of small-scale farmers in the process of developing PVP-related laws, and a lack of assessment of the likely impacts of these laws.</t>
-  </si>
-  <si>
-    <t>No state should be forced to establish an IPR regime that goes beyond the minimum requirements of the TRIPS Agreement; FTAs obliging countries to join UPOV 1991 or to adopt UPOV-compliant legislation, therefore, are questionable.</t>
-  </si>
-  <si>
-    <t>The paper finds that all countries, regardless of their development level, have been tightening their IPR systems, driven by exogenous processes derived from TRIPS obligations and adoption of TRIPS-plus provisions, rather than a response to domestic needs.</t>
-  </si>
-  <si>
-    <t>The results point to a dysfunctional PVP system that does not fit the socio-economic and agricultural conditions in the region. Only seven of the current 17 OAPI member states have made use of the system, at great cost and at the expense of public funds. Only 51 PVP Certificates are in force after 10 years and the private sector’s use of the system is negligible.</t>
-  </si>
-  <si>
-    <t>The note, by researchers from Wageningen University and Research Centre and the Overseas Development Institute, explains how the TRIPS Agreement places obligations on WTO members to provide minimum standards of IP protection, but also leaves developing countries a certain amount of flexibility to tailor IPR regimes to their specific circumstances.</t>
-  </si>
-  <si>
-    <t>The study concludes by pointing to significant lessons, including: (1) IPR regimes should be consistent with developing countries’ priorities and capacities instead of being externally imposed;</t>
-  </si>
-  <si>
-    <t>The primary aim of the study is to address the linkages between the requirements of the Nagoya Protocol, ITPGRFA, and PVP under the UPOV Convention, specifically reviewing measures to implement obligations under the three treaties in the EU and Switzerland.</t>
-  </si>
-  <si>
-    <t>It concludes that sui generis PVP systems adopted outside of the UPOV Convention framework – as permitted by TRIPS – may provide a way to better balance rights and obligations relating to the Nagoya Protocol, Plant Treaty and PVP.</t>
-  </si>
-  <si>
-    <t>The paper also describes the institutional features of UPOV, its relationship with WIPO and how participation in UPOV’s work is engendered, and presents some of the discussions around alternatives to UPOV, given that there is no legal basis for implying that a non-UPOV-compliant PVP law is contrary to the TRIPS Agreement simply for being inconsistent with UPOV.</t>
-  </si>
-  <si>
-    <t>The paper focuses on UPOV as an institution, as it is the sole international agency concerned with IP protection of new plant varieties, and concerns have been expressed about the lack of transparency, democratic accountability and possibilities for public debate in its operation.</t>
-  </si>
-  <si>
-    <t>The lack of a counterfactual that would allow an assessment of what could be expected to have happened without the measure/policy/convention in place, leaves UPOV’s study only able to show a correlation between the introduction of the UPOV Convention and certain trends, but failing to make convincing arguments in favour of causality.</t>
-  </si>
-  <si>
-    <t>This thesis analyzes multilateral, continental and regional IP and trade agreements for how their provisions integrate IP (PBRs and patents) and food security norms and policies, and the extent to which IP frameworks are adaptable to the regional conditions that determine food security in the West African context.</t>
-  </si>
-  <si>
-    <t>The African Model Law was drafted to guide African countries in fulfilling their international obligations. These are, inter alia, the CBD, the TRIPS Agreement and ITPGRFA, which oblige Parties to introduce ABS laws, Farmers’ Rights and PVP systems.</t>
-  </si>
-  <si>
-    <t>Most countries pass seed laws without the knowledge and/or effective participation of the smallholder farmers directly affected.</t>
-  </si>
-  <si>
-    <t>The article details the expert consensus that developing countries complying with TRIPS are better off opting for a sui generis PVP system in light of their development status, societal needs, and treaty obligations in TRIPS, the CBD and the ITPGRFA.</t>
-  </si>
-  <si>
-    <t>The conflicts between international agreements such as the CBD and ITPGRFA on the one hand, and UPOV and TRIPS on the other, were transposed in the national PVP laws as countries attempted to reconcile conflicting interests of different stakeholders.</t>
-  </si>
-  <si>
-    <t>The wording of Article 27.3(b), vis-à-vis a sui generis system of protection, creates interpretative difficulties as to what type of sui generis system WTO members should adopt to protect plant varieties.</t>
-  </si>
-  <si>
-    <t>However, in reality, and as the article concludes, it is still not clear whether farmers and local communities can benefit from such provisions because their varieties in practice do not pass the DUS eligibility requirements.</t>
-  </si>
-  <si>
-    <t>The practical implementation of these rights, however, has been hindered by IP laws, seed laws and other regulations.</t>
-  </si>
-  <si>
-    <t>The paper also finds flaws with WIPO’s technical assistance and support, which is always about the introduction of PVP laws modelled on UPOV 1991, even if such a model is unsuitable for the beneficiary country.</t>
-  </si>
-  <si>
-    <t>However, the operationalization of Article 9.2(c) at the national, regional and international levels is severely lacking. Farmers face considerable challenges in exercising their right to participate, with the consequence that decisions not only ignore their needs, but also adversely affect farmers’ freedom to operate.</t>
-  </si>
-  <si>
-    <t>This working paper is a tool to assist developing countries in designing a sui generis PVP system that is consistent with the requirements of the TRIPS Agreement, is suitable for their seed and agricultural systems, and promotes the objectives of the CBD, the Nagoya Protocol and the ITPGRFA.</t>
-  </si>
-  <si>
-    <t>Some countries have opted to join UPOV 1991 in order to comply with TRIPS, many in response to pressures from developed countries or obligations imposed in FTAs.</t>
-  </si>
-  <si>
-    <t>The study explains the different forms of legal protection required by international IPR agreements, including the system of PBRs in UPOV 1978 and 1991, the choice between patent and sui generis protection created by Article 27.3(b) of the TRIPS Agreement, and the impact of TRIPS-plus bilateral and regional treaties.</t>
-  </si>
-  <si>
-    <t>Nigeria was not a signatory to the International Union for the Protection of New Varieties of Plants (UPOV) Convention (Okonkwo, et al 2021) which to a large extent impeded the exploitation of such rights. It even deprived plant breeders in Nigeria access to high-quality new varieties of plant from foreign countries and also discourages foreign plant breeders since their new plant variety cannot be protected.</t>
-  </si>
-  <si>
-    <t>One of the most significant developments was the adoption of the International Union for the Protection of New Plant Varieties Convention (UPOV Convention) in 1961. The UPOV system of plant variety protection came into being with the adoption of the International Convention for the Protection of New Varieties of Plants by a Diplomatic Conference in Paris on December 2, 1961.</t>
-  </si>
-  <si>
-    <t>Meanwhile, the Trade-Related Aspects of Intellectual Property Rights Agreement (TRIPS), which Nigeria is a signatory to, recognizes and provides for the patentability of inventions in all fields of technology and specifically calls for the protection of plant varieties either by patent or by an effective sui generis system or by any combination thereof in line with the provisions of Article 27 of the TRIPS Agreement. Member states of the TRIPS Agreement are obligated to comply with this mandate.</t>
-  </si>
-  <si>
-    <t>The Act aligns with international standards, such as those set by the International Union for the Protection of New Varieties of Plants (UPOV). PVRs grant exclusive rights to breeders of new plant varieties, allowing them to control the propagation and commercialization of their varieties.</t>
-  </si>
-  <si>
-    <t>In some jurisdictions like the United State and Australia, the subject matter of protection covered by a Traditional IP and by a plant breeder’s right might be the same, namely a plant variety while in several other jurisdictions like European Union and India, the subject matter of protection is different, and, in general, plant varieties are excluded from patentability.</t>
-  </si>
-  <si>
-    <t>As far as the International Union for the Protection of New Plant Varieties Convention (UPOV) is concerned, a member is free to protect plant varieties, in addition to the grant of a breeder’s right, by the grant of other titles, particularly patents. This policy matter is left to the sovereign decision of each member.</t>
-  </si>
-  <si>
-    <t>The National Agricultural Seeds Council (NASC) should be given adequate resources and trained personnel to effectively manage the PVP system. This will endeavour that NASC can handle applications, conduct examinations and enforce rights where necessary.</t>
-  </si>
-  <si>
-    <t>A well structured awareness program could be implemented at all level of the society to sensitize farmers, breeders, legislators and the general public on the intellectual property rights and plant variety rights and how they support innovation and food security.</t>
-  </si>
-  <si>
-    <t>Regular monitoring of the market for unauthorized use or infringement on plant varieties. Prompt action should be taken to enforce intellectual property rights through legal means such as sending cease-and-desist letters or pursuing litigation.</t>
-  </si>
-  <si>
-    <t>Gecentraliseerde en gespecialiseerde rechtbanken voor plantenrassenbescherming (PVP) op landelijk en EU-niveau – conform het Nederlandse model – kunnen helpen om hier meer juridische ervaring en kennis over op te doen.</t>
-  </si>
-  <si>
-    <t>Al dertig jaar beschermt het systeem van het Communautair Bureau voor plantenrassen (CBP) effectief dit intellectueel eigendom om innovatie aan te jagen. De voorgaande evaluatie in 2011 en de gezamenlijke studie van het CBP en EUIPO uit 2022 bekrachtigden dit.</t>
-  </si>
-  <si>
     <t>Nederlandse boeren en tuinders zijn kritisch op octrooien, zeker met het oog op NGTs. Octrooien ondermijnen het kwekersrecht als primair intellectueel eigendomsrecht.</t>
   </si>
   <si>
-    <t>This passage directly states legislative and policy aims of the Basic Regulation, including fostering innovation and providing balanced protection.</t>
-  </si>
-  <si>
-    <t>The passage explicitly links CPVR protection to innovation in plant breeding and investment in plant innovations.</t>
-  </si>
-  <si>
-    <t>The phrase 'strong and balanced IP protection for all stakeholders' is directly relevant to how CPVR should balance rights and interests within the system.</t>
-  </si>
-  <si>
-    <t>This passage discusses negative effects on the plant breeding industry and a chilling effect on releasing new varieties, which relates to innovation outcomes and market activity.</t>
-  </si>
-  <si>
-    <t>The passage addresses the scope of breeders' enforcement rights and how legal interpretation affects the balance of protection under CPVR.</t>
-  </si>
-  <si>
-    <t>This directly concerns the legal protection and enforcement regime for CPVR holders, relevant to the balance and proportionality of rights under the system.</t>
-  </si>
-  <si>
-    <t>This passage is about the scope and effectiveness of rights during provisional protection, including compensation and enforcement clarity under CPVR.</t>
-  </si>
-  <si>
-    <t>This statement sets out overarching policy objectives for the CPVR framework: ensuring full protection and future-proofing the system.</t>
-  </si>
-  <si>
-    <t>The reference to technical progress in plant breeding connects CPVR reform to innovation and the breeding environment.</t>
-  </si>
-  <si>
-    <t>Directly discusses balancing breeders’ rights with Farmers’ Rights in PVP laws.</t>
-  </si>
-  <si>
-    <t>Explicitly refers to balancing Farmers’ Rights and breeders’ rights within PVP regimes.</t>
-  </si>
-  <si>
-    <t>Addresses CPVR/PVP-related effects on innovation and sector development.</t>
-  </si>
-  <si>
-    <t>Direct evidence on impact of PVP on breeding activity, innovation, and market development.</t>
-  </si>
-  <si>
-    <t>Direct statement about balancing breeders’ and farmers’ rights in PVP systems.</t>
-  </si>
-  <si>
-    <t>Clearly addresses the balance between breeders’ rights and Farmers’ Rights.</t>
-  </si>
-  <si>
-    <t>Discusses exceptions and limitations to breeders’ rights in favor of farmers’ rights.</t>
-  </si>
-  <si>
-    <t>Explicit reference to objectives of national PVP law and how laws should achieve them.</t>
-  </si>
-  <si>
-    <t>Directly concerns innovation outcomes in seed systems under PVP/IP policy.</t>
-  </si>
-  <si>
-    <t>Directly addresses innovation effects of plant variety IP protection.</t>
-  </si>
-  <si>
-    <t>Clear evidence on lack of innovation and market development impact from UPOV-style PVP.</t>
-  </si>
-  <si>
-    <t>Addresses innovation/seed sector development and market-oriented effects of PVP/IPRs.</t>
-  </si>
-  <si>
-    <t>Explicitly frames PVP/IP design as balancing rights and obligations between breeders and farmers.</t>
-  </si>
-  <si>
-    <t>Direct evidence on market development and breeding sector dynamics under PVP/IP regimes.</t>
-  </si>
-  <si>
-    <t>Relevant to proportional design of plant variety rights frameworks balancing different interests.</t>
-  </si>
-  <si>
-    <t>Directly addresses balanced accommodation of breeders’ and farmers’ rights.</t>
-  </si>
-  <si>
-    <t>Concise evidence on innovation investment patterns linked to plant variety protection.</t>
-  </si>
-  <si>
-    <t>Directly addresses market presence and breeding activity outcomes from PVP regimes.</t>
-  </si>
-  <si>
-    <t>Direct evidence on market access/trade effects of plant variety protection.</t>
-  </si>
-  <si>
-    <t>References assessment of whether the PVP system aligns with public policy objectives.</t>
-  </si>
-  <si>
-    <t>States claimed performance achievements of the PVP system against its intended goals.</t>
-  </si>
-  <si>
-    <t>Directly concerns varietal innovation and competitiveness outcomes.</t>
-  </si>
-  <si>
-    <t>Direct evidence on limited innovation effects of PVP systems.</t>
-  </si>
-  <si>
-    <t>Addresses tailoring rights to protect farmers’ practices alongside breeder protection.</t>
-  </si>
-  <si>
-    <t>Explicit statement on balancing breeders’ and farmers’ interests.</t>
-  </si>
-  <si>
-    <t>Direct evidence of legal design balancing rights across stakeholder groups.</t>
-  </si>
-  <si>
-    <t>Directly addresses balancing breeders’ rights and Farmers’ Rights in PVP design.</t>
-  </si>
-  <si>
-    <t>Directly concerns imbalance between breeders’ and farmers’ rights under a PVP regime.</t>
-  </si>
-  <si>
-    <t>Explicitly states failure to balance breeders’ and farmers’ rights.</t>
-  </si>
-  <si>
-    <t>Clear discussion of imbalance between breeder and farmer rights.</t>
-  </si>
-  <si>
-    <t>Addresses imbalance and lack of consideration of farmers’ interests in PVP rulemaking.</t>
-  </si>
-  <si>
-    <t>Directly assesses whether a stated goal of PVP legislation was achieved.</t>
-  </si>
-  <si>
-    <t>Direct statement that a PVP regime balances right holders and Farmers’ Rights.</t>
-  </si>
-  <si>
-    <t>Explicitly frames the law as balancing breeder incentives with Farmers’ Rights.</t>
-  </si>
-  <si>
-    <t>Direct evidence on farmers’ rights, public interest exceptions, benefit sharing and compulsory licensing.</t>
-  </si>
-  <si>
-    <t>Directly addresses balancing breeders’ and farmers’ rights in one PVP regime.</t>
-  </si>
-  <si>
-    <t>Directly addresses balancing exclusive breeder rights with protections for farmers.</t>
-  </si>
-  <si>
-    <t>Directly discusses farmer exceptions limiting breeder exclusivity within PVP laws.</t>
-  </si>
-  <si>
-    <t>Clear discussion of legal scope of breeders’ rights and farmers’ seed rights.</t>
-  </si>
-  <si>
-    <t>Directly concerns legal balance and broader exceptions for farmers under sui generis PVP.</t>
-  </si>
-  <si>
-    <t>Direct analysis of the balance between breeders’ rights and Farmers’ Rights under PVP regimes.</t>
-  </si>
-  <si>
-    <t>Explicitly addresses balancing breeders’ and farmers’ interests in plant variety law.</t>
-  </si>
-  <si>
-    <t>Relevant as a framework for a PVP system that incorporates farmers’ varieties alongside breeders’ rights.</t>
-  </si>
-  <si>
-    <t>Direct statement on exemptions for farmers and balancing breeders’ and farmers’ rights.</t>
-  </si>
-  <si>
-    <t>Enumerates the intended objectives of a sui generis plant variety protection regime.</t>
-  </si>
-  <si>
-    <t>Directly concerns innovation incentives and diffusion of new varieties.</t>
-  </si>
-  <si>
-    <t>Direct reference to objectives that a PVP regime should pursue.</t>
-  </si>
-  <si>
-    <t>This passage directly links PVR to innovation incentives and breeding activity.</t>
-  </si>
-  <si>
-    <t>This describes CPVR/PVR as balancing competing interests and policy considerations.</t>
-  </si>
-  <si>
-    <t>The excerpt explicitly addresses innovation outcomes and responsiveness to market needs.</t>
-  </si>
-  <si>
-    <t>This passage directly concerns balancing breeders' rights with farmers' rights and benefit-sharing.</t>
-  </si>
-  <si>
-    <t>This identifies policy aims and intended achievements of the PVP Act relevant to legislative objectives.</t>
-  </si>
-  <si>
-    <t>This passage links plant variety protection to trade facilitation and agricultural innovation.</t>
-  </si>
-  <si>
-    <t>This states a core legislative/policy objective of the plant variety protection framework: protecting breeders and encouraging new varieties.</t>
-  </si>
-  <si>
-    <t>This directly addresses market access, foreign breeder participation, and innovation opportunities.</t>
-  </si>
-  <si>
-    <t>This passage speaks directly to breeding incentives, investment, and innovation in agriculture.</t>
-  </si>
-  <si>
-    <t>This explicitly lists the objectives of the 2021 Act.</t>
-  </si>
-  <si>
-    <t>This directly concerns CPVR's effect on breeding investment, productivity, and innovation.</t>
-  </si>
-  <si>
-    <t>This passage addresses the balance between breeders' interests and seed-saving exceptions affecting farmers.</t>
-  </si>
-  <si>
-    <t>This states a policy objective of the protection system: rewarding breeders' efforts and investments.</t>
-  </si>
-  <si>
-    <t>This identifies formal institutional objectives tied to the plant variety regulatory framework.</t>
-  </si>
-  <si>
-    <t>This passage sets out policy and operational objectives relevant to oversight and intended outcomes.</t>
-  </si>
-  <si>
-    <t>This outlines oversight and implementation objectives connected to the plant breeders' rights framework.</t>
-  </si>
-  <si>
-    <t>This directly concerns oversight and enforcement functions of the CPVR-related system.</t>
-  </si>
-  <si>
-    <t>This states the Act's core objective of encouraging development of new plant varieties.</t>
-  </si>
-  <si>
-    <t>This describes institutional objectives and functions, including administration and licensing oversight.</t>
-  </si>
-  <si>
-    <t>This passage clearly sets out exceptions limiting breeders' exclusive rights, showing rights balancing.</t>
-  </si>
-  <si>
-    <t>This concerns the scope and exercise of breeders' rights within the legal regime.</t>
-  </si>
-  <si>
-    <t>This directly links the PVP Act to incentives for new varieties and breeding activity.</t>
-  </si>
-  <si>
-    <t>This is directly about investment incentives and development of new varieties.</t>
-  </si>
-  <si>
-    <t>This addresses market access and competitiveness through foreign breeder participation.</t>
-  </si>
-  <si>
-    <t>This directly concerns R&amp;D, productivity, and economic impacts tied to innovation.</t>
-  </si>
-  <si>
-    <t>This passage addresses commercialization, investment opportunities, and economic effects of the regime.</t>
-  </si>
-  <si>
-    <t>This concerns administration and oversight capacity for implementing PVP objectives.</t>
-  </si>
-  <si>
-    <t>This directly references assessing PVR impacts on innovation.</t>
-  </si>
-  <si>
-    <t>This passage directly discusses the CPVR system’s effectiveness in protecting rights and driving innovation, and references prior evaluations confirming performance.</t>
-  </si>
-  <si>
-    <t>The excerpt links CPVR to breeders’ incentives, business model, and continued innovation in developing resilient varieties.</t>
-  </si>
-  <si>
-    <t>This passage explicitly concerns the farm-saved seed exception and its limiting effect on breeders’ rights, which is central to balancing farmers’ and breeders’ rights.</t>
-  </si>
-  <si>
-    <t>The text addresses reduced breeding programmes and the resulting lower availability of new varieties, which speaks directly to innovation outcomes and market availability.</t>
-  </si>
-  <si>
-    <t>This directly questions the effectiveness and added value of CPVR in achieving its protective objective for perennial varieties.</t>
-  </si>
-  <si>
-    <t>The passage ties CPVR-related EDV harmonisation to technological developments and ensuring benefits from innovation reach farmers and growers.</t>
-  </si>
-  <si>
-    <t>This concerns harmonisation of the CPVR framework across Member States, a policy objective relevant to the system’s functioning.</t>
-  </si>
-  <si>
-    <t>This passage directly connects CPVR to innovation, competition, market structure, and variety availability.</t>
-  </si>
-  <si>
-    <t>This reflects how CPVR is framed as balancing protection with continued breeding access and fair competition that benefits growers.</t>
-  </si>
-  <si>
-    <t>This is a strong statement on CPVR’s effect on breeding activity, innovation diffusion, and availability of improved varieties.</t>
-  </si>
-  <si>
-    <t>This passage directly addresses the balance within CPVR between exclusive rights and the breeder’s exemption allowing further use by competing breeders.</t>
-  </si>
-  <si>
-    <t>This discusses the need to balance breeders’ remuneration, access to innovation, and avoiding excessive dependence of farmers and growers, all within the CPVR context.</t>
-  </si>
-  <si>
-    <t>This passage states the protective objective of the CPVR system and its broader policy contribution to a diverse and resilient agricultural sector.</t>
-  </si>
-  <si>
-    <t>This evaluates the system’s past service and calls for modernisation to maintain effectiveness, directly relevant to achievement of objectives and future fitness.</t>
-  </si>
-  <si>
-    <t>Directly references UPOV 1991 and discusses alignment of the Basic Regulation with that international framework.</t>
-  </si>
-  <si>
-    <t>Identifies enforcement availability as an operational barrier in CPVR implementation.</t>
-  </si>
-  <si>
-    <t>Explicitly compares the Basic Regulation with UPOV 1991, showing interaction with an international IP standard.</t>
-  </si>
-  <si>
-    <t>Addresses enforcement shortcomings and need for clarification in implementation and remedies.</t>
-  </si>
-  <si>
-    <t>Directly concerns the relationship between CPVR and the EU IP enforcement framework.</t>
-  </si>
-  <si>
-    <t>References the UPOV Convention and indicates CPVR should be updated in light of that international guidance.</t>
+    <t>This passage states the policy objective of the Basic Regulation in fostering innovation through balanced IP protection.</t>
+  </si>
+  <si>
+    <t>The snippet directly links CPVR protection to innovation in plant breeding and investment in plant innovations.</t>
+  </si>
+  <si>
+    <t>The phrase 'strong and balanced IP protection for all stakeholders' is directly relevant to balancing interests within the CPVR framework.</t>
+  </si>
+  <si>
+    <t>This passage discusses CPVR interpretation affecting the plant breeding industry, which relates to competitiveness and innovation conditions.</t>
+  </si>
+  <si>
+    <t>This passage concerns the scope of breeders' rights and limitations in enforcement under CPVR, relevant to the balance of rights.</t>
+  </si>
+  <si>
+    <t>The reference to a 'chilling effect on the release of new plant varieties' directly concerns innovation outcomes and market introduction.</t>
+  </si>
+  <si>
+    <t>This concerns the legal protection and enforcement rights of breeders under CPVR, clearly relevant to rights balance.</t>
+  </si>
+  <si>
+    <t>This passage links effective provisional protection to reliable incentives for prospective rights holders, which bears on innovation conditions.</t>
+  </si>
+  <si>
+    <t>The quote directly addresses the scope and clarity of breeders' entitlement to compensation under CPVR.</t>
+  </si>
+  <si>
+    <t>Directly addresses balancing breeders’ rights with Farmers’ Rights and benefit-sharing in PVP laws.</t>
+  </si>
+  <si>
+    <t>Explicitly discusses balancing Farmers’ Rights and breeders’ rights in PVP regimes.</t>
+  </si>
+  <si>
+    <t>Directly concerns PVP/IP effects on innovation, R&amp;D, and seed sector development.</t>
+  </si>
+  <si>
+    <t>Direct evidence on plant breeding activity, R&amp;D, and seed industry outcomes tied to PVP.</t>
+  </si>
+  <si>
+    <t>Evaluates whether PVP/UPOV achieved its intended goals of stimulating breeding and sector development.</t>
+  </si>
+  <si>
+    <t>Concise and explicit statement on balancing breeders’ and farmers’ rights in PVP systems.</t>
+  </si>
+  <si>
+    <t>Explicitly frames PVP as balancing breeder incentives against Farmers’ Rights and related public interests.</t>
+  </si>
+  <si>
+    <t>Directly addresses balancing breeders’ rights with Farmers’ Rights in sui generis PVP laws.</t>
+  </si>
+  <si>
+    <t>Direct reference to farmer exceptions within PVP laws to balance exclusive breeders’ rights.</t>
+  </si>
+  <si>
+    <t>Strong evidence on balancing rights through explicit farmer exemptions in PVP regimes.</t>
+  </si>
+  <si>
+    <t>Direct mention of clarifying objectives of national PVP law and assessing whether laws meet them.</t>
+  </si>
+  <si>
+    <t>Addresses impact of IPR/PVP on agricultural performance and innovation-related outcomes.</t>
+  </si>
+  <si>
+    <t>Directly discusses innovation effects and market consequences of IP protection for plant varieties.</t>
+  </si>
+  <si>
+    <t>Evidence on differential economic and innovation-related outcomes of plant variety IP regimes.</t>
+  </si>
+  <si>
+    <t>Directly concerns market structure, competitiveness, and concentration effects of plant variety rights.</t>
+  </si>
+  <si>
+    <t>Clear statement about lack of innovation and seed industry development under UPOV-based PVP.</t>
+  </si>
+  <si>
+    <t>Assesses effectiveness and performance of the PVP system against expected policy purposes.</t>
+  </si>
+  <si>
+    <t>Addresses how PVP/IP should affect seed sector development and competitiveness in context.</t>
+  </si>
+  <si>
+    <t>Explicitly discusses balancing rights and obligations between breeders and farmers in PVP design.</t>
+  </si>
+  <si>
+    <t>Direct evidence on PVP/IP impact on seed sector growth and market development.</t>
+  </si>
+  <si>
+    <t>Relevant to breeding priorities, innovation direction, and market orientation under IPR/PVP.</t>
+  </si>
+  <si>
+    <t>References breeders’ exemptions and farmers’ abilities to save/exchange/sell seed within PVP design.</t>
+  </si>
+  <si>
+    <t>Direct mention of crafting balanced provisions on Farmers’ Rights within PVP-related legal frameworks.</t>
+  </si>
+  <si>
+    <t>Directly addresses balancing breeders’ and farmers’ rights in relation to PVP.</t>
+  </si>
+  <si>
+    <t>Relevant to innovation outcomes and investment patterns under plant variety protection.</t>
+  </si>
+  <si>
+    <t>Directly concerns how PVP affects the balance between breeders’ rights and farmers’ rights.</t>
+  </si>
+  <si>
+    <t>Direct evidence on whether UPOV/PVP affects breeding activity and seed market engagement.</t>
+  </si>
+  <si>
+    <t>Directly addresses market access/trade effects of plant variety protection.</t>
+  </si>
+  <si>
+    <t>Assesses extent to which the UPOV/PVP system meets public policy objectives.</t>
+  </si>
+  <si>
+    <t>Relates to innovation incentives and market effects of PVP.</t>
+  </si>
+  <si>
+    <t>Direct claim about achievement of PVP objectives and performance impacts.</t>
+  </si>
+  <si>
+    <t>Directly concerns varietal innovation, breeder activity, and competitiveness outcomes.</t>
+  </si>
+  <si>
+    <t>Evaluates whether evidence supports claims that UPOV achieved its goals.</t>
+  </si>
+  <si>
+    <t>Direct evidence on the effect of PVP on research and innovation outcomes.</t>
+  </si>
+  <si>
+    <t>Directly discusses balancing breeders’ rights with farmers’ rights and exceptions in PVP laws.</t>
+  </si>
+  <si>
+    <t>Direct statement on balancing breeders’, farmers’, and community rights in plant variety governance.</t>
+  </si>
+  <si>
+    <t>Shows concrete balancing of breeder protection with farmer access and rights.</t>
+  </si>
+  <si>
+    <t>Direct reference to limiting IPRs to balance interests and protect Farmers’ Rights.</t>
+  </si>
+  <si>
+    <t>Directly about balancing breeders’ and farmers’ interests in PVP law.</t>
+  </si>
+  <si>
+    <t>Relevant because it concerns incorporating Farmers’ Rights into plant variety protection systems.</t>
+  </si>
+  <si>
+    <t>Explicit assessment of failure to balance breeders’ and farmers’ rights.</t>
+  </si>
+  <si>
+    <t>Concerns the claimed market/investment effects of plant breeders’ rights.</t>
+  </si>
+  <si>
+    <t>Directly describes conflict and balance between Farmers’ Rights and PBRs.</t>
+  </si>
+  <si>
+    <t>Directly addresses imbalance between breeders’ and farmers’ rights in PVP legislation.</t>
+  </si>
+  <si>
+    <t>Directly addresses proportionality and balancing of private breeder interests with public/farmer interests.</t>
+  </si>
+  <si>
+    <t>Explicit evaluation of whether a stated policy objective of PVP legislation was achieved.</t>
+  </si>
+  <si>
+    <t>Direct statement on imbalance between breeders’ rights and Farmers’ Rights.</t>
+  </si>
+  <si>
+    <t>Direct assessment of a PVP regime balancing right holders and Farmers’ Rights.</t>
+  </si>
+  <si>
+    <t>Shows attempt to balance farmer interests with breeder/private sector incentives under plant variety law.</t>
+  </si>
+  <si>
+    <t>Explicit statement about balancing breeders’ rights and Farmers’ Rights in a PVP law.</t>
+  </si>
+  <si>
+    <t>Directly covers farmers’ rights, public interest exceptions, and compulsory licensing in CPVR/PVP context.</t>
+  </si>
+  <si>
+    <t>Directly links plant variety protection to innovation and breeding activity.</t>
+  </si>
+  <si>
+    <t>Shows explicit dual objective of breeder protection and farmer rights recognition.</t>
+  </si>
+  <si>
+    <t>Directly addresses farmer exceptions limiting breeder exclusivity in PVP law.</t>
+  </si>
+  <si>
+    <t>Direct call for farmer exceptions in national PVP laws to balance rights.</t>
+  </si>
+  <si>
+    <t>Relevant to the legal/policy rationale for protecting Farmers’ Rights in plant variety regimes.</t>
+  </si>
+  <si>
+    <t>Directly addresses farmers’ privilege and narrowing exceptions under plant variety legislation.</t>
+  </si>
+  <si>
+    <t>Direct comparison of breeders’ rights expansion and restrictions on Farmers’ Rights under UPOV.</t>
+  </si>
+  <si>
+    <t>Direct legal reference to limits on Farmers’ Rights under plant variety protection.</t>
+  </si>
+  <si>
+    <t>Directly concerns balancing breeders’ and farmers’ rights in PVP laws.</t>
+  </si>
+  <si>
+    <t>Directly addresses restrictions on farmers’ rights within PVP-related legal frameworks.</t>
+  </si>
+  <si>
+    <t>Explicit farmer exemption within a sui generis PVP regime; directly relevant to balancing rights.</t>
+  </si>
+  <si>
+    <t>Directly describes the intended balance of breeders’ rights with farmers’ and public interests.</t>
+  </si>
+  <si>
+    <t>States policy objectives that a PVP system should promote and be assessed against.</t>
+  </si>
+  <si>
+    <t>Directly refers to objectives that should guide plant variety protection regimes.</t>
+  </si>
+  <si>
+    <t>Directly links PVR to innovation incentives and breeding activity.</t>
+  </si>
+  <si>
+    <t>Addresses balancing innovation incentives with broader preservation concerns within PVR regimes.</t>
+  </si>
+  <si>
+    <t>Mentions policy goals and intended achievements of the PVP Act, including innovation and economic growth.</t>
+  </si>
+  <si>
+    <t>Connects plant breeders' IP protection to agricultural innovation and economic growth.</t>
+  </si>
+  <si>
+    <t>Directly concerns market access and innovation impacts of plant variety protection laws.</t>
+  </si>
+  <si>
+    <t>Directly states that breeder protection encourages development of new plant varieties.</t>
+  </si>
+  <si>
+    <t>Describes effects on access to foreign varieties, foreign breeders, and innovation opportunities.</t>
+  </si>
+  <si>
+    <t>Clearly addresses incentives for breeding activity and development of new varieties.</t>
+  </si>
+  <si>
+    <t>Direct statement of the Act’s legislative and policy objectives.</t>
+  </si>
+  <si>
+    <t>Directly addresses commercialization, investment, productivity, and innovation outcomes.</t>
+  </si>
+  <si>
+    <t>Explicitly concerns balancing breeders’ interests and farmers’ ability to save seed.</t>
+  </si>
+  <si>
+    <t>States the protection system’s core policy objective of rewarding breeders’ efforts and investments.</t>
+  </si>
+  <si>
+    <t>Describes the scope of breeders’ exclusive rights under plant variety protection.</t>
+  </si>
+  <si>
+    <t>Directly states the Act’s objective to encourage development of new plant varieties.</t>
+  </si>
+  <si>
+    <t>Describes implementing framework and institutional functions under the Act.</t>
+  </si>
+  <si>
+    <t>Sets out breeders’ exclusive rights under CPVR-like protection.</t>
+  </si>
+  <si>
+    <t>Directly addresses exceptions and limitations balancing breeders’ rights with third-party uses.</t>
+  </si>
+  <si>
+    <t>Direct evidence on incentives for varietal innovation and breeding activity.</t>
+  </si>
+  <si>
+    <t>Directly links PVP to investment and development of new varieties.</t>
+  </si>
+  <si>
+    <t>Addresses market access and participation by foreign breeders.</t>
+  </si>
+  <si>
+    <t>Directly concerns innovation, R&amp;D, productivity, and economic competitiveness outcomes.</t>
+  </si>
+  <si>
+    <t>Describes commercialization and investment opportunities arising from plant variety rights.</t>
+  </si>
+  <si>
+    <t>Relates to implementation capacity, oversight of applications, and enforcement under the PVP framework.</t>
+  </si>
+  <si>
+    <t>Explicitly refers to assessing PVR impact on innovation.</t>
+  </si>
+  <si>
+    <t>This passage directly discusses the effectiveness of the CPVR/CBP system in achieving its purpose and refers to prior evaluations confirming this performance.</t>
+  </si>
+  <si>
+    <t>This directly links CPVR legislation to incentives for breeding innovation and development of improved varieties.</t>
+  </si>
+  <si>
+    <t>This passage explicitly addresses the farm-saved seed exception and its limiting effect on breeders’ rights, which is central to the balance between breeders’ and farmers’ rights.</t>
+  </si>
+  <si>
+    <t>This passage concerns declining breeding programmes and reduced availability of new varieties, directly relevant to innovation outcomes and market access.</t>
+  </si>
+  <si>
+    <t>This directly questions the effectiveness and value of CPVR protection for perennial varieties, which relates to achievement of legislative objectives.</t>
+  </si>
+  <si>
+    <t>This concerns the role of the CPVR framework in harmonisation and effective functioning across Member States, relevant to policy objectives.</t>
+  </si>
+  <si>
+    <t>This passage explicitly connects CPVR-related EDV rules to the uptake and benefit of breeding innovations.</t>
+  </si>
+  <si>
+    <t>This addresses implementation and institutional functioning of the CPVR system, especially harmonisation and effective adjudication.</t>
+  </si>
+  <si>
+    <t>This directly discusses breeding innovation, competition, market structure, and access to diverse varieties under the CPVR framework.</t>
+  </si>
+  <si>
+    <t>This passage addresses balancing breeder protection with avoidance of burdens on farmers and maintaining fair competition and access.</t>
+  </si>
+  <si>
+    <t>This explicitly links the CPVR system to follow-on breeding, innovation diffusion, and increased availability of improved varieties.</t>
+  </si>
+  <si>
+    <t>This passage describes an intrinsic exception within breeders’ rights allowing use by competing breeders, which is central to balancing exclusive rights with access for further breeding.</t>
+  </si>
+  <si>
+    <t>This passage directly addresses proportionality and balancing interests: breeders need remuneration, but innovations should not be locked up in ways that burden farmers and downstream breeding.</t>
+  </si>
+  <si>
+    <t>This states the intended outcomes and effectiveness of a strong CPVR/CBP system in protecting rights and supporting broader policy goals.</t>
+  </si>
+  <si>
+    <t>This passage evaluates the system’s past service and discusses the need to modernise it to continue meeting its objectives.</t>
+  </si>
+  <si>
+    <t>Directly references alignment of the Basic Regulation with UPOV 1991, which fits the international IP standards framework.</t>
+  </si>
+  <si>
+    <t>Identifies enforcement as an operational issue affecting effective implementation of CPVR protection.</t>
+  </si>
+  <si>
+    <t>Compares the EU CPVR rule with UPOV 1991 wording, directly addressing alignment with an international IP framework.</t>
+  </si>
+  <si>
+    <t>Discusses how CPVR interacts with the EU IP enforcement framework.</t>
+  </si>
+  <si>
+    <t>Shows a barrier in implementation and enforcement caused by unclear relationship with the EU enforcement directive.</t>
+  </si>
+  <si>
+    <t>Explicitly links the EU CPVR EDV definition to UPOV Convention guidance.</t>
   </si>
   <si>
     <t>Describes ambiguity and inconsistent national interpretation as barriers to effective enforcement and implementation.</t>
   </si>
   <si>
-    <t>Directly concerns harmonization of the Basic Regulation with the UPOV Convention.</t>
-  </si>
-  <si>
-    <t>Directly discusses CPVR/PVP in relation to TRIPS and broader international IP standards.</t>
-  </si>
-  <si>
-    <t>Explicitly links plant variety protection with TRIPS, UPOV 1991, and compliance beyond minimum international standards.</t>
-  </si>
-  <si>
-    <t>Shows how the PVP/UPOV framework interacts with other international legal frameworks.</t>
-  </si>
-  <si>
-    <t>Directly addresses alignment between PVP laws, TRIPS, UPOV 1991, and other treaty obligations.</t>
-  </si>
-  <si>
-    <t>Identifies knowledge and participatory deficits as barriers affecting implementation of PVP-related laws.</t>
-  </si>
-  <si>
-    <t>Explicitly addresses PVP within TRIPS and UPOV-based international IP alignment.</t>
-  </si>
-  <si>
-    <t>Clearly relates PVP/IP developments to TRIPS and TRIPS-plus international frameworks.</t>
-  </si>
-  <si>
-    <t>Describes operational underperformance and practical barriers in implementation and uptake of the PVP system.</t>
-  </si>
-  <si>
-    <t>Indicates implementation failure and weak operational performance of the PVP regime.</t>
-  </si>
-  <si>
-    <t>Directly concerns the relationship between plant variety protection and TRIPS-based international IP obligations.</t>
-  </si>
-  <si>
-    <t>References national capacities as a constraint affecting effective implementation of IPR/PVP regimes.</t>
-  </si>
-  <si>
-    <t>Directly addresses interaction of UPOV-based PVP with other international and EU legal frameworks.</t>
-  </si>
-  <si>
-    <t>Explicitly links PVP design choices to TRIPS and UPOV framework interactions.</t>
-  </si>
-  <si>
-    <t>Directly concerns how UPOV-based CPVR/PVP interacts with TRIPS and the wider international IP framework.</t>
-  </si>
-  <si>
-    <t>Identifies governance and institutional transparency issues as barriers to effective operation and implementation.</t>
-  </si>
-  <si>
-    <t>Highlights assessment and evidentiary shortcomings that hinder proper evaluation and implementation learning.</t>
-  </si>
-  <si>
-    <t>Addresses PVP/PBRs within multilateral and regional IP frameworks.</t>
-  </si>
-  <si>
-    <t>Directly situates PVP within international treaty obligations including TRIPS.</t>
-  </si>
-  <si>
-    <t>This is a clear participation and knowledge barrier affecting implementation of seed/PVP laws.</t>
-  </si>
-  <si>
-    <t>Shows stakeholder exclusion as a barrier in development and implementation of PVP rules.</t>
-  </si>
-  <si>
-    <t>Directly indicates underperformance in achieving intended implementation outcomes.</t>
-  </si>
-  <si>
-    <t>Explicitly links PVP design to TRIPS and related international frameworks.</t>
-  </si>
-  <si>
-    <t>Directly discusses interaction and tension between UPOV, TRIPS, and other international regimes in PVP lawmaking.</t>
-  </si>
-  <si>
-    <t>Directly concerns TRIPS requirements and their interpretation for plant variety protection.</t>
-  </si>
-  <si>
-    <t>Shows a practical implementation barrier arising from eligibility requirements preventing access to protection.</t>
-  </si>
-  <si>
-    <t>Directly names hindrances to implementation in the legal and regulatory environment.</t>
-  </si>
-  <si>
-    <t>Relates PVP options to UPOV framework choices and international policy space.</t>
-  </si>
-  <si>
-    <t>Clearly addresses how different UPOV standards shape the PVP framework and its legal effects.</t>
-  </si>
-  <si>
-    <t>Identifies technical assistance shortcomings as a barrier to suitable implementation of PVP laws.</t>
-  </si>
-  <si>
-    <t>Directly refers to operational and participatory barriers in implementation.</t>
-  </si>
-  <si>
-    <t>Directly links PVP design to TRIPS and multiple international legal frameworks.</t>
-  </si>
-  <si>
-    <t>Explicitly addresses the relationship between UPOV 1991, TRIPS, and trade agreements.</t>
-  </si>
-  <si>
-    <t>Directly concerns international IP standards and the PVP framework under UPOV and TRIPS.</t>
-  </si>
-  <si>
-    <t>This passage identifies a barrier to effective CPVR/PVR implementation in Nigeria, namely lack of accession to UPOV and resulting inability to protect rights and attract breeders.</t>
-  </si>
-  <si>
-    <t>This directly discusses the international UPOV framework governing plant variety protection.</t>
-  </si>
-  <si>
-    <t>This passage clearly links plant variety protection to the TRIPS international IP regime and its standards.</t>
-  </si>
-  <si>
-    <t>This explicitly states alignment of Nigeria's PVP Act with UPOV international standards.</t>
-  </si>
-  <si>
-    <t>This compares plant variety rights with traditional IP and explicitly references the European Union framework.</t>
-  </si>
-  <si>
-    <t>This passage explains how UPOV interacts with other IP systems, especially patents.</t>
-  </si>
-  <si>
-    <t>This identifies administrative capacity and enforcement shortcomings as barriers to implementation.</t>
-  </si>
-  <si>
-    <t>This indicates lack of awareness/knowledge among stakeholders as an implementation barrier.</t>
-  </si>
-  <si>
-    <t>This points to enforcement and compliance challenges in practice, implying need for stronger monitoring and legal action.</t>
+    <t>Directly addresses harmonization of the Basic Regulation with the UPOV Convention.</t>
+  </si>
+  <si>
+    <t>This passage directly discusses challenges arising in implementing PVR regulations.</t>
+  </si>
+  <si>
+    <t>This directly references UPOV as part of the international framework for plant variety protection.</t>
+  </si>
+  <si>
+    <t>This passage identifies a concrete barrier to implementation and effective protection: Nigeria's non-signatory status and resulting inability to protect rights adequately.</t>
+  </si>
+  <si>
+    <t>This directly links CPVR/PVP to TRIPS and explains the international IP standards applicable to plant variety protection.</t>
+  </si>
+  <si>
+    <t>This explicitly states alignment of Nigeria's Act with UPOV international standards.</t>
+  </si>
+  <si>
+    <t>This passage explicitly discusses the European Union approach and interaction between plant breeders' rights and traditional IP systems.</t>
+  </si>
+  <si>
+    <t>This passage directly addresses how UPOV interacts with other IP titles, especially patents.</t>
+  </si>
+  <si>
+    <t>This describes UPOV's role in the international IP framework for plant variety protection.</t>
+  </si>
+  <si>
+    <t>This clearly explains how TRIPS situates plant variety protection within the broader international IP framework.</t>
+  </si>
+  <si>
+    <t>This passage concerns compliance and monitoring requirements, which relate to implementation challenges and operational performance.</t>
+  </si>
+  <si>
+    <t>This directly concerns enforcement responsibilities and implementation of PVP rights.</t>
+  </si>
+  <si>
+    <t>This passage addresses enforcement mechanisms, relevant to implementation and compliance performance.</t>
+  </si>
+  <si>
+    <t>This recommendation indicates an implementation gap or barrier requiring clearer guidelines.</t>
+  </si>
+  <si>
+    <t>This directly identifies capacity and resource barriers affecting implementation and enforcement.</t>
+  </si>
+  <si>
+    <t>This identifies lack of awareness/knowledge as a barrier to implementation.</t>
+  </si>
+  <si>
+    <t>This passage directly concerns monitoring and enforcement weaknesses in operational implementation.</t>
   </si>
   <si>
     <t>This passage directly identifies enforcement difficulty, limited information, and limited compliance as barriers to implementation.</t>
   </si>
   <si>
-    <t>This indicates capacity and knowledge gaps in legal implementation and enforcement, suggesting institutional barriers.</t>
-  </si>
-  <si>
-    <t>This directly situates CPVR within the EU intellectual property framework through reference to CBP and EUIPO.</t>
-  </si>
-  <si>
-    <t>This explicitly concerns harmonisation of plant variety rights across EU member states, aligning with EU IP framework interaction.</t>
-  </si>
-  <si>
-    <t>This passage discusses the interaction between CPVR and another IP system, patents, within the broader IP framework.</t>
+    <t>This indicates lack of legal experience and knowledge as an implementation barrier and suggests institutional capacity-building.</t>
+  </si>
+  <si>
+    <t>This explicitly concerns harmonisation of plant variety rights across EU member states, fitting EU IP framework alignment.</t>
+  </si>
+  <si>
+    <t>This passage discusses interaction between CPVR and another IP system, namely patents, as part of the broader IP framework.</t>
   </si>
   <si>
     <t>high</t>
@@ -1597,10 +1478,10 @@
     <t>medium</t>
   </si>
   <si>
-    <t>2026-06-23T12:56:04</t>
-  </si>
-  <si>
-    <t>2026-06-23T12:56:56</t>
+    <t>2026-07-02T11:27:19</t>
+  </si>
+  <si>
+    <t>2026-07-02T11:28:16</t>
   </si>
   <si>
     <t>4885febfda356ba8</t>
@@ -1612,22 +1493,22 @@
     <t>db560946c5a52cd1</t>
   </si>
   <si>
-    <t>2ee6bef93b3b77c9</t>
-  </si>
-  <si>
-    <t>bd6601c5070fc80c</t>
+    <t>98bededa55afd02f</t>
+  </si>
+  <si>
+    <t>f0dd8fa3e5752042</t>
+  </si>
+  <si>
+    <t>72026d02c929d901</t>
   </si>
   <si>
     <t>e1e2caa33ec59a34</t>
   </si>
   <si>
-    <t>0fbeb3714e4d99db</t>
-  </si>
-  <si>
-    <t>33a71b544ae6c7de</t>
-  </si>
-  <si>
-    <t>4f163a135bc17337</t>
+    <t>8f7de4efa5402144</t>
+  </si>
+  <si>
+    <t>d975bc2534fd8579</t>
   </si>
   <si>
     <t>0c20ac50506c75a2</t>
@@ -1636,49 +1517,76 @@
     <t>b8e99b557b0df60d</t>
   </si>
   <si>
-    <t>dc836c70dde3b3ec</t>
-  </si>
-  <si>
-    <t>a3e2b39836f890e7</t>
+    <t>844ba2592f33535d</t>
+  </si>
+  <si>
+    <t>b3207cab8d086a60</t>
+  </si>
+  <si>
+    <t>3172f5c8665644aa</t>
   </si>
   <si>
     <t>ace21b1014840d7a</t>
   </si>
   <si>
-    <t>72d553eacbf09656</t>
-  </si>
-  <si>
-    <t>7ec8a57650b33d41</t>
-  </si>
-  <si>
-    <t>fe66cc237a60b6bb</t>
-  </si>
-  <si>
-    <t>d1fd21e3def5d43c</t>
-  </si>
-  <si>
-    <t>efd29b8bcdf0e113</t>
+    <t>01ce524455567fa1</t>
+  </si>
+  <si>
+    <t>725718f8cce70bde</t>
+  </si>
+  <si>
+    <t>86f9fd792fdea9b5</t>
+  </si>
+  <si>
+    <t>e06b0430058f30af</t>
+  </si>
+  <si>
+    <t>99f5cee5ab69890a</t>
+  </si>
+  <si>
+    <t>9f057107360b071f</t>
+  </si>
+  <si>
+    <t>2f2a2d4fdddf2ce5</t>
+  </si>
+  <si>
+    <t>40ea384e41ef3fc2</t>
+  </si>
+  <si>
+    <t>a935f86a0c5126ae</t>
   </si>
   <si>
     <t>710295c6f40bb5c8</t>
   </si>
   <si>
-    <t>1b9802e67cddc7a4</t>
-  </si>
-  <si>
-    <t>8ece802227cddda7</t>
-  </si>
-  <si>
-    <t>d85ed0a857aae219</t>
-  </si>
-  <si>
-    <t>ff07727ab527cd24</t>
-  </si>
-  <si>
-    <t>0cd46382c29f2a48</t>
-  </si>
-  <si>
-    <t>8dd2dd642e1d315c</t>
+    <t>2b36e8dab8a5648f</t>
+  </si>
+  <si>
+    <t>86f270ae5e95ff8a</t>
+  </si>
+  <si>
+    <t>7680d149c8b94b74</t>
+  </si>
+  <si>
+    <t>d04cffe2b85cd0d7</t>
+  </si>
+  <si>
+    <t>071493a68f1e8d5d</t>
+  </si>
+  <si>
+    <t>dc3e134674e896a1</t>
+  </si>
+  <si>
+    <t>160e82849a1a8166</t>
+  </si>
+  <si>
+    <t>18751b38e143ef91</t>
+  </si>
+  <si>
+    <t>c28a30a8513a0b24</t>
+  </si>
+  <si>
+    <t>cb968229c1c8878c</t>
   </si>
   <si>
     <t>4bd05c7e87d658c2</t>
@@ -1687,88 +1595,115 @@
     <t>59ae96c4df0e7401</t>
   </si>
   <si>
-    <t>d3751d4ac050866f</t>
-  </si>
-  <si>
-    <t>d3d75d40c7c521e3</t>
-  </si>
-  <si>
-    <t>6e1be905ab366c8f</t>
-  </si>
-  <si>
-    <t>46265e6689fc8cb8</t>
-  </si>
-  <si>
-    <t>3ab73892d60edaee</t>
+    <t>546ba805691b521a</t>
+  </si>
+  <si>
+    <t>3ae3a9bd9d4e61a8</t>
+  </si>
+  <si>
+    <t>74cfbf038999e159</t>
+  </si>
+  <si>
+    <t>55319c1188af6a39</t>
+  </si>
+  <si>
+    <t>b4886fd65e51073a</t>
+  </si>
+  <si>
+    <t>fc829fb72afb8307</t>
+  </si>
+  <si>
+    <t>c6ca26935ceec33f</t>
+  </si>
+  <si>
+    <t>9718cfd8f425438e</t>
+  </si>
+  <si>
+    <t>a9c85f8d635fcf7b</t>
+  </si>
+  <si>
+    <t>364450c6438db814</t>
   </si>
   <si>
     <t>ff4439e8e74edd46</t>
   </si>
   <si>
-    <t>9a1631f79be77783</t>
-  </si>
-  <si>
-    <t>73463ed99b1eb362</t>
-  </si>
-  <si>
-    <t>b693b5b1d161ccb2</t>
-  </si>
-  <si>
-    <t>b89de33b1bd36762</t>
-  </si>
-  <si>
-    <t>7b07da17f2dcd3eb</t>
-  </si>
-  <si>
-    <t>12745a641a812973</t>
-  </si>
-  <si>
-    <t>1219ed264d8b5eb8</t>
-  </si>
-  <si>
-    <t>a83ebdf948c5a6ff</t>
-  </si>
-  <si>
-    <t>25e9a79eb8f769ff</t>
-  </si>
-  <si>
-    <t>7e679d407991150b</t>
-  </si>
-  <si>
-    <t>50f8702d33675053</t>
-  </si>
-  <si>
-    <t>1055e7c4c2d49418</t>
-  </si>
-  <si>
-    <t>59dfd30ed9cb1616</t>
-  </si>
-  <si>
-    <t>e327d00306000a5b</t>
-  </si>
-  <si>
-    <t>c62b0f89ad0a471d</t>
-  </si>
-  <si>
-    <t>40a89b7c91e60af9</t>
+    <t>c22ff725209dcbb0</t>
+  </si>
+  <si>
+    <t>b14d62ede1e1db36</t>
+  </si>
+  <si>
+    <t>9fa7c6eec63e9f94</t>
+  </si>
+  <si>
+    <t>5ffc25da278f2b03</t>
+  </si>
+  <si>
+    <t>846a8805a563f57d</t>
+  </si>
+  <si>
+    <t>170ea9d8daf3b01d</t>
+  </si>
+  <si>
+    <t>05ee80f77df4e240</t>
+  </si>
+  <si>
+    <t>88969835f75cbb71</t>
+  </si>
+  <si>
+    <t>35b4ff21d0660d6b</t>
+  </si>
+  <si>
+    <t>1f1b90085c7d0029</t>
+  </si>
+  <si>
+    <t>5443b8974ce1bd12</t>
+  </si>
+  <si>
+    <t>4bec4828159d55eb</t>
+  </si>
+  <si>
+    <t>d2eca2ae96a37ee2</t>
+  </si>
+  <si>
+    <t>78fac43720d60aaf</t>
+  </si>
+  <si>
+    <t>520f6782c8c92078</t>
+  </si>
+  <si>
+    <t>fc8a050d2da50c8c</t>
+  </si>
+  <si>
+    <t>209f2929690faae5</t>
+  </si>
+  <si>
+    <t>e52a1cb34dcc65a3</t>
+  </si>
+  <si>
+    <t>ee0c205150adb22c</t>
+  </si>
+  <si>
+    <t>576d1d3d907f197f</t>
   </si>
   <si>
     <t>f036538bd0dea5d6</t>
   </si>
   <si>
-    <t>7afefb9d42f4a9d1</t>
-  </si>
-  <si>
-    <t>8049a7bff17c57dc</t>
-  </si>
-  <si>
-    <t>4388d46be5f4b8fd</t>
-  </si>
-  <si>
-    <t>e3c4c959cf6031f8</t>
-  </si>
-  <si>
-    <t>34c8e4fd00e08313</t>
+    <t>97e14cc9107a5420</t>
+  </si>
+  <si>
+    <t>7709c9cd7f790966</t>
+  </si>
+  <si>
+    <t>10dd845a03a20407</t>
+  </si>
+  <si>
+    <t>032e06b7239f695c</t>
+  </si>
+  <si>
+    <t>ae6cdb0af8fd56c8</t>
   </si>
   <si>
     <t>5b5819ac52d0b023</t>
@@ -1777,19 +1712,16 @@
     <t>e3a5c4646a9fc31e</t>
   </si>
   <si>
-    <t>6025b4ce84fc4487</t>
-  </si>
-  <si>
-    <t>1d539724f40a9953</t>
-  </si>
-  <si>
     <t>123dcf8ac7e98135</t>
   </si>
   <si>
+    <t>38925af6a96863e2</t>
+  </si>
+  <si>
     <t>0de7741e2a239bc3</t>
   </si>
   <si>
-    <t>96b33a8f6964cdff</t>
+    <t>0147ce461594fa81</t>
   </si>
   <si>
     <t>3a944d3f2619206e</t>
@@ -1801,7 +1733,7 @@
     <t>591bdb5619d39779</t>
   </si>
   <si>
-    <t>269c2b54a24d056e</t>
+    <t>1328309a28cf8b59</t>
   </si>
   <si>
     <t>191cfade26dd2660</t>
@@ -1810,16 +1742,7 @@
     <t>264a73640bb1982f</t>
   </si>
   <si>
-    <t>da63aa3a7e13c048</t>
-  </si>
-  <si>
-    <t>02621b8c7e831045</t>
-  </si>
-  <si>
-    <t>bcd8d28ffb035e31</t>
-  </si>
-  <si>
-    <t>57f3cf4c8fe36cfa</t>
+    <t>a990f81ffcf59bce</t>
   </si>
   <si>
     <t>2d3935181a7a7a69</t>
@@ -1828,10 +1751,10 @@
     <t>ee34dc0d05c65322</t>
   </si>
   <si>
-    <t>505248a5bbfc0c3f</t>
-  </si>
-  <si>
-    <t>3cb7262761c2e819</t>
+    <t>a08f92b776c60f1e</t>
+  </si>
+  <si>
+    <t>d0d1c03232d4fa0c</t>
   </si>
   <si>
     <t>82e16611267d7b4d</t>
@@ -1846,7 +1769,7 @@
     <t>2413ebb6556e7a5e</t>
   </si>
   <si>
-    <t>9c2deae9df8b3943</t>
+    <t>bc00dbd4e73d9b58</t>
   </si>
   <si>
     <t>40a7e61fd2681f5b</t>
@@ -1858,7 +1781,7 @@
     <t>2bbd24aff5c71111</t>
   </si>
   <si>
-    <t>799de20a4e0989ee</t>
+    <t>b4879ca6b9d5083b</t>
   </si>
   <si>
     <t>c7a2297bac7f559e</t>
@@ -1867,19 +1790,22 @@
     <t>78cb1f4d8b416c03</t>
   </si>
   <si>
-    <t>8e22298c3870f290</t>
+    <t>44ad2f268f8d8af9</t>
+  </si>
+  <si>
+    <t>e45d39b715987073</t>
   </si>
   <si>
     <t>795509f569ebfaff</t>
   </si>
   <si>
-    <t>9bb6989b0ffeb8ba</t>
+    <t>d486bc2ea7f336d5</t>
   </si>
   <si>
     <t>e9956f323d8accdf</t>
   </si>
   <si>
-    <t>6f75e0e6250a55fb</t>
+    <t>47ae0b2eea9ea3c7</t>
   </si>
   <si>
     <t>dd307a1bb0f6090a</t>
@@ -1906,10 +1832,10 @@
     <t>236a9557f4480740</t>
   </si>
   <si>
-    <t>af9709176b3996a4</t>
-  </si>
-  <si>
-    <t>aafdd255c9937d8a</t>
+    <t>e5907597a32b23e5</t>
+  </si>
+  <si>
+    <t>a219cb68e868f0d5</t>
   </si>
   <si>
     <t>4890c931db6b8386</t>
@@ -1921,121 +1847,43 @@
     <t>26bd3ff19bf9afcd</t>
   </si>
   <si>
-    <t>0729ef8ce1290116</t>
-  </si>
-  <si>
-    <t>5fdc7889d695d0f2</t>
-  </si>
-  <si>
-    <t>9810f808124f7408</t>
-  </si>
-  <si>
-    <t>674f1a0a533f9190</t>
-  </si>
-  <si>
-    <t>21bf8b1bf2f2adb6</t>
-  </si>
-  <si>
-    <t>654846c94f785e67</t>
-  </si>
-  <si>
-    <t>1da37a1d8d486ab1</t>
-  </si>
-  <si>
-    <t>a780c33a307a118d</t>
-  </si>
-  <si>
-    <t>ead5648f464dafa3</t>
-  </si>
-  <si>
-    <t>796292d827323651</t>
-  </si>
-  <si>
-    <t>4903e28dd60d5ecd</t>
-  </si>
-  <si>
-    <t>300ca3ee4c67a705</t>
-  </si>
-  <si>
-    <t>ffe1644364c6db95</t>
-  </si>
-  <si>
-    <t>ab915f8a58eda3fe</t>
-  </si>
-  <si>
-    <t>9a38591854475020</t>
-  </si>
-  <si>
-    <t>c4807b601ecb8592</t>
-  </si>
-  <si>
-    <t>dd3790687ac5b7b0</t>
-  </si>
-  <si>
-    <t>b41556d8fb19470c</t>
-  </si>
-  <si>
-    <t>bd6e3da05ce2eb6e</t>
-  </si>
-  <si>
-    <t>890c81e6b5f8d61c</t>
-  </si>
-  <si>
-    <t>785071f468117dc3</t>
-  </si>
-  <si>
-    <t>93030d1f83d4eb4d</t>
-  </si>
-  <si>
-    <t>7a5e63721b5e9000</t>
-  </si>
-  <si>
-    <t>8e4892d198fb93b7</t>
-  </si>
-  <si>
-    <t>7713606991b655bc</t>
-  </si>
-  <si>
-    <t>aff59f5d4b436d4d</t>
-  </si>
-  <si>
-    <t>a8d7eac386d963fe</t>
-  </si>
-  <si>
-    <t>e39a0864cc485051</t>
-  </si>
-  <si>
-    <t>6817e792c13cb4f9</t>
-  </si>
-  <si>
-    <t>53096d14728f8754</t>
-  </si>
-  <si>
-    <t>4cbc3584e37ea710</t>
-  </si>
-  <si>
-    <t>d871d4045e347eb6</t>
-  </si>
-  <si>
-    <t>9b8dfadcdec5791f</t>
+    <t>6227106da093eac2</t>
+  </si>
+  <si>
+    <t>114070558bc54c2a</t>
   </si>
   <si>
     <t>7dda530f2181d6e8</t>
   </si>
   <si>
-    <t>114070558bc54c2a</t>
-  </si>
-  <si>
-    <t>3b5aab9193583918</t>
-  </si>
-  <si>
-    <t>9fc311c3627daf78</t>
+    <t>c610e80e31bf16e2</t>
+  </si>
+  <si>
+    <t>f2a89608af05241d</t>
   </si>
   <si>
     <t>b498bb48c3975e6e</t>
   </si>
   <si>
-    <t>7a8a2b2aab73207a</t>
+    <t>d45207dcc9ebd233</t>
+  </si>
+  <si>
+    <t>e4ad86fea430ac7b</t>
+  </si>
+  <si>
+    <t>3b18bfae1869ce04</t>
+  </si>
+  <si>
+    <t>415634839bca9a42</t>
+  </si>
+  <si>
+    <t>c1401458417fd692</t>
+  </si>
+  <si>
+    <t>03eb048a207eb554</t>
+  </si>
+  <si>
+    <t>ce24005c1116597e</t>
   </si>
   <si>
     <t>952879e5e9fdd222</t>
@@ -2051,9 +1899,6 @@
   </si>
   <si>
     <t>270721c8fc0479be</t>
-  </si>
-  <si>
-    <t>b7137d5f5e96a21b</t>
   </si>
   <si>
     <t>da6c16f3ca4cf465</t>
@@ -2417,7 +2262,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J154"/>
+  <dimension ref="A1:J142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -2457,31 +2302,31 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E2" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="H2" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I2" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J2" t="s">
-        <v>469</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2489,31 +2334,31 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E3" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="H3" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I3" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J3" t="s">
-        <v>470</v>
+        <v>441</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2521,31 +2366,31 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D4" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="H4" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="I4" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J4" t="s">
-        <v>471</v>
+        <v>442</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2553,31 +2398,31 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E5" t="s">
         <v>163</v>
-      </c>
-      <c r="C5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D5" t="s">
-        <v>170</v>
-      </c>
-      <c r="E5" t="s">
-        <v>175</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="H5" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I5" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J5" t="s">
-        <v>472</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -2585,31 +2430,31 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C6" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D6" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E6" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="H6" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I6" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J6" t="s">
-        <v>473</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2617,31 +2462,31 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C7" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D7" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E7" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="H7" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I7" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J7" t="s">
-        <v>474</v>
+        <v>445</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -2649,31 +2494,31 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C8" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D8" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E8" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="H8" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I8" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J8" t="s">
-        <v>475</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -2681,31 +2526,31 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C9" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E9" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="H9" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="I9" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J9" t="s">
-        <v>476</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -2713,31 +2558,31 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D10" t="s">
+        <v>159</v>
+      </c>
+      <c r="E10" t="s">
         <v>167</v>
       </c>
-      <c r="D10" t="s">
-        <v>170</v>
-      </c>
-      <c r="E10" t="s">
-        <v>178</v>
-      </c>
       <c r="F10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="H10" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="I10" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J10" t="s">
-        <v>477</v>
+        <v>448</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -2745,31 +2590,31 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C11" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D11" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E11" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="F11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="H11" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I11" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J11" t="s">
-        <v>478</v>
+        <v>449</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -2777,31 +2622,31 @@
         <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C12" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D12" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E12" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="F12">
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="H12" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I12" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J12" t="s">
-        <v>479</v>
+        <v>450</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -2809,31 +2654,31 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
+        <v>158</v>
+      </c>
+      <c r="E13" t="s">
         <v>170</v>
-      </c>
-      <c r="E13" t="s">
-        <v>181</v>
       </c>
       <c r="F13">
         <v>5</v>
       </c>
       <c r="G13" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="H13" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I13" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J13" t="s">
-        <v>480</v>
+        <v>451</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -2841,31 +2686,31 @@
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C14" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E14" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="F14">
         <v>5</v>
       </c>
       <c r="G14" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="H14" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I14" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J14" t="s">
-        <v>481</v>
+        <v>452</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2873,31 +2718,31 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C15" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D15" t="s">
+        <v>157</v>
+      </c>
+      <c r="E15" t="s">
         <v>171</v>
-      </c>
-      <c r="E15" t="s">
-        <v>183</v>
       </c>
       <c r="F15">
         <v>5</v>
       </c>
       <c r="G15" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="H15" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I15" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J15" t="s">
-        <v>482</v>
+        <v>453</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2905,31 +2750,31 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C16" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D16" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E16" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="H16" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I16" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J16" t="s">
-        <v>483</v>
+        <v>454</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2937,31 +2782,31 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C17" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D17" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E17" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G17" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="H17" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I17" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J17" t="s">
-        <v>484</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2969,31 +2814,31 @@
         <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C18" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D18" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E18" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="H18" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I18" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J18" t="s">
-        <v>485</v>
+        <v>456</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -3001,31 +2846,31 @@
         <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C19" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D19" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E19" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="F19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G19" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="H19" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I19" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J19" t="s">
-        <v>486</v>
+        <v>457</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -3033,31 +2878,31 @@
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C20" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D20" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E20" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="F20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G20" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="H20" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I20" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J20" t="s">
-        <v>487</v>
+        <v>458</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -3065,31 +2910,31 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D21" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E21" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="F21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G21" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="H21" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I21" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J21" t="s">
-        <v>488</v>
+        <v>459</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -3097,31 +2942,31 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C22" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D22" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E22" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="F22">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G22" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="H22" t="s">
-        <v>466</v>
+        <v>437</v>
       </c>
       <c r="I22" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J22" t="s">
-        <v>489</v>
+        <v>460</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -3129,31 +2974,31 @@
         <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C23" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D23" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E23" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="F23">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G23" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="H23" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I23" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J23" t="s">
-        <v>490</v>
+        <v>461</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -3161,31 +3006,31 @@
         <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C24" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D24" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E24" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="F24">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="H24" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I24" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J24" t="s">
-        <v>491</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -3193,31 +3038,31 @@
         <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C25" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D25" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E25" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="F25">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G25" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="H25" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="I25" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J25" t="s">
-        <v>492</v>
+        <v>463</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -3225,31 +3070,31 @@
         <v>34</v>
       </c>
       <c r="B26" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C26" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D26" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E26" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="F26">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="H26" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I26" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J26" t="s">
-        <v>493</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -3257,31 +3102,31 @@
         <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C27" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D27" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E27" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="F27">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="H27" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="I27" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J27" t="s">
-        <v>494</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -3289,31 +3134,31 @@
         <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C28" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D28" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E28" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="F28">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G28" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="H28" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="I28" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J28" t="s">
-        <v>495</v>
+        <v>466</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -3321,31 +3166,31 @@
         <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C29" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D29" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E29" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="F29">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G29" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="H29" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I29" t="s">
+        <v>438</v>
+      </c>
+      <c r="J29" t="s">
         <v>467</v>
-      </c>
-      <c r="J29" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -3353,31 +3198,31 @@
         <v>38</v>
       </c>
       <c r="B30" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C30" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D30" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E30" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="F30">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G30" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="H30" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="I30" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J30" t="s">
-        <v>497</v>
+        <v>468</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -3385,31 +3230,31 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C31" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D31" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E31" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="F31">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="H31" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="I31" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J31" t="s">
-        <v>498</v>
+        <v>469</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -3417,31 +3262,31 @@
         <v>40</v>
       </c>
       <c r="B32" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C32" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D32" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E32" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F32">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G32" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="H32" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I32" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J32" t="s">
-        <v>499</v>
+        <v>470</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -3449,31 +3294,31 @@
         <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C33" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D33" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E33" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="F33">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G33" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="H33" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I33" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J33" t="s">
-        <v>500</v>
+        <v>471</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -3481,31 +3326,31 @@
         <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C34" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D34" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E34" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F34">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G34" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="H34" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I34" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J34" t="s">
-        <v>501</v>
+        <v>472</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -3513,31 +3358,31 @@
         <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C35" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D35" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E35" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="F35">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="H35" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I35" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J35" t="s">
-        <v>502</v>
+        <v>473</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -3545,31 +3390,31 @@
         <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C36" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D36" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E36" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="F36">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="H36" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I36" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J36" t="s">
-        <v>503</v>
+        <v>474</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -3577,31 +3422,31 @@
         <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C37" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D37" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E37" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="F37">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G37" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="H37" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I37" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J37" t="s">
-        <v>504</v>
+        <v>475</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -3609,31 +3454,31 @@
         <v>46</v>
       </c>
       <c r="B38" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C38" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D38" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E38" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F38">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="H38" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I38" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J38" t="s">
-        <v>505</v>
+        <v>476</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -3641,31 +3486,31 @@
         <v>47</v>
       </c>
       <c r="B39" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C39" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D39" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="E39" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="F39">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="H39" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="I39" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J39" t="s">
-        <v>506</v>
+        <v>477</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -3673,31 +3518,31 @@
         <v>48</v>
       </c>
       <c r="B40" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C40" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D40" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E40" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="F40">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="H40" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I40" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J40" t="s">
-        <v>507</v>
+        <v>478</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -3705,31 +3550,31 @@
         <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C41" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D41" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="E41" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="F41">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="H41" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I41" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J41" t="s">
-        <v>508</v>
+        <v>479</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -3737,31 +3582,31 @@
         <v>50</v>
       </c>
       <c r="B42" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C42" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D42" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E42" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="F42">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="H42" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I42" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J42" t="s">
-        <v>509</v>
+        <v>480</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -3769,31 +3614,31 @@
         <v>51</v>
       </c>
       <c r="B43" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C43" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D43" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="E43" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="F43">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="H43" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I43" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J43" t="s">
-        <v>510</v>
+        <v>481</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -3801,31 +3646,31 @@
         <v>52</v>
       </c>
       <c r="B44" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C44" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D44" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E44" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="F44">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="H44" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I44" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J44" t="s">
-        <v>511</v>
+        <v>482</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -3833,31 +3678,31 @@
         <v>53</v>
       </c>
       <c r="B45" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C45" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D45" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E45" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="F45">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="H45" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I45" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J45" t="s">
-        <v>512</v>
+        <v>483</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -3865,31 +3710,31 @@
         <v>54</v>
       </c>
       <c r="B46" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C46" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D46" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E46" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="F46">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G46" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="H46" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I46" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J46" t="s">
-        <v>513</v>
+        <v>484</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -3897,31 +3742,31 @@
         <v>55</v>
       </c>
       <c r="B47" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C47" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D47" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E47" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="F47">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G47" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="H47" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I47" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J47" t="s">
-        <v>514</v>
+        <v>485</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -3929,31 +3774,31 @@
         <v>56</v>
       </c>
       <c r="B48" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C48" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D48" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E48" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="F48">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G48" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="H48" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I48" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J48" t="s">
-        <v>515</v>
+        <v>486</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -3961,31 +3806,31 @@
         <v>57</v>
       </c>
       <c r="B49" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C49" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D49" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E49" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F49">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G49" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="H49" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I49" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J49" t="s">
-        <v>516</v>
+        <v>487</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -3993,31 +3838,31 @@
         <v>58</v>
       </c>
       <c r="B50" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C50" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D50" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E50" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="F50">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G50" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="H50" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I50" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J50" t="s">
-        <v>517</v>
+        <v>488</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -4025,31 +3870,31 @@
         <v>59</v>
       </c>
       <c r="B51" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C51" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D51" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E51" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F51">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G51" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="H51" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I51" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J51" t="s">
-        <v>518</v>
+        <v>489</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -4057,31 +3902,31 @@
         <v>60</v>
       </c>
       <c r="B52" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C52" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D52" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E52" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="F52">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G52" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="H52" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="I52" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J52" t="s">
-        <v>519</v>
+        <v>490</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -4089,31 +3934,31 @@
         <v>61</v>
       </c>
       <c r="B53" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C53" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D53" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E53" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="F53">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G53" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="H53" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="I53" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J53" t="s">
-        <v>520</v>
+        <v>491</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -4121,31 +3966,31 @@
         <v>62</v>
       </c>
       <c r="B54" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C54" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D54" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E54" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="F54">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G54" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="H54" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I54" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J54" t="s">
-        <v>521</v>
+        <v>492</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -4153,31 +3998,31 @@
         <v>63</v>
       </c>
       <c r="B55" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D55" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E55" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="F55">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G55" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
       <c r="H55" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I55" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J55" t="s">
-        <v>522</v>
+        <v>493</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -4185,31 +4030,31 @@
         <v>64</v>
       </c>
       <c r="B56" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C56" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D56" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E56" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="F56">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G56" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="H56" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I56" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J56" t="s">
-        <v>523</v>
+        <v>494</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -4217,31 +4062,31 @@
         <v>65</v>
       </c>
       <c r="B57" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C57" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D57" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E57" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="F57">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G57" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="H57" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I57" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J57" t="s">
-        <v>524</v>
+        <v>495</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -4249,31 +4094,31 @@
         <v>66</v>
       </c>
       <c r="B58" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C58" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D58" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E58" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="F58">
-        <v>452</v>
+        <v>22</v>
       </c>
       <c r="G58" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="H58" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I58" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J58" t="s">
-        <v>525</v>
+        <v>496</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -4281,31 +4126,31 @@
         <v>67</v>
       </c>
       <c r="B59" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C59" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D59" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E59" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="F59">
-        <v>452</v>
+        <v>22</v>
       </c>
       <c r="G59" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="H59" t="s">
-        <v>466</v>
+        <v>437</v>
       </c>
       <c r="I59" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J59" t="s">
-        <v>526</v>
+        <v>497</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -4313,31 +4158,31 @@
         <v>68</v>
       </c>
       <c r="B60" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C60" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D60" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E60" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="F60">
-        <v>452</v>
+        <v>23</v>
       </c>
       <c r="G60" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="H60" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I60" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J60" t="s">
-        <v>527</v>
+        <v>498</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -4345,31 +4190,31 @@
         <v>69</v>
       </c>
       <c r="B61" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C61" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D61" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E61" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="F61">
-        <v>452</v>
+        <v>23</v>
       </c>
       <c r="G61" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="H61" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I61" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J61" t="s">
-        <v>528</v>
+        <v>499</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -4377,31 +4222,31 @@
         <v>70</v>
       </c>
       <c r="B62" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C62" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D62" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E62" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="F62">
-        <v>452</v>
+        <v>24</v>
       </c>
       <c r="G62" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="H62" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="I62" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J62" t="s">
-        <v>529</v>
+        <v>500</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -4409,31 +4254,31 @@
         <v>71</v>
       </c>
       <c r="B63" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C63" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D63" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E63" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="F63">
-        <v>453</v>
+        <v>24</v>
       </c>
       <c r="G63" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="H63" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I63" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J63" t="s">
-        <v>530</v>
+        <v>501</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -4441,31 +4286,31 @@
         <v>72</v>
       </c>
       <c r="B64" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C64" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D64" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E64" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="F64">
-        <v>453</v>
+        <v>25</v>
       </c>
       <c r="G64" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="H64" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I64" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J64" t="s">
-        <v>531</v>
+        <v>502</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -4473,31 +4318,31 @@
         <v>73</v>
       </c>
       <c r="B65" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C65" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D65" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E65" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F65">
-        <v>453</v>
+        <v>25</v>
       </c>
       <c r="G65" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="H65" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I65" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J65" t="s">
-        <v>532</v>
+        <v>503</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -4505,31 +4350,31 @@
         <v>74</v>
       </c>
       <c r="B66" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C66" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D66" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E66" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="F66">
-        <v>454</v>
+        <v>28</v>
       </c>
       <c r="G66" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="H66" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="I66" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J66" t="s">
-        <v>533</v>
+        <v>504</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -4537,31 +4382,31 @@
         <v>75</v>
       </c>
       <c r="B67" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C67" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D67" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E67" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="F67">
-        <v>454</v>
+        <v>28</v>
       </c>
       <c r="G67" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="H67" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I67" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J67" t="s">
-        <v>534</v>
+        <v>505</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -4569,31 +4414,31 @@
         <v>76</v>
       </c>
       <c r="B68" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C68" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D68" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E68" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="F68">
-        <v>454</v>
+        <v>29</v>
       </c>
       <c r="G68" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="H68" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I68" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J68" t="s">
-        <v>535</v>
+        <v>506</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -4601,31 +4446,31 @@
         <v>77</v>
       </c>
       <c r="B69" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C69" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D69" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E69" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="F69">
-        <v>455</v>
+        <v>29</v>
       </c>
       <c r="G69" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="H69" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I69" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J69" t="s">
-        <v>536</v>
+        <v>507</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -4633,31 +4478,31 @@
         <v>78</v>
       </c>
       <c r="B70" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C70" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D70" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E70" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F70">
-        <v>455</v>
+        <v>30</v>
       </c>
       <c r="G70" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="H70" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I70" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J70" t="s">
-        <v>537</v>
+        <v>508</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -4665,31 +4510,31 @@
         <v>79</v>
       </c>
       <c r="B71" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C71" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D71" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E71" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="F71">
-        <v>456</v>
+        <v>31</v>
       </c>
       <c r="G71" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="H71" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="I71" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J71" t="s">
-        <v>538</v>
+        <v>509</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -4697,31 +4542,31 @@
         <v>80</v>
       </c>
       <c r="B72" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C72" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D72" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E72" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="F72">
-        <v>456</v>
+        <v>33</v>
       </c>
       <c r="G72" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="H72" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="I72" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J72" t="s">
-        <v>539</v>
+        <v>510</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -4729,31 +4574,31 @@
         <v>81</v>
       </c>
       <c r="B73" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C73" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D73" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E73" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="F73">
-        <v>457</v>
+        <v>33</v>
       </c>
       <c r="G73" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="H73" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I73" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J73" t="s">
-        <v>540</v>
+        <v>511</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -4761,31 +4606,31 @@
         <v>82</v>
       </c>
       <c r="B74" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C74" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D74" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E74" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F74">
-        <v>457</v>
+        <v>33</v>
       </c>
       <c r="G74" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="H74" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I74" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J74" t="s">
-        <v>541</v>
+        <v>512</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -4793,31 +4638,31 @@
         <v>83</v>
       </c>
       <c r="B75" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C75" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D75" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E75" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F75">
-        <v>457</v>
+        <v>34</v>
       </c>
       <c r="G75" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="H75" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I75" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J75" t="s">
-        <v>542</v>
+        <v>513</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -4825,31 +4670,31 @@
         <v>84</v>
       </c>
       <c r="B76" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C76" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D76" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E76" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F76">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="G76" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="H76" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I76" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J76" t="s">
-        <v>543</v>
+        <v>514</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -4857,31 +4702,31 @@
         <v>85</v>
       </c>
       <c r="B77" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C77" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D77" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E77" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="F77">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="G77" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="H77" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="I77" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J77" t="s">
-        <v>544</v>
+        <v>515</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -4889,31 +4734,31 @@
         <v>86</v>
       </c>
       <c r="B78" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C78" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D78" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="E78" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F78">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="G78" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="H78" t="s">
-        <v>466</v>
+        <v>437</v>
       </c>
       <c r="I78" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J78" t="s">
-        <v>545</v>
+        <v>516</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -4921,31 +4766,31 @@
         <v>87</v>
       </c>
       <c r="B79" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C79" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D79" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E79" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="F79">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="G79" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="H79" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I79" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J79" t="s">
-        <v>546</v>
+        <v>517</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -4953,31 +4798,31 @@
         <v>88</v>
       </c>
       <c r="B80" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C80" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D80" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E80" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="F80">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G80" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="H80" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I80" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J80" t="s">
-        <v>547</v>
+        <v>518</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -4985,31 +4830,31 @@
         <v>89</v>
       </c>
       <c r="B81" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C81" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D81" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E81" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="F81">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G81" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="H81" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I81" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J81" t="s">
-        <v>548</v>
+        <v>519</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -5017,31 +4862,31 @@
         <v>90</v>
       </c>
       <c r="B82" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C82" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D82" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E82" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F82">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G82" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="H82" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I82" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J82" t="s">
-        <v>549</v>
+        <v>520</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -5049,31 +4894,31 @@
         <v>91</v>
       </c>
       <c r="B83" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C83" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D83" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E83" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F83">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="G83" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="H83" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I83" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J83" t="s">
-        <v>550</v>
+        <v>521</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -5081,31 +4926,31 @@
         <v>92</v>
       </c>
       <c r="B84" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C84" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D84" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E84" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="F84">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="G84" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="H84" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I84" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J84" t="s">
-        <v>551</v>
+        <v>522</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -5113,31 +4958,31 @@
         <v>93</v>
       </c>
       <c r="B85" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C85" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D85" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E85" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="F85">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="G85" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="H85" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I85" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J85" t="s">
-        <v>552</v>
+        <v>523</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -5145,31 +4990,31 @@
         <v>94</v>
       </c>
       <c r="B86" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C86" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D86" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E86" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>455</v>
       </c>
       <c r="G86" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="H86" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I86" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J86" t="s">
-        <v>553</v>
+        <v>524</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -5177,31 +5022,31 @@
         <v>95</v>
       </c>
       <c r="B87" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C87" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D87" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E87" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>455</v>
       </c>
       <c r="G87" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="H87" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I87" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J87" t="s">
-        <v>554</v>
+        <v>525</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -5209,31 +5054,31 @@
         <v>96</v>
       </c>
       <c r="B88" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C88" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D88" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E88" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>456</v>
       </c>
       <c r="G88" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="H88" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="I88" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J88" t="s">
-        <v>555</v>
+        <v>526</v>
       </c>
     </row>
     <row r="89" spans="1:10">
@@ -5241,31 +5086,31 @@
         <v>97</v>
       </c>
       <c r="B89" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C89" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D89" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E89" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="F89">
-        <v>1</v>
+        <v>457</v>
       </c>
       <c r="G89" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="H89" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I89" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J89" t="s">
-        <v>556</v>
+        <v>527</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -5273,31 +5118,31 @@
         <v>98</v>
       </c>
       <c r="B90" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C90" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D90" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E90" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="F90">
-        <v>1</v>
+        <v>458</v>
       </c>
       <c r="G90" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="H90" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I90" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J90" t="s">
-        <v>557</v>
+        <v>528</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -5305,31 +5150,31 @@
         <v>99</v>
       </c>
       <c r="B91" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C91" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D91" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E91" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>458</v>
       </c>
       <c r="G91" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="H91" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I91" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J91" t="s">
-        <v>558</v>
+        <v>529</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -5337,31 +5182,31 @@
         <v>100</v>
       </c>
       <c r="B92" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C92" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D92" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E92" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="F92">
-        <v>2</v>
+        <v>458</v>
       </c>
       <c r="G92" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="H92" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="I92" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J92" t="s">
-        <v>559</v>
+        <v>530</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -5369,31 +5214,31 @@
         <v>101</v>
       </c>
       <c r="B93" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C93" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D93" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E93" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="F93">
-        <v>2</v>
+        <v>460</v>
       </c>
       <c r="G93" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="H93" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I93" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J93" t="s">
-        <v>560</v>
+        <v>531</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -5401,31 +5246,31 @@
         <v>102</v>
       </c>
       <c r="B94" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C94" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D94" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E94" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="F94">
-        <v>2</v>
+        <v>460</v>
       </c>
       <c r="G94" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="H94" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="I94" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J94" t="s">
-        <v>561</v>
+        <v>532</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -5433,31 +5278,31 @@
         <v>103</v>
       </c>
       <c r="B95" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C95" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D95" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E95" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="F95">
-        <v>2</v>
+        <v>460</v>
       </c>
       <c r="G95" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="H95" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I95" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J95" t="s">
-        <v>562</v>
+        <v>533</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -5465,31 +5310,31 @@
         <v>104</v>
       </c>
       <c r="B96" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C96" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D96" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E96" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="F96">
-        <v>2</v>
+        <v>460</v>
       </c>
       <c r="G96" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="H96" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I96" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J96" t="s">
-        <v>563</v>
+        <v>534</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -5497,31 +5342,31 @@
         <v>105</v>
       </c>
       <c r="B97" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C97" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D97" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E97" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="F97">
-        <v>2</v>
+        <v>460</v>
       </c>
       <c r="G97" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="H97" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I97" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J97" t="s">
-        <v>564</v>
+        <v>535</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -5529,31 +5374,31 @@
         <v>106</v>
       </c>
       <c r="B98" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C98" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D98" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E98" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="F98">
-        <v>2</v>
+        <v>461</v>
       </c>
       <c r="G98" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="H98" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I98" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J98" t="s">
-        <v>565</v>
+        <v>536</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -5561,31 +5406,31 @@
         <v>107</v>
       </c>
       <c r="B99" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C99" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D99" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E99" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="F99">
-        <v>2</v>
+        <v>461</v>
       </c>
       <c r="G99" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="H99" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I99" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="J99" t="s">
-        <v>566</v>
+        <v>537</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -5593,31 +5438,31 @@
         <v>108</v>
       </c>
       <c r="B100" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C100" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D100" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="E100" t="s">
-        <v>178</v>
+        <v>255</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
       <c r="G100" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="H100" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I100" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="J100" t="s">
-        <v>567</v>
+        <v>538</v>
       </c>
     </row>
     <row r="101" spans="1:10">
@@ -5625,31 +5470,31 @@
         <v>109</v>
       </c>
       <c r="B101" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C101" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D101" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="E101" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
       <c r="G101" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="H101" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I101" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="J101" t="s">
-        <v>568</v>
+        <v>539</v>
       </c>
     </row>
     <row r="102" spans="1:10">
@@ -5657,31 +5502,31 @@
         <v>110</v>
       </c>
       <c r="B102" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C102" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D102" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="E102" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="F102">
         <v>1</v>
       </c>
       <c r="G102" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="H102" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I102" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="J102" t="s">
-        <v>569</v>
+        <v>540</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -5689,31 +5534,31 @@
         <v>111</v>
       </c>
       <c r="B103" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C103" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D103" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="E103" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
       <c r="G103" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="H103" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I103" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="J103" t="s">
-        <v>570</v>
+        <v>541</v>
       </c>
     </row>
     <row r="104" spans="1:10">
@@ -5721,31 +5566,31 @@
         <v>112</v>
       </c>
       <c r="B104" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C104" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D104" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="E104" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="F104">
         <v>1</v>
       </c>
       <c r="G104" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="H104" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I104" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="J104" t="s">
-        <v>571</v>
+        <v>542</v>
       </c>
     </row>
     <row r="105" spans="1:10">
@@ -5753,31 +5598,31 @@
         <v>113</v>
       </c>
       <c r="B105" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C105" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D105" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="E105" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="F105">
         <v>1</v>
       </c>
       <c r="G105" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="H105" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I105" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="J105" t="s">
-        <v>572</v>
+        <v>543</v>
       </c>
     </row>
     <row r="106" spans="1:10">
@@ -5785,31 +5630,31 @@
         <v>114</v>
       </c>
       <c r="B106" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C106" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D106" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="E106" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
       <c r="G106" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="H106" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I106" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="J106" t="s">
-        <v>573</v>
+        <v>544</v>
       </c>
     </row>
     <row r="107" spans="1:10">
@@ -5817,31 +5662,31 @@
         <v>115</v>
       </c>
       <c r="B107" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C107" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D107" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="E107" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="F107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G107" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="H107" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="I107" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="J107" t="s">
-        <v>574</v>
+        <v>545</v>
       </c>
     </row>
     <row r="108" spans="1:10">
@@ -5849,31 +5694,31 @@
         <v>116</v>
       </c>
       <c r="B108" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C108" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D108" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="E108" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="F108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G108" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="H108" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I108" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="J108" t="s">
-        <v>575</v>
+        <v>546</v>
       </c>
     </row>
     <row r="109" spans="1:10">
@@ -5881,31 +5726,31 @@
         <v>117</v>
       </c>
       <c r="B109" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C109" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D109" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="E109" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="F109">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G109" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="H109" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="I109" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="J109" t="s">
-        <v>576</v>
+        <v>547</v>
       </c>
     </row>
     <row r="110" spans="1:10">
@@ -5913,31 +5758,31 @@
         <v>118</v>
       </c>
       <c r="B110" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C110" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D110" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="E110" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="F110">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G110" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="H110" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="I110" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="J110" t="s">
-        <v>577</v>
+        <v>548</v>
       </c>
     </row>
     <row r="111" spans="1:10">
@@ -5945,31 +5790,31 @@
         <v>119</v>
       </c>
       <c r="B111" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C111" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D111" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="E111" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="F111">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G111" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="H111" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I111" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="J111" t="s">
-        <v>578</v>
+        <v>549</v>
       </c>
     </row>
     <row r="112" spans="1:10">
@@ -5977,31 +5822,31 @@
         <v>120</v>
       </c>
       <c r="B112" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C112" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D112" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="E112" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="F112">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G112" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="H112" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I112" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="J112" t="s">
-        <v>579</v>
+        <v>550</v>
       </c>
     </row>
     <row r="113" spans="1:10">
@@ -6009,31 +5854,31 @@
         <v>121</v>
       </c>
       <c r="B113" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C113" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D113" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="E113" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="F113">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G113" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="H113" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I113" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="J113" t="s">
-        <v>580</v>
+        <v>551</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -6041,31 +5886,31 @@
         <v>122</v>
       </c>
       <c r="B114" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C114" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D114" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="E114" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="F114">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G114" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="H114" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I114" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="J114" t="s">
-        <v>581</v>
+        <v>552</v>
       </c>
     </row>
     <row r="115" spans="1:10">
@@ -6073,31 +5918,31 @@
         <v>123</v>
       </c>
       <c r="B115" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="C115" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D115" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="E115" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="F115">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G115" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="H115" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I115" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J115" t="s">
-        <v>582</v>
+        <v>553</v>
       </c>
     </row>
     <row r="116" spans="1:10">
@@ -6105,31 +5950,31 @@
         <v>124</v>
       </c>
       <c r="B116" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="C116" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D116" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="E116" t="s">
-        <v>189</v>
+        <v>270</v>
       </c>
       <c r="F116">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G116" t="s">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="H116" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I116" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J116" t="s">
-        <v>583</v>
+        <v>554</v>
       </c>
     </row>
     <row r="117" spans="1:10">
@@ -6137,31 +5982,31 @@
         <v>125</v>
       </c>
       <c r="B117" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="C117" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D117" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E117" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="F117">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G117" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="H117" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I117" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J117" t="s">
-        <v>584</v>
+        <v>555</v>
       </c>
     </row>
     <row r="118" spans="1:10">
@@ -6169,31 +6014,31 @@
         <v>126</v>
       </c>
       <c r="B118" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="C118" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D118" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="E118" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="F118">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G118" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="H118" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="I118" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J118" t="s">
-        <v>585</v>
+        <v>556</v>
       </c>
     </row>
     <row r="119" spans="1:10">
@@ -6201,31 +6046,31 @@
         <v>127</v>
       </c>
       <c r="B119" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="C119" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D119" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E119" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="F119">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G119" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="H119" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I119" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J119" t="s">
-        <v>586</v>
+        <v>557</v>
       </c>
     </row>
     <row r="120" spans="1:10">
@@ -6233,31 +6078,31 @@
         <v>128</v>
       </c>
       <c r="B120" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="C120" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D120" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E120" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="F120">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G120" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="H120" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I120" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J120" t="s">
-        <v>587</v>
+        <v>558</v>
       </c>
     </row>
     <row r="121" spans="1:10">
@@ -6265,31 +6110,31 @@
         <v>129</v>
       </c>
       <c r="B121" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="C121" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D121" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E121" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="F121">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G121" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="H121" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I121" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J121" t="s">
-        <v>588</v>
+        <v>559</v>
       </c>
     </row>
     <row r="122" spans="1:10">
@@ -6297,31 +6142,31 @@
         <v>130</v>
       </c>
       <c r="B122" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="C122" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D122" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="E122" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="F122">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G122" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="H122" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="I122" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J122" t="s">
-        <v>589</v>
+        <v>560</v>
       </c>
     </row>
     <row r="123" spans="1:10">
@@ -6329,31 +6174,31 @@
         <v>131</v>
       </c>
       <c r="B123" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C123" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D123" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="E123" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="F123">
-        <v>15</v>
+        <v>452</v>
       </c>
       <c r="G123" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="H123" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="I123" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J123" t="s">
-        <v>590</v>
+        <v>561</v>
       </c>
     </row>
     <row r="124" spans="1:10">
@@ -6361,31 +6206,31 @@
         <v>132</v>
       </c>
       <c r="B124" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C124" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D124" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E124" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="F124">
-        <v>17</v>
+        <v>453</v>
       </c>
       <c r="G124" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="H124" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I124" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J124" t="s">
-        <v>591</v>
+        <v>562</v>
       </c>
     </row>
     <row r="125" spans="1:10">
@@ -6393,31 +6238,31 @@
         <v>133</v>
       </c>
       <c r="B125" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C125" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D125" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E125" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="F125">
-        <v>18</v>
+        <v>453</v>
       </c>
       <c r="G125" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="H125" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I125" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J125" t="s">
-        <v>592</v>
+        <v>563</v>
       </c>
     </row>
     <row r="126" spans="1:10">
@@ -6425,31 +6270,31 @@
         <v>134</v>
       </c>
       <c r="B126" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C126" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D126" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="E126" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="F126">
-        <v>19</v>
+        <v>453</v>
       </c>
       <c r="G126" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="H126" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I126" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J126" t="s">
-        <v>593</v>
+        <v>564</v>
       </c>
     </row>
     <row r="127" spans="1:10">
@@ -6457,31 +6302,31 @@
         <v>135</v>
       </c>
       <c r="B127" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C127" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D127" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="E127" t="s">
-        <v>208</v>
+        <v>280</v>
       </c>
       <c r="F127">
-        <v>20</v>
+        <v>454</v>
       </c>
       <c r="G127" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="H127" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I127" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J127" t="s">
-        <v>594</v>
+        <v>565</v>
       </c>
     </row>
     <row r="128" spans="1:10">
@@ -6489,31 +6334,31 @@
         <v>136</v>
       </c>
       <c r="B128" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C128" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D128" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="E128" t="s">
-        <v>209</v>
+        <v>281</v>
       </c>
       <c r="F128">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="G128" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="H128" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="I128" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J128" t="s">
-        <v>595</v>
+        <v>566</v>
       </c>
     </row>
     <row r="129" spans="1:10">
@@ -6521,31 +6366,31 @@
         <v>137</v>
       </c>
       <c r="B129" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C129" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D129" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E129" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F129">
-        <v>23</v>
+        <v>455</v>
       </c>
       <c r="G129" t="s">
+        <v>422</v>
+      </c>
+      <c r="H129" t="s">
+        <v>436</v>
+      </c>
+      <c r="I129" t="s">
         <v>439</v>
       </c>
-      <c r="H129" t="s">
-        <v>465</v>
-      </c>
-      <c r="I129" t="s">
-        <v>468</v>
-      </c>
       <c r="J129" t="s">
-        <v>596</v>
+        <v>567</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -6553,31 +6398,31 @@
         <v>138</v>
       </c>
       <c r="B130" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C130" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D130" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E130" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="F130">
-        <v>24</v>
+        <v>455</v>
       </c>
       <c r="G130" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="H130" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I130" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J130" t="s">
-        <v>597</v>
+        <v>568</v>
       </c>
     </row>
     <row r="131" spans="1:10">
@@ -6585,31 +6430,31 @@
         <v>139</v>
       </c>
       <c r="B131" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C131" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D131" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E131" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="F131">
-        <v>24</v>
+        <v>455</v>
       </c>
       <c r="G131" t="s">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="H131" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I131" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J131" t="s">
-        <v>598</v>
+        <v>569</v>
       </c>
     </row>
     <row r="132" spans="1:10">
@@ -6617,31 +6462,31 @@
         <v>140</v>
       </c>
       <c r="B132" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C132" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D132" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="E132" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="F132">
-        <v>24</v>
+        <v>457</v>
       </c>
       <c r="G132" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="H132" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="I132" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J132" t="s">
-        <v>599</v>
+        <v>570</v>
       </c>
     </row>
     <row r="133" spans="1:10">
@@ -6649,31 +6494,31 @@
         <v>141</v>
       </c>
       <c r="B133" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C133" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D133" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="E133" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="F133">
-        <v>28</v>
+        <v>457</v>
       </c>
       <c r="G133" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="H133" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I133" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J133" t="s">
-        <v>600</v>
+        <v>571</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -6681,31 +6526,31 @@
         <v>142</v>
       </c>
       <c r="B134" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C134" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D134" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E134" t="s">
-        <v>217</v>
+        <v>287</v>
       </c>
       <c r="F134">
-        <v>28</v>
+        <v>460</v>
       </c>
       <c r="G134" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
       <c r="H134" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I134" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J134" t="s">
-        <v>601</v>
+        <v>572</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -6713,31 +6558,31 @@
         <v>143</v>
       </c>
       <c r="B135" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C135" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D135" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E135" t="s">
-        <v>218</v>
+        <v>288</v>
       </c>
       <c r="F135">
-        <v>29</v>
+        <v>460</v>
       </c>
       <c r="G135" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="H135" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I135" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J135" t="s">
-        <v>602</v>
+        <v>573</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -6745,31 +6590,31 @@
         <v>144</v>
       </c>
       <c r="B136" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C136" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D136" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="E136" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="F136">
-        <v>29</v>
+        <v>460</v>
       </c>
       <c r="G136" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="H136" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I136" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J136" t="s">
-        <v>603</v>
+        <v>574</v>
       </c>
     </row>
     <row r="137" spans="1:10">
@@ -6777,31 +6622,31 @@
         <v>145</v>
       </c>
       <c r="B137" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C137" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D137" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="E137" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="F137">
-        <v>31</v>
+        <v>461</v>
       </c>
       <c r="G137" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="H137" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I137" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J137" t="s">
-        <v>604</v>
+        <v>575</v>
       </c>
     </row>
     <row r="138" spans="1:10">
@@ -6809,31 +6654,31 @@
         <v>146</v>
       </c>
       <c r="B138" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C138" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D138" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E138" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="F138">
-        <v>33</v>
+        <v>461</v>
       </c>
       <c r="G138" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="H138" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I138" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J138" t="s">
-        <v>605</v>
+        <v>576</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -6841,31 +6686,31 @@
         <v>147</v>
       </c>
       <c r="B139" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C139" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D139" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E139" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F139">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G139" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="H139" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I139" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J139" t="s">
-        <v>606</v>
+        <v>577</v>
       </c>
     </row>
     <row r="140" spans="1:10">
@@ -6873,31 +6718,31 @@
         <v>148</v>
       </c>
       <c r="B140" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C140" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D140" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E140" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="F140">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G140" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
       <c r="H140" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I140" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J140" t="s">
-        <v>607</v>
+        <v>578</v>
       </c>
     </row>
     <row r="141" spans="1:10">
@@ -6905,31 +6750,31 @@
         <v>149</v>
       </c>
       <c r="B141" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="C141" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D141" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="E141" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="F141">
-        <v>453</v>
+        <v>2</v>
       </c>
       <c r="G141" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="H141" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="I141" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J141" t="s">
-        <v>608</v>
+        <v>579</v>
       </c>
     </row>
     <row r="142" spans="1:10">
@@ -6937,415 +6782,31 @@
         <v>150</v>
       </c>
       <c r="B142" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="C142" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D142" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E142" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="F142">
-        <v>453</v>
+        <v>2</v>
       </c>
       <c r="G142" t="s">
-        <v>452</v>
+        <v>435</v>
       </c>
       <c r="H142" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="I142" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J142" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10">
-      <c r="A143" t="s">
-        <v>151</v>
-      </c>
-      <c r="B143" t="s">
-        <v>165</v>
-      </c>
-      <c r="C143" t="s">
-        <v>168</v>
-      </c>
-      <c r="D143" t="s">
-        <v>172</v>
-      </c>
-      <c r="E143" t="s">
-        <v>302</v>
-      </c>
-      <c r="F143">
-        <v>453</v>
-      </c>
-      <c r="G143" t="s">
-        <v>453</v>
-      </c>
-      <c r="H143" t="s">
-        <v>465</v>
-      </c>
-      <c r="I143" t="s">
-        <v>468</v>
-      </c>
-      <c r="J143" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10">
-      <c r="A144" t="s">
-        <v>152</v>
-      </c>
-      <c r="B144" t="s">
-        <v>165</v>
-      </c>
-      <c r="C144" t="s">
-        <v>168</v>
-      </c>
-      <c r="D144" t="s">
-        <v>172</v>
-      </c>
-      <c r="E144" t="s">
-        <v>303</v>
-      </c>
-      <c r="F144">
-        <v>454</v>
-      </c>
-      <c r="G144" t="s">
-        <v>454</v>
-      </c>
-      <c r="H144" t="s">
-        <v>465</v>
-      </c>
-      <c r="I144" t="s">
-        <v>468</v>
-      </c>
-      <c r="J144" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10">
-      <c r="A145" t="s">
-        <v>153</v>
-      </c>
-      <c r="B145" t="s">
-        <v>165</v>
-      </c>
-      <c r="C145" t="s">
-        <v>168</v>
-      </c>
-      <c r="D145" t="s">
-        <v>172</v>
-      </c>
-      <c r="E145" t="s">
-        <v>304</v>
-      </c>
-      <c r="F145">
-        <v>454</v>
-      </c>
-      <c r="G145" t="s">
-        <v>455</v>
-      </c>
-      <c r="H145" t="s">
-        <v>465</v>
-      </c>
-      <c r="I145" t="s">
-        <v>468</v>
-      </c>
-      <c r="J145" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10">
-      <c r="A146" t="s">
-        <v>154</v>
-      </c>
-      <c r="B146" t="s">
-        <v>165</v>
-      </c>
-      <c r="C146" t="s">
-        <v>168</v>
-      </c>
-      <c r="D146" t="s">
-        <v>172</v>
-      </c>
-      <c r="E146" t="s">
-        <v>305</v>
-      </c>
-      <c r="F146">
-        <v>455</v>
-      </c>
-      <c r="G146" t="s">
-        <v>456</v>
-      </c>
-      <c r="H146" t="s">
-        <v>465</v>
-      </c>
-      <c r="I146" t="s">
-        <v>468</v>
-      </c>
-      <c r="J146" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10">
-      <c r="A147" t="s">
-        <v>155</v>
-      </c>
-      <c r="B147" t="s">
-        <v>165</v>
-      </c>
-      <c r="C147" t="s">
-        <v>168</v>
-      </c>
-      <c r="D147" t="s">
-        <v>173</v>
-      </c>
-      <c r="E147" t="s">
-        <v>306</v>
-      </c>
-      <c r="F147">
-        <v>460</v>
-      </c>
-      <c r="G147" t="s">
-        <v>457</v>
-      </c>
-      <c r="H147" t="s">
-        <v>465</v>
-      </c>
-      <c r="I147" t="s">
-        <v>468</v>
-      </c>
-      <c r="J147" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10">
-      <c r="A148" t="s">
-        <v>156</v>
-      </c>
-      <c r="B148" t="s">
-        <v>165</v>
-      </c>
-      <c r="C148" t="s">
-        <v>168</v>
-      </c>
-      <c r="D148" t="s">
-        <v>173</v>
-      </c>
-      <c r="E148" t="s">
-        <v>307</v>
-      </c>
-      <c r="F148">
-        <v>461</v>
-      </c>
-      <c r="G148" t="s">
-        <v>458</v>
-      </c>
-      <c r="H148" t="s">
-        <v>465</v>
-      </c>
-      <c r="I148" t="s">
-        <v>468</v>
-      </c>
-      <c r="J148" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10">
-      <c r="A149" t="s">
-        <v>157</v>
-      </c>
-      <c r="B149" t="s">
-        <v>165</v>
-      </c>
-      <c r="C149" t="s">
-        <v>168</v>
-      </c>
-      <c r="D149" t="s">
-        <v>173</v>
-      </c>
-      <c r="E149" t="s">
-        <v>308</v>
-      </c>
-      <c r="F149">
-        <v>461</v>
-      </c>
-      <c r="G149" t="s">
-        <v>459</v>
-      </c>
-      <c r="H149" t="s">
-        <v>465</v>
-      </c>
-      <c r="I149" t="s">
-        <v>468</v>
-      </c>
-      <c r="J149" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10">
-      <c r="A150" t="s">
-        <v>158</v>
-      </c>
-      <c r="B150" t="s">
-        <v>166</v>
-      </c>
-      <c r="C150" t="s">
-        <v>168</v>
-      </c>
-      <c r="D150" t="s">
-        <v>173</v>
-      </c>
-      <c r="E150" t="s">
-        <v>255</v>
-      </c>
-      <c r="F150">
-        <v>1</v>
-      </c>
-      <c r="G150" t="s">
-        <v>460</v>
-      </c>
-      <c r="H150" t="s">
-        <v>465</v>
-      </c>
-      <c r="I150" t="s">
-        <v>468</v>
-      </c>
-      <c r="J150" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10">
-      <c r="A151" t="s">
-        <v>159</v>
-      </c>
-      <c r="B151" t="s">
-        <v>166</v>
-      </c>
-      <c r="C151" t="s">
-        <v>168</v>
-      </c>
-      <c r="D151" t="s">
-        <v>173</v>
-      </c>
-      <c r="E151" t="s">
-        <v>309</v>
-      </c>
-      <c r="F151">
-        <v>2</v>
-      </c>
-      <c r="G151" t="s">
-        <v>461</v>
-      </c>
-      <c r="H151" t="s">
-        <v>465</v>
-      </c>
-      <c r="I151" t="s">
-        <v>468</v>
-      </c>
-      <c r="J151" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10">
-      <c r="A152" t="s">
-        <v>160</v>
-      </c>
-      <c r="B152" t="s">
-        <v>166</v>
-      </c>
-      <c r="C152" t="s">
-        <v>168</v>
-      </c>
-      <c r="D152" t="s">
-        <v>172</v>
-      </c>
-      <c r="E152" t="s">
-        <v>310</v>
-      </c>
-      <c r="F152">
-        <v>1</v>
-      </c>
-      <c r="G152" t="s">
-        <v>462</v>
-      </c>
-      <c r="H152" t="s">
-        <v>465</v>
-      </c>
-      <c r="I152" t="s">
-        <v>468</v>
-      </c>
-      <c r="J152" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10">
-      <c r="A153" t="s">
-        <v>161</v>
-      </c>
-      <c r="B153" t="s">
-        <v>166</v>
-      </c>
-      <c r="C153" t="s">
-        <v>168</v>
-      </c>
-      <c r="D153" t="s">
-        <v>172</v>
-      </c>
-      <c r="E153" t="s">
-        <v>259</v>
-      </c>
-      <c r="F153">
-        <v>2</v>
-      </c>
-      <c r="G153" t="s">
-        <v>463</v>
-      </c>
-      <c r="H153" t="s">
-        <v>465</v>
-      </c>
-      <c r="I153" t="s">
-        <v>468</v>
-      </c>
-      <c r="J153" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10">
-      <c r="A154" t="s">
-        <v>162</v>
-      </c>
-      <c r="B154" t="s">
-        <v>166</v>
-      </c>
-      <c r="C154" t="s">
-        <v>168</v>
-      </c>
-      <c r="D154" t="s">
-        <v>172</v>
-      </c>
-      <c r="E154" t="s">
-        <v>311</v>
-      </c>
-      <c r="F154">
-        <v>2</v>
-      </c>
-      <c r="G154" t="s">
-        <v>464</v>
-      </c>
-      <c r="H154" t="s">
-        <v>466</v>
-      </c>
-      <c r="I154" t="s">
-        <v>468</v>
-      </c>
-      <c r="J154" t="s">
-        <v>621</v>
+        <v>580</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/coded_findings.xlsx
+++ b/outputs/coded_findings.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="155">
   <si>
     <t>snippet_id</t>
   </si>
@@ -70,6 +70,12 @@
     <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_EFFECTIVENESS__0008</t>
   </si>
   <si>
+    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_EFFECTIVENESS__0009</t>
+  </si>
+  <si>
+    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_EFFECTIVENESS__0010</t>
+  </si>
+  <si>
     <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_EFFECTIVENESS__0001</t>
   </si>
   <si>
@@ -109,6 +115,15 @@
     <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_EFFECTIVENESS__0013</t>
   </si>
   <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_EFFECTIVENESS__0014</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_EFFECTIVENESS__0015</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_EFFECTIVENESS__0016</t>
+  </si>
+  <si>
     <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0001</t>
   </si>
   <si>
@@ -133,75 +148,6 @@
     <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0008</t>
   </si>
   <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0009</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0010</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0011</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0012</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0013</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0014</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0015</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0001</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0002</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0003</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0004</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0005</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0006</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0007</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0008</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0009</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0010</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0011</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0012</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0013</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0014</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0015</t>
-  </si>
-  <si>
-    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0016</t>
-  </si>
-  <si>
     <t>AIPPI position paper on the CPVO.CPVR Call for Evidence March 2025.pdf</t>
   </si>
   <si>
@@ -217,12 +163,12 @@
     <t>OBJECTIVES</t>
   </si>
   <si>
+    <t>RIGHTS_BALANCE</t>
+  </si>
+  <si>
     <t>INNOVATION_MARKET</t>
   </si>
   <si>
-    <t>RIGHTS_BALANCE</t>
-  </si>
-  <si>
     <t>IP_FRAMEWORK</t>
   </si>
   <si>
@@ -241,22 +187,28 @@
     <t>Holders of CPVR should have the same rights and remedies granted to other IP holders under the EU enforcement directive. To this end, the relation between the Basic Regulation and the EU enforcement directive should be clarified.</t>
   </si>
   <si>
+    <t>The definition of EDVs under Article 13(6), especially as regards the concepts of "predominantly derived" under Article 13(6)(a) and "conforms essentially to the initial variety in the expression of the characteristics …." under Article 13(6)(c), should be updated taking into account the guidance provided by the Explanatory Notes on Essentially Derived Varieties under the 1991 Act of the UPOV Convention, adopted by the Council at its fifty-seventh ordinary session on 27 October 2023 and further guidance should be provided on how to establish in practice if a variety is an EDV.</t>
+  </si>
+  <si>
     <t>Article 95 provides that "Prior to the grant of Community plant variety rights, the holder may require reasonable compensation from any person who has, in the time between publication of the application for a Community plant variety right and grant thereof, effected an act that he would be prohibited from performing subsequent thereto". However, the concept of reasonable compensation is extremely vague and lends itself to different interpretations at the national level in the case of enforcement.</t>
   </si>
   <si>
+    <t>For provisional protection to be effective, it would be advisable to delineate the concept of "reasonable compensation" in its conceivable amount so as to provide reliable reference elements for (prospective) rights holders to prevent acts potentially adversely affecting their PVRs, where subsequently granted.</t>
+  </si>
+  <si>
     <t>In Nigeria, the relationship between Plant Variety Protection (PVP) and traditional intellectual property rights (IPR) is evolving, especially with the recent enactment of the Plant Variety Protection Act in 2021 which aimed at: promoting increased staple crop productivity for smallholder farmers in Nigeria and encourage investment in plant breeding and crop variety development; promoting increased mutual accountability in the seed sector; and protecting new varieties of plants.</t>
   </si>
   <si>
     <t>Section 5 of the Plant Variety Protection Act 2021 established a Plant Variety Protection Office in Nigeria to grant breeders rights, facilitate transfer and licensing of plant breeder’s rights, collaborate with local and international bodies whose functions relate to plant breeding and perform other necessary functions.</t>
   </si>
   <si>
-    <t>The National Agricultural Seed Council NASC (2007) is instrumental in Nigeria's seed sector regulation, overseeing the Plant Breeders' Rights Act implementation, promote and stimulate the development of dependable seed industry, facilitating the registration of new plant varieties, protect farmers from the sales of poor quality seeds, facilitate the production and marketing of high quality seeds in Nigeria, provide a legal backing for the official testing certification, sales, importation, exportation and use of seed.</t>
-  </si>
-  <si>
     <t>PVR regimes, which are a part of larger IP regimes, seek to achieve a careful equilibrium between encouraging innovation and guaranteeing the preservation of genetic variation.</t>
   </si>
   <si>
-    <t>PVR regimes encourage the generation of new varieties that are suited to address changing market needs and environmental issues by providing incentives for research and development.</t>
+    <t>Fundamentally, PVR gives breeders an exclusive authority to commercially propagate, market, and distribute their registered plant varieties. PVR regimes encourage the generation of new varieties that are suited to address changing market needs and environmental issues by providing incentives for research and development.</t>
+  </si>
+  <si>
+    <t>However, the implementation of PVR regulations raises complex ethical, legal and socioeconomic considerations. Concerns about farmers' rights, benefit-sharing arrangements, and access to genetic resources are major problems that highlight the necessity of a comprehensive and inclusive approach to plant variety sustainability.</t>
   </si>
   <si>
     <t>Nigeria was not a signatory to the International Union for the Protection of New Varieties of Plants (UPOV) Convention (Okonkwo, et al 2021) which to a large extent impeded the exploitation of such rights. It even deprived plant breeders in Nigeria access to high-quality new varieties of plant from foreign countries and also discourages foreign plant breeders since their new plant variety cannot be protected. These lacunae had surreptitiously deprived Nigeria of innovative opportunities in this sector unlike her counterparts – Uganda (Uganda Plant Variety Act2014), Kenya (Seed and Plant Varieties Act 2012) and South Africa (Plant Breeder’s Rights Act 1976).</t>
@@ -268,259 +220,151 @@
     <t>This system encourages investment in plant breeding and crop variety development, aiming to boost agricultural productivity and innovation.</t>
   </si>
   <si>
-    <t>1. The PVP Act grants registered plant breeders Intellectual Property rights, thereby providing incentives for the development of new crop varieties and encouraging more farmers to engage in plant breeding.
-2. Breeding entities collaborate with farmers and local institutions during plant variety evaluations, enhancing capacity building and creating employment opportunities.
-3. Intellectual Property protection for plant breeders boosts investment in breeding and developing new plant varieties, as investors can now rely on a structured protection system.</t>
-  </si>
-  <si>
-    <t>4. The PVP Act will encourage non-resident or foreign plant breeder applications, enhancing access to foreign plant varieties by ensuring adequate protection of their varieties.
-5. It is expected that the proper implementation of the provisions of the PVP will encourage research and development by breeders, thereby leading to higher agricultural productivity, and a boost in the agricultural sector would have a reverberating effect on Nigeria’s economy.</t>
-  </si>
-  <si>
-    <t>However, the implementation of PVR regulations raises complex ethical, legal and socioeconomic considerations. Concerns about farmers' rights, benefit-sharing arrangements, and access to genetic resources are major problems that highlight the necessity of a comprehensive and inclusive approach to plant variety sustainability.</t>
-  </si>
-  <si>
     <t>Breeders have the right to save seeds for the future use to the exclusion of other farmers within a reasonable limit and subject to the safeguarding of the interest of the breeders(Article 15(2) of UPOV).</t>
   </si>
   <si>
     <t>A plant breeder has exclusive rights to propagate materials of a protected variety. Authorization must be obtained from such a breeder for the production and reproduction, conditioning for propagation; offering for sale; selling or marketing; exporting; importing and stocking in relation to any of the mentioned purposes. Any authorization given by the plant breeder may be subject to conditions and limitations. However, such exclusive rights of a plant breeder cannot impede the doing of the following acts by a third party without authorization: Private and non-commercial purposes; Experimental purposes; and for the purpose of breeding any other variety, except it is essentially derived from an initially protected variety.</t>
   </si>
   <si>
+    <t>1. The PVP Act grants registered plant breeders Intellectual Property rights, thereby providing incentives for the development of new crop varieties and encouraging more farmers to engage in plant breeding.</t>
+  </si>
+  <si>
+    <t>3. Intellectual Property protection for plant breeders boosts investment in breeding and developing new plant varieties, as investors can now rely on a structured protection system.</t>
+  </si>
+  <si>
+    <t>4. The PVP Act will encourage non-resident or foreign plant breeder applications, enhancing access to foreign plant varieties by ensuring adequate protection of their varieties.</t>
+  </si>
+  <si>
+    <t>5. It is expected that the proper implementation of the provisions of the PVP will encourage research and development by breeders, thereby leading to higher agricultural productivity, and a boost in the agricultural sector would have a reverberating effect on Nigeria’s economy.</t>
+  </si>
+  <si>
+    <t>The passing of the Plant Protection Variety Act heralded numerous opportunities in the agricultural sector as plant breeders can commercialize their intellectual property by assigning or authorizing any activity in relation to any registered plant variety. This also opens investment opportunities for investors seeking to explore this aspect of agriculture and further creates job opportunities for people skilled in agriculture.</t>
+  </si>
+  <si>
     <t>To ensure breeders can benefit from the full scope of protection provided for under UPOV 1991 and to make the system future-proof in view of technical progress in plant breeding, the Basic Regulation and related regulations should be improved and clarified</t>
   </si>
   <si>
+    <t>Trigger exhaustion (Article 16 Basic Regulation). The wording of the trigger for exhaustion in Article 16 Basic Regulation (disposed of to others) deviates from the wording used in Article 16 UPOV 1991 (sold or otherwise marketed). The trigger for exhaustion should be clarified.</t>
+  </si>
+  <si>
+    <t>Enforcement. Holders of CPVR should have the same rights and remedies granted to other IP holders under the EU enforcement directive. To this end, the relation between the Basic Regulation and the EU enforcement directive should be clarified.</t>
+  </si>
+  <si>
     <t>Furthermore, cost-efficient enforcement measures should be available for breeders to act against unauthorized use of protected plant material and harvested material.</t>
   </si>
   <si>
-    <t>The trigger for exhaustion should be clarified.</t>
-  </si>
-  <si>
-    <t>The wording of the trigger for exhaustion in Article 16 Basic Regulation (disposed of to others) deviates from the wording used in Article 16 UPOV 1991 (sold or otherwise marketed).</t>
-  </si>
-  <si>
-    <t>The approach of the Court, that there is no unauthorized use of variety constituents if no authorization is required to propagate the material, limits the right to act against harvested material beyond the intentions of the UPOV legislator</t>
-  </si>
-  <si>
-    <t>Such implementing regulations have not yet been introduced.</t>
-  </si>
-  <si>
-    <t>When a sale has taken place is interpreted differently under national laws.</t>
-  </si>
-  <si>
-    <t>The definition of EDVs under Article 13(6), especially as regards the concepts of "predominantly derived" under Article 13(6)(a) and "conforms essentially to the initial variety in the expression of the characteristics …." under Article 13(6)(c), should be updated taking into account the guidance provided by the Explanatory Notes on Essentially Derived Varieties under the 1991 Act of the UPOV Convention</t>
-  </si>
-  <si>
-    <t>and further guidance should be provided on how to establish in practice if a variety is an EDV.</t>
-  </si>
-  <si>
-    <t>However, it is unclear who is entitled to enforce the related rights after the PVR expiry, and by which means.</t>
-  </si>
-  <si>
-    <t>However, the concept of reasonable compensation is extremely vague and lends itself to different interpretations at the national level in the case of enforcement.</t>
+    <t>Essentially Derived Varieties - EDVs (Article 13(6), Basic Regulation). The definition of EDVs under Article 13(6), especially as regards the concepts of "predominantly derived" under Article 13(6)(a) and "conforms essentially to the initial variety in the expression of the characteristics …." under Article 13(6)(c), should be updated taking into account the guidance provided by the Explanatory Notes on Essentially Derived Varieties under the 1991 Act of the UPOV Convention, adopted by the Council at its fifty-seventh ordinary session on 27 October 2023</t>
+  </si>
+  <si>
+    <t>Variety Denominations (Article 17, Basic Regulation). Under the terms of Article 17, the obligations relating to the use of the variety denominations contained in paragraphs 1 and 2 "shall apply even after the termination of the Community plant variety right". However, it is unclear who is entitled to enforce the related rights after the PVR expiry, and by which means.</t>
+  </si>
+  <si>
+    <t>Provisional protection (Article 95, Basic Regulation). Article 95 provides that "Prior to the grant of Community plant variety rights, the holder may require reasonable compensation from any person who has, in the time between publication of the application for a Community plant variety right and grant thereof, effected an act that he would be prohibited from performing subsequent thereto". However, the concept of reasonable compensation is extremely vague and lends itself to different interpretations at the national level in the case of enforcement.</t>
   </si>
   <si>
     <t>A harmonization of terminology with the UPOV Convention might be advisable as well as the inclusion of a specific article providing for basic definitions.</t>
   </si>
   <si>
-    <t>One of the most significant developments was the adoption of the International Union for the Protection of New Plant Varieties Convention (UPOV Convention) in 1961. The UPOV system of plant variety protection came into being with the adoption of the International Convention for the Protection of New Varieties of Plants by a Diplomatic Conference in Paris on December 2, 1961.</t>
-  </si>
-  <si>
-    <t>Nigeria was not a signatory to the International Union for the Protection of New Varieties of Plants (UPOV) Convention (Okonkwo, et al 2021) which to a large extent impeded the exploitation of such rights. It even deprived plant breeders in Nigeria access to high-quality new varieties of plant from foreign countries and also discourages foreign plant breeders since their new plant variety cannot be protected.</t>
-  </si>
-  <si>
-    <t>Meanwhile, the Trade-Related Aspects of Intellectual Property Rights Agreement (TRIPS), which Nigeria is a signatory to, recognizes and provides for the patentability of inventions in all fields of technology and specifically calls for the protection of plant varieties either by patent or by an effective sui generis system or by any combination thereof in line with the provisions of Article 27 of the TRIPS Agreement.</t>
-  </si>
-  <si>
-    <t>The Act aligns with international standards, such as those set by the International Union for the Protection of New Varieties of Plants (UPOV).</t>
-  </si>
-  <si>
-    <t>In some jurisdictions like the United State and Australia, the subject matter of protection covered by a Traditional IP and by a plant breeder’s right might be the same, namely a plant variety while in several other jurisdictions like European Union and India, the subject matter of protection is different, and, in general, plant varieties are excluded from patentability.</t>
-  </si>
-  <si>
-    <t>As far as the International Union for the Protection of New Plant Varieties Convention (UPOV) is concerned, a member is free to protect plant varieties, in addition to the grant of a breeder’s right, by the grant of other titles, particularly patents.</t>
-  </si>
-  <si>
-    <t>UPOV provides a sui generis system for the protection of plant varieties and the rights of plant breeders by ensuring that their effort and investments are adequately rewarded.</t>
-  </si>
-  <si>
-    <t>The Agreement on Trade-Related Aspects of Intellectual Property Rights (TRIPS) is administered by the World Trade Organization (WTO). According to the Agreement on Trade-Related Aspect of Intellectual Property Right (1994), the treaty covers a broader range of intellectual property rights, including patents, trademarks, copyrights, and trade secrets, in addition to PVP.</t>
-  </si>
-  <si>
-    <t>It allows flexibility for countries to determine their own criteria, which may include patent, or by an effective sui generis system (which could be UPOV standards) or by combination of both systems.</t>
-  </si>
-  <si>
-    <t>The Service also set a defined standards on agricultural quarantine procedure; ensuring compliance with International agreements, protocols, conventions and treaties on agricultural quarantine, including forestry, endangered species, plants variety and planting materials; monitoring the agricultural quarantine Regulations and standards; ensuring that agricultural quarantine projects are carried out in compliance with plant variety and public health regulations;</t>
-  </si>
-  <si>
-    <t>NASC is responsible for enforcing PVP rights in Nigeria. This includes monitoring the market for potential infringements and taking legal action against unauthorized use of protected varieties.</t>
-  </si>
-  <si>
-    <t>The Registrar should make effective guidelines for the effective implementation of the Act.</t>
-  </si>
-  <si>
-    <t>The National Agricultural Seeds Council (NASC) should be given adequate resources and trained personnel to effectively manage the PVP system. This will endeavour that NASC can handle applications, conduct examinations and enforce rights where necessary.</t>
-  </si>
-  <si>
-    <t>A well structured awareness program could be implemented at all level of the society to sensitize farmers, breeders, legislators and the general public on the intellectual property rights and plant variety rights and how they support innovation and food security.</t>
-  </si>
-  <si>
-    <t>Regular monitoring of the market for unauthorized use or infringement on plant varieties. Prompt action should be taken to enforce intellectual property rights through legal means such as sending cease-and-desist letters or pursuing litigation.</t>
-  </si>
-  <si>
-    <t>This passage directly states the policy objective of the Basic Regulation in terms of fostering innovation through balanced IP protection.</t>
-  </si>
-  <si>
-    <t>The snippet explicitly links CPVR protection to fostering innovation in plant breeding and investment in plant innovations.</t>
-  </si>
-  <si>
-    <t>The phrase "strong and balanced IP protection for all stakeholders" is relevant to how CPVR balances interests among affected parties.</t>
-  </si>
-  <si>
-    <t>This directly addresses the impact of CPVR-related interpretation on the plant breeding industry, which is relevant to innovation and competitiveness.</t>
-  </si>
-  <si>
-    <t>This passage discusses the scope of breeders' rights and legal limits on action against harvested material within the CPVR context.</t>
-  </si>
-  <si>
-    <t>The reference to a "chilling effect on the release of new plant varieties" directly concerns CPVR's effect on varietal innovation and market introduction.</t>
-  </si>
-  <si>
-    <t>This is directly about the legal rights and remedies available to CPVR holders and the adequacy of the enforcement regime.</t>
-  </si>
-  <si>
-    <t>This passage concerns the scope of legal protection and compensation under CPVR, fitting the rights/licensing balance dimension.</t>
-  </si>
-  <si>
-    <t>This passage directly states the aims of the PVP Act, matching legislative and policy objectives.</t>
-  </si>
-  <si>
-    <t>This describes institutional functions under the Act, including oversight and implementation of CPVR-like objectives.</t>
-  </si>
-  <si>
-    <t>This passage discusses implementation and oversight responsibilities connected to achieving the law’s policy goals.</t>
-  </si>
-  <si>
-    <t>This directly links PVR to encouraging innovation.</t>
-  </si>
-  <si>
-    <t>This passage clearly addresses innovation outcomes and market responsiveness.</t>
-  </si>
-  <si>
-    <t>This discusses effects on innovation opportunities and access to foreign varieties, relevant to innovation and market access.</t>
-  </si>
-  <si>
-    <t>This passage directly addresses breeding activity and incentives for varietal innovation.</t>
-  </si>
-  <si>
-    <t>Direct statement about impact on investment, crop variety development, productivity, and innovation.</t>
-  </si>
-  <si>
-    <t>This lists innovation and market-related benefits including new varieties, breeding participation, and investment.</t>
-  </si>
-  <si>
-    <t>This directly addresses market access, breeder applications, R&amp;D, productivity, and broader competitiveness effects.</t>
-  </si>
-  <si>
-    <t>This directly references farmers’ rights and benefit-sharing in the context of PVR.</t>
-  </si>
-  <si>
-    <t>This passage expressly addresses how rights and exceptions are balanced between breeders and farmers.</t>
-  </si>
-  <si>
-    <t>This is a clear statement of breeders’ exclusive rights together with exceptions for third parties, matching the balance-of-rights label.</t>
-  </si>
-  <si>
-    <t>This directly references UPOV 1991 and discusses how the Basic Regulation should align with that international framework.</t>
-  </si>
-  <si>
-    <t>This passage identifies enforcement as an operational issue affecting the practical implementation of CPVR protection.</t>
-  </si>
-  <si>
-    <t>In context, this follows the statement that Article 16 Basic Regulation deviates from Article 16 UPOV 1991, indicating interaction and alignment issues with the UPOV framework.</t>
-  </si>
-  <si>
-    <t>This explicitly compares the CPVR Basic Regulation with UPOV 1991, showing how the EU framework interacts with an international IP standard.</t>
-  </si>
-  <si>
-    <t>This describes a practical barrier in implementation arising from legal interpretation that affects how protection operates in practice.</t>
-  </si>
-  <si>
-    <t>This explicitly links interpretation of the Basic Regulation to the intentions of the UPOV legislator, showing interaction with the international IP framework.</t>
-  </si>
-  <si>
-    <t>This indicates an implementation gap in operationalizing Article 13(4), which is a barrier to effective CPVR functioning.</t>
-  </si>
-  <si>
-    <t>This highlights inconsistent interpretation across jurisdictions, which creates an implementation and compliance barrier.</t>
-  </si>
-  <si>
-    <t>This passage points to enforcement and legal clarity problems in implementation, indicating barriers in the operational framework.</t>
-  </si>
-  <si>
-    <t>This directly addresses how CPVR interacts with the broader EU IP enforcement framework.</t>
-  </si>
-  <si>
-    <t>This passage directly references the UPOV Convention and calls for updating EU rules in light of that international guidance.</t>
-  </si>
-  <si>
-    <t>This identifies a practical implementation barrier: lack of guidance on applying the EDV concept in practice.</t>
-  </si>
-  <si>
-    <t>This passage explicitly identifies uncertainty about enforcement, a core implementation barrier.</t>
-  </si>
-  <si>
-    <t>This directly describes vagueness and divergent national interpretation in enforcement, which is an implementation barrier.</t>
-  </si>
-  <si>
-    <t>This explicitly discusses harmonization of the Basic Regulation with the UPOV Convention, showing alignment with international IP standards.</t>
-  </si>
-  <si>
-    <t>This directly discusses problems arising in the implementation of PVR regulations.</t>
-  </si>
-  <si>
-    <t>This passage directly references UPOV as part of the international legal framework for plant variety protection.</t>
-  </si>
-  <si>
-    <t>This identifies a barrier to implementation and effective operation of plant breeders' rights in Nigeria.</t>
-  </si>
-  <si>
-    <t>This directly concerns TRIPS and how plant variety protection fits within international IP standards.</t>
-  </si>
-  <si>
-    <t>This explicitly states alignment of Nigeria's PVP Act with UPOV international standards.</t>
-  </si>
-  <si>
-    <t>This passage directly references the European Union and compares CPVR-related protection with other IP systems.</t>
-  </si>
-  <si>
-    <t>This explains UPOV's interaction with other IP titles, especially patents.</t>
-  </si>
-  <si>
-    <t>This clearly situates plant variety protection within the UPOV international framework.</t>
-  </si>
-  <si>
-    <t>This directly describes TRIPS and its relationship to plant variety protection within the broader IP framework.</t>
-  </si>
-  <si>
-    <t>This discusses how TRIPS interacts with UPOV and other IP protection options for plant varieties.</t>
-  </si>
-  <si>
-    <t>This concerns compliance and monitoring functions relevant to implementation capacity and enforcement of plant variety-related regulation.</t>
-  </si>
-  <si>
-    <t>This directly addresses enforcement and operational implementation of PVP rights.</t>
-  </si>
-  <si>
-    <t>This is a direct statement about implementation needs, indicating current implementation gaps.</t>
-  </si>
-  <si>
-    <t>This clearly identifies administrative capacity and enforcement as implementation barriers.</t>
-  </si>
-  <si>
-    <t>This indicates knowledge and awareness gaps as barriers to effective implementation.</t>
-  </si>
-  <si>
-    <t>This directly concerns monitoring and enforcement barriers in implementation of plant variety protection.</t>
+    <t>This passage explicitly states policy goals for the Basic Regulation, including fostering innovation and providing balanced protection.</t>
+  </si>
+  <si>
+    <t>The phrase "strong and balanced IP protection for all stakeholders" directly concerns balancing rights within the CPVR framework.</t>
+  </si>
+  <si>
+    <t>This passage directly links CPVR to innovation in plant breeding and investment in plant innovations.</t>
+  </si>
+  <si>
+    <t>This passage discusses a concrete impact of CPVR interpretation on the plant breeding industry, relevant to innovation and competitiveness.</t>
+  </si>
+  <si>
+    <t>This passage concerns the scope of breeders' rights and limitations on enforcing those rights under CPVR.</t>
+  </si>
+  <si>
+    <t>The reference to a "chilling effect on the release of new plant varieties" directly concerns innovation outcomes and market introduction.</t>
+  </si>
+  <si>
+    <t>This passage directly addresses the rights and remedies available to CPVR holders within the legal regime.</t>
+  </si>
+  <si>
+    <t>This concerns the EDV framework, which is closely tied to breeding activity, varietal development, and competitive innovation conditions.</t>
+  </si>
+  <si>
+    <t>This passage addresses provisional protection and compensation, which are core elements of the balance and enforceability of breeders' rights.</t>
+  </si>
+  <si>
+    <t>This directly concerns strengthening and clarifying legal protections for rights holders under CPVR.</t>
+  </si>
+  <si>
+    <t>This passage explicitly states the aims of the 2021 Act, directly matching legislative and policy objectives.</t>
+  </si>
+  <si>
+    <t>This describes institutional functions under the Act, including oversight and administration relevant to CPVR-type objectives and implementation.</t>
+  </si>
+  <si>
+    <t>This directly links plant variety rights to encouraging innovation.</t>
+  </si>
+  <si>
+    <t>This passage addresses both innovation outcomes and market aspects, including commercialization and incentives for developing new varieties.</t>
+  </si>
+  <si>
+    <t>This explicitly discusses farmers' rights and related balancing considerations within the PVR framework.</t>
+  </si>
+  <si>
+    <t>This passage links plant variety protection to innovation opportunities, access to foreign varieties, and breeder participation in the market.</t>
+  </si>
+  <si>
+    <t>This directly discusses breeding activity, incentives, and development of new varieties as innovation outcomes.</t>
+  </si>
+  <si>
+    <t>This states intended outcomes of the protection system, aligning with legislative and policy objectives.</t>
+  </si>
+  <si>
+    <t>This passage clearly addresses innovation and breeding investment impacts.</t>
+  </si>
+  <si>
+    <t>This passage directly concerns the balance between breeders' interests and seed-saving/farmer-related exceptions under the legal framework.</t>
+  </si>
+  <si>
+    <t>This passage clearly sets out breeders' exclusive rights alongside exceptions, showing the legal balance of rights and limitations.</t>
+  </si>
+  <si>
+    <t>This directly links the Act to incentives for developing new varieties and increasing breeding activity.</t>
+  </si>
+  <si>
+    <t>This explicitly addresses investment and development of new varieties, central to innovation and market effects.</t>
+  </si>
+  <si>
+    <t>This passage is about market access and cross-border breeder participation resulting from protection.</t>
+  </si>
+  <si>
+    <t>This directly concerns R&amp;D by breeders and broader economic and innovation-related effects.</t>
+  </si>
+  <si>
+    <t>This passage discusses commercialization, investment opportunities, and sectoral economic effects, all relevant to innovation and market impact.</t>
+  </si>
+  <si>
+    <t>Directly references alignment of the Basic Regulation with UPOV 1991, which fits the international IP framework label.</t>
+  </si>
+  <si>
+    <t>Explicit comparison between the CPVR Basic Regulation and UPOV 1991 shows interaction with an international IP standard.</t>
+  </si>
+  <si>
+    <t>Directly addresses how CPVR interacts with the EU IP enforcement framework.</t>
+  </si>
+  <si>
+    <t>This points to enforcement availability as an implementation issue affecting operational effectiveness of CPVR.</t>
+  </si>
+  <si>
+    <t>References the UPOV Convention as guidance for updating CPVR rules, fitting international IP alignment.</t>
+  </si>
+  <si>
+    <t>Highlights ambiguity in enforcement responsibility and means, which is a barrier to implementation.</t>
+  </si>
+  <si>
+    <t>Describes vagueness and divergent national interpretations in enforcement, a clear implementation barrier.</t>
+  </si>
+  <si>
+    <t>Explicitly calls for harmonization with the UPOV Convention, directly matching the international IP framework label.</t>
   </si>
   <si>
     <t>high</t>
@@ -529,21 +373,21 @@
     <t>medium</t>
   </si>
   <si>
-    <t>2026-07-09T10:17:51</t>
-  </si>
-  <si>
-    <t>2026-07-09T10:18:33</t>
+    <t>2026-07-09T13:57:31</t>
+  </si>
+  <si>
+    <t>2026-07-09T13:57:52</t>
   </si>
   <si>
     <t>4885febfda356ba8</t>
   </si>
   <si>
+    <t>db560946c5a52cd1</t>
+  </si>
+  <si>
     <t>0b0cda6ea456ae18</t>
   </si>
   <si>
-    <t>db560946c5a52cd1</t>
-  </si>
-  <si>
     <t>98bededa55afd02f</t>
   </si>
   <si>
@@ -556,22 +400,28 @@
     <t>e1e2caa33ec59a34</t>
   </si>
   <si>
+    <t>b8687c2ff2bbad02</t>
+  </si>
+  <si>
     <t>d975bc2534fd8579</t>
   </si>
   <si>
+    <t>1f3cc95cab3d84c6</t>
+  </si>
+  <si>
     <t>a15be750d6e0dcbd</t>
   </si>
   <si>
     <t>0a0c5adc352ca23e</t>
   </si>
   <si>
-    <t>08c353fa30611a7d</t>
-  </si>
-  <si>
     <t>bdc4a4c520252ed4</t>
   </si>
   <si>
-    <t>60d3fa74711ddeff</t>
+    <t>27957cdc75878627</t>
+  </si>
+  <si>
+    <t>aa25b5fbb0c63bc9</t>
   </si>
   <si>
     <t>62cf06fc8b087b12</t>
@@ -580,115 +430,55 @@
     <t>6d1276c2c269771d</t>
   </si>
   <si>
+    <t>a17bedcc73b313ea</t>
+  </si>
+  <si>
     <t>e25cc72fd7fe642d</t>
   </si>
   <si>
-    <t>efacde607b80658b</t>
-  </si>
-  <si>
-    <t>34dd33de5ac7629c</t>
-  </si>
-  <si>
-    <t>aa25b5fbb0c63bc9</t>
-  </si>
-  <si>
     <t>304d5e591be7ff7c</t>
   </si>
   <si>
     <t>93ef8e4a617899b8</t>
   </si>
   <si>
+    <t>c385ada89e152b2a</t>
+  </si>
+  <si>
+    <t>3bdd9b777dc8ddd5</t>
+  </si>
+  <si>
+    <t>b49ca5012f68706e</t>
+  </si>
+  <si>
+    <t>388aa1a7a82d4eb6</t>
+  </si>
+  <si>
+    <t>12ce00b83501e378</t>
+  </si>
+  <si>
     <t>78ca97f356748bd0</t>
   </si>
   <si>
+    <t>60826a686b8efa72</t>
+  </si>
+  <si>
+    <t>e5907597a32b23e5</t>
+  </si>
+  <si>
     <t>4aeae4ca4140550c</t>
   </si>
   <si>
-    <t>02320d07c59995ce</t>
-  </si>
-  <si>
-    <t>df15847f6244263d</t>
-  </si>
-  <si>
-    <t>afe8efcc899a9e05</t>
-  </si>
-  <si>
-    <t>a96fbd4aebaa92bf</t>
-  </si>
-  <si>
-    <t>b7875c4a24d1d482</t>
-  </si>
-  <si>
-    <t>42e2af84a8ff5a48</t>
-  </si>
-  <si>
-    <t>f6b1d1db08f0788f</t>
-  </si>
-  <si>
-    <t>e6fca2a027950d2f</t>
-  </si>
-  <si>
-    <t>0ff5e22b763e2912</t>
-  </si>
-  <si>
-    <t>5924a93992a5d60f</t>
-  </si>
-  <si>
-    <t>b40bb7c20515e487</t>
-  </si>
-  <si>
-    <t>2086a057450bb753</t>
+    <t>3992db46e85ec29d</t>
+  </si>
+  <si>
+    <t>fb665a95cd9a7236</t>
+  </si>
+  <si>
+    <t>6216360d628f61d6</t>
   </si>
   <si>
     <t>26bd3ff19bf9afcd</t>
-  </si>
-  <si>
-    <t>6227106da093eac2</t>
-  </si>
-  <si>
-    <t>114070558bc54c2a</t>
-  </si>
-  <si>
-    <t>7dda530f2181d6e8</t>
-  </si>
-  <si>
-    <t>c610e80e31bf16e2</t>
-  </si>
-  <si>
-    <t>f2a89608af05241d</t>
-  </si>
-  <si>
-    <t>b498bb48c3975e6e</t>
-  </si>
-  <si>
-    <t>d45207dcc9ebd233</t>
-  </si>
-  <si>
-    <t>af8a661d6f556646</t>
-  </si>
-  <si>
-    <t>741a032d201d2cb0</t>
-  </si>
-  <si>
-    <t>78836028559f5700</t>
-  </si>
-  <si>
-    <t>415634839bca9a42</t>
-  </si>
-  <si>
-    <t>c1401458417fd692</t>
-  </si>
-  <si>
-    <t>ce24005c1116597e</t>
-  </si>
-  <si>
-    <t>952879e5e9fdd222</t>
-  </si>
-  <si>
-    <t>7d12f70da1199b71</t>
-  </si>
-  <si>
-    <t>08fe648d8f55b74f</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1086,31 +876,31 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="H2" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I2" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J2" t="s">
-        <v>172</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1118,31 +908,31 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="H3" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I3" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J3" t="s">
-        <v>173</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1150,31 +940,31 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="H4" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="I4" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J4" t="s">
-        <v>174</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1182,31 +972,31 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="H5" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I5" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J5" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1214,31 +1004,31 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I6" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J6" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1246,31 +1036,31 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I7" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J7" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1278,31 +1068,31 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="F8">
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="H8" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I8" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J8" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1310,31 +1100,31 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s">
-        <v>168</v>
+        <v>118</v>
       </c>
       <c r="I9" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J9" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1342,31 +1132,31 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F10">
-        <v>454</v>
+        <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I10" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J10" t="s">
-        <v>180</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1374,31 +1164,31 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F11">
-        <v>458</v>
+        <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="H11" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I11" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J11" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1406,31 +1196,31 @@
         <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F12">
-        <v>457</v>
+        <v>4</v>
       </c>
       <c r="G12" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="H12" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I12" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J12" t="s">
-        <v>182</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1438,31 +1228,31 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="F13">
-        <v>451</v>
+        <v>7</v>
       </c>
       <c r="G13" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="H13" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I13" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J13" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1470,31 +1260,31 @@
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F14">
-        <v>451</v>
+        <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="H14" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I14" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J14" t="s">
-        <v>184</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1502,31 +1292,31 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" t="s">
         <v>63</v>
       </c>
-      <c r="C15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" t="s">
-        <v>81</v>
-      </c>
       <c r="F15">
-        <v>453</v>
+        <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="H15" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I15" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J15" t="s">
-        <v>185</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1534,31 +1324,31 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" t="s">
         <v>64</v>
       </c>
-      <c r="D16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" t="s">
-        <v>82</v>
-      </c>
       <c r="F16">
-        <v>454</v>
+        <v>2</v>
       </c>
       <c r="G16" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="H16" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I16" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J16" t="s">
-        <v>186</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1566,31 +1356,31 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="E17" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F17">
-        <v>454</v>
+        <v>3</v>
       </c>
       <c r="G17" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="H17" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I17" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J17" t="s">
-        <v>187</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1598,31 +1388,31 @@
         <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="E18" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="F18">
-        <v>460</v>
+        <v>4</v>
       </c>
       <c r="G18" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="H18" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I18" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J18" t="s">
-        <v>188</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1630,31 +1420,31 @@
         <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" t="s">
         <v>67</v>
       </c>
-      <c r="E19" t="s">
-        <v>85</v>
-      </c>
       <c r="F19">
-        <v>460</v>
+        <v>4</v>
       </c>
       <c r="G19" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="H19" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I19" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J19" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1662,31 +1452,31 @@
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F20">
-        <v>452</v>
+        <v>4</v>
       </c>
       <c r="G20" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="H20" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I20" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J20" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1694,31 +1484,31 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" t="s">
         <v>68</v>
       </c>
-      <c r="E21" t="s">
-        <v>87</v>
-      </c>
       <c r="F21">
-        <v>455</v>
+        <v>5</v>
       </c>
       <c r="G21" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="H21" t="s">
-        <v>168</v>
+        <v>118</v>
       </c>
       <c r="I21" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J21" t="s">
-        <v>191</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1726,31 +1516,31 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="E22" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="F22">
-        <v>458</v>
+        <v>8</v>
       </c>
       <c r="G22" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="H22" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I22" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J22" t="s">
-        <v>192</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1758,31 +1548,31 @@
         <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G23" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="H23" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I23" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="J23" t="s">
-        <v>193</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1790,31 +1580,31 @@
         <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E24" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="H24" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I24" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="J24" t="s">
-        <v>194</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1822,31 +1612,31 @@
         <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="E25" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G25" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="H25" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="I25" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="J25" t="s">
-        <v>195</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1854,31 +1644,31 @@
         <v>34</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="E26" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="H26" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I26" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="J26" t="s">
-        <v>196</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1886,31 +1676,31 @@
         <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E27" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="H27" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I27" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="J27" t="s">
-        <v>197</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1918,31 +1708,31 @@
         <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E28" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="H28" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I28" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="J28" t="s">
-        <v>198</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1950,31 +1740,31 @@
         <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="E29" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="H29" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I29" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="J29" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1982,31 +1772,31 @@
         <v>38</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="E30" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="H30" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I30" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="J30" t="s">
-        <v>200</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2014,31 +1804,31 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="H31" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I31" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="J31" t="s">
-        <v>201</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -2046,31 +1836,31 @@
         <v>40</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E32" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="H32" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I32" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="J32" t="s">
-        <v>202</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -2078,31 +1868,31 @@
         <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E33" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="H33" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I33" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="J33" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -2110,31 +1900,31 @@
         <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D34" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E34" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="H34" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I34" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="J34" t="s">
-        <v>204</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2142,607 +1932,31 @@
         <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D35" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="E35" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="H35" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="I35" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="J35" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36" t="s">
-        <v>65</v>
-      </c>
-      <c r="D36" t="s">
-        <v>70</v>
-      </c>
-      <c r="E36" t="s">
-        <v>99</v>
-      </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-      <c r="G36" t="s">
-        <v>150</v>
-      </c>
-      <c r="H36" t="s">
-        <v>168</v>
-      </c>
-      <c r="I36" t="s">
-        <v>171</v>
-      </c>
-      <c r="J36" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" t="s">
-        <v>62</v>
-      </c>
-      <c r="C37" t="s">
-        <v>65</v>
-      </c>
-      <c r="D37" t="s">
-        <v>69</v>
-      </c>
-      <c r="E37" t="s">
-        <v>100</v>
-      </c>
-      <c r="F37">
-        <v>1</v>
-      </c>
-      <c r="G37" t="s">
-        <v>151</v>
-      </c>
-      <c r="H37" t="s">
-        <v>168</v>
-      </c>
-      <c r="I37" t="s">
-        <v>171</v>
-      </c>
-      <c r="J37" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" t="s">
-        <v>63</v>
-      </c>
-      <c r="C38" t="s">
-        <v>65</v>
-      </c>
-      <c r="D38" t="s">
-        <v>70</v>
-      </c>
-      <c r="E38" t="s">
-        <v>86</v>
-      </c>
-      <c r="F38">
-        <v>452</v>
-      </c>
-      <c r="G38" t="s">
-        <v>152</v>
-      </c>
-      <c r="H38" t="s">
-        <v>169</v>
-      </c>
-      <c r="I38" t="s">
-        <v>171</v>
-      </c>
-      <c r="J38" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" t="s">
-        <v>63</v>
-      </c>
-      <c r="C39" t="s">
-        <v>65</v>
-      </c>
-      <c r="D39" t="s">
-        <v>69</v>
-      </c>
-      <c r="E39" t="s">
-        <v>101</v>
-      </c>
-      <c r="F39">
-        <v>453</v>
-      </c>
-      <c r="G39" t="s">
-        <v>153</v>
-      </c>
-      <c r="H39" t="s">
-        <v>168</v>
-      </c>
-      <c r="I39" t="s">
-        <v>171</v>
-      </c>
-      <c r="J39" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" t="s">
-        <v>63</v>
-      </c>
-      <c r="C40" t="s">
-        <v>65</v>
-      </c>
-      <c r="D40" t="s">
-        <v>70</v>
-      </c>
-      <c r="E40" t="s">
-        <v>102</v>
-      </c>
-      <c r="F40">
-        <v>453</v>
-      </c>
-      <c r="G40" t="s">
         <v>154</v>
-      </c>
-      <c r="H40" t="s">
-        <v>168</v>
-      </c>
-      <c r="I40" t="s">
-        <v>171</v>
-      </c>
-      <c r="J40" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" t="s">
-        <v>63</v>
-      </c>
-      <c r="C41" t="s">
-        <v>65</v>
-      </c>
-      <c r="D41" t="s">
-        <v>69</v>
-      </c>
-      <c r="E41" t="s">
-        <v>103</v>
-      </c>
-      <c r="F41">
-        <v>453</v>
-      </c>
-      <c r="G41" t="s">
-        <v>155</v>
-      </c>
-      <c r="H41" t="s">
-        <v>168</v>
-      </c>
-      <c r="I41" t="s">
-        <v>171</v>
-      </c>
-      <c r="J41" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" t="s">
-        <v>63</v>
-      </c>
-      <c r="C42" t="s">
-        <v>65</v>
-      </c>
-      <c r="D42" t="s">
-        <v>69</v>
-      </c>
-      <c r="E42" t="s">
-        <v>104</v>
-      </c>
-      <c r="F42">
-        <v>454</v>
-      </c>
-      <c r="G42" t="s">
-        <v>156</v>
-      </c>
-      <c r="H42" t="s">
-        <v>168</v>
-      </c>
-      <c r="I42" t="s">
-        <v>171</v>
-      </c>
-      <c r="J42" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" t="s">
-        <v>65</v>
-      </c>
-      <c r="D43" t="s">
-        <v>69</v>
-      </c>
-      <c r="E43" t="s">
-        <v>105</v>
-      </c>
-      <c r="F43">
-        <v>454</v>
-      </c>
-      <c r="G43" t="s">
-        <v>157</v>
-      </c>
-      <c r="H43" t="s">
-        <v>168</v>
-      </c>
-      <c r="I43" t="s">
-        <v>171</v>
-      </c>
-      <c r="J43" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" t="s">
-        <v>65</v>
-      </c>
-      <c r="D44" t="s">
-        <v>69</v>
-      </c>
-      <c r="E44" t="s">
-        <v>106</v>
-      </c>
-      <c r="F44">
-        <v>455</v>
-      </c>
-      <c r="G44" t="s">
-        <v>158</v>
-      </c>
-      <c r="H44" t="s">
-        <v>168</v>
-      </c>
-      <c r="I44" t="s">
-        <v>171</v>
-      </c>
-      <c r="J44" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" t="s">
-        <v>53</v>
-      </c>
-      <c r="B45" t="s">
-        <v>63</v>
-      </c>
-      <c r="C45" t="s">
-        <v>65</v>
-      </c>
-      <c r="D45" t="s">
-        <v>69</v>
-      </c>
-      <c r="E45" t="s">
-        <v>107</v>
-      </c>
-      <c r="F45">
-        <v>455</v>
-      </c>
-      <c r="G45" t="s">
-        <v>159</v>
-      </c>
-      <c r="H45" t="s">
-        <v>168</v>
-      </c>
-      <c r="I45" t="s">
-        <v>171</v>
-      </c>
-      <c r="J45" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" t="s">
-        <v>54</v>
-      </c>
-      <c r="B46" t="s">
-        <v>63</v>
-      </c>
-      <c r="C46" t="s">
-        <v>65</v>
-      </c>
-      <c r="D46" t="s">
-        <v>69</v>
-      </c>
-      <c r="E46" t="s">
-        <v>108</v>
-      </c>
-      <c r="F46">
-        <v>455</v>
-      </c>
-      <c r="G46" t="s">
-        <v>160</v>
-      </c>
-      <c r="H46" t="s">
-        <v>168</v>
-      </c>
-      <c r="I46" t="s">
-        <v>171</v>
-      </c>
-      <c r="J46" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" t="s">
-        <v>55</v>
-      </c>
-      <c r="B47" t="s">
-        <v>63</v>
-      </c>
-      <c r="C47" t="s">
-        <v>65</v>
-      </c>
-      <c r="D47" t="s">
-        <v>69</v>
-      </c>
-      <c r="E47" t="s">
-        <v>109</v>
-      </c>
-      <c r="F47">
-        <v>456</v>
-      </c>
-      <c r="G47" t="s">
-        <v>161</v>
-      </c>
-      <c r="H47" t="s">
-        <v>168</v>
-      </c>
-      <c r="I47" t="s">
-        <v>171</v>
-      </c>
-      <c r="J47" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" t="s">
-        <v>56</v>
-      </c>
-      <c r="B48" t="s">
-        <v>63</v>
-      </c>
-      <c r="C48" t="s">
-        <v>65</v>
-      </c>
-      <c r="D48" t="s">
-        <v>70</v>
-      </c>
-      <c r="E48" t="s">
-        <v>110</v>
-      </c>
-      <c r="F48">
-        <v>457</v>
-      </c>
-      <c r="G48" t="s">
-        <v>162</v>
-      </c>
-      <c r="H48" t="s">
-        <v>169</v>
-      </c>
-      <c r="I48" t="s">
-        <v>171</v>
-      </c>
-      <c r="J48" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
-      <c r="A49" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" t="s">
-        <v>63</v>
-      </c>
-      <c r="C49" t="s">
-        <v>65</v>
-      </c>
-      <c r="D49" t="s">
-        <v>70</v>
-      </c>
-      <c r="E49" t="s">
-        <v>111</v>
-      </c>
-      <c r="F49">
-        <v>457</v>
-      </c>
-      <c r="G49" t="s">
-        <v>163</v>
-      </c>
-      <c r="H49" t="s">
-        <v>168</v>
-      </c>
-      <c r="I49" t="s">
-        <v>171</v>
-      </c>
-      <c r="J49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" t="s">
-        <v>58</v>
-      </c>
-      <c r="B50" t="s">
-        <v>63</v>
-      </c>
-      <c r="C50" t="s">
-        <v>65</v>
-      </c>
-      <c r="D50" t="s">
-        <v>70</v>
-      </c>
-      <c r="E50" t="s">
-        <v>112</v>
-      </c>
-      <c r="F50">
-        <v>460</v>
-      </c>
-      <c r="G50" t="s">
-        <v>164</v>
-      </c>
-      <c r="H50" t="s">
-        <v>168</v>
-      </c>
-      <c r="I50" t="s">
-        <v>171</v>
-      </c>
-      <c r="J50" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" t="s">
-        <v>59</v>
-      </c>
-      <c r="B51" t="s">
-        <v>63</v>
-      </c>
-      <c r="C51" t="s">
-        <v>65</v>
-      </c>
-      <c r="D51" t="s">
-        <v>70</v>
-      </c>
-      <c r="E51" t="s">
-        <v>113</v>
-      </c>
-      <c r="F51">
-        <v>460</v>
-      </c>
-      <c r="G51" t="s">
-        <v>165</v>
-      </c>
-      <c r="H51" t="s">
-        <v>168</v>
-      </c>
-      <c r="I51" t="s">
-        <v>171</v>
-      </c>
-      <c r="J51" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="A52" t="s">
-        <v>60</v>
-      </c>
-      <c r="B52" t="s">
-        <v>63</v>
-      </c>
-      <c r="C52" t="s">
-        <v>65</v>
-      </c>
-      <c r="D52" t="s">
-        <v>70</v>
-      </c>
-      <c r="E52" t="s">
-        <v>114</v>
-      </c>
-      <c r="F52">
-        <v>461</v>
-      </c>
-      <c r="G52" t="s">
-        <v>166</v>
-      </c>
-      <c r="H52" t="s">
-        <v>168</v>
-      </c>
-      <c r="I52" t="s">
-        <v>171</v>
-      </c>
-      <c r="J52" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="A53" t="s">
-        <v>61</v>
-      </c>
-      <c r="B53" t="s">
-        <v>63</v>
-      </c>
-      <c r="C53" t="s">
-        <v>65</v>
-      </c>
-      <c r="D53" t="s">
-        <v>70</v>
-      </c>
-      <c r="E53" t="s">
-        <v>115</v>
-      </c>
-      <c r="F53">
-        <v>461</v>
-      </c>
-      <c r="G53" t="s">
-        <v>167</v>
-      </c>
-      <c r="H53" t="s">
-        <v>168</v>
-      </c>
-      <c r="I53" t="s">
-        <v>171</v>
-      </c>
-      <c r="J53" t="s">
-        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/coded_findings.xlsx
+++ b/outputs/coded_findings.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecorys-my.sharepoint.com/personal/vincent_frippiat_ecorys_com/Documents/Documents/PnR/Sustainable Agriculture/PDF Processing Eleonora/lit_review/outputs/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_04E1C3EE2EA30B2A452D4CA58D6E0B5B78785B04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -484,8 +490,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -548,13 +554,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -592,7 +606,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -626,6 +640,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -660,9 +675,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -835,11 +851,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -871,7 +887,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -903,7 +919,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -935,7 +951,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -967,7 +983,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -999,7 +1015,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1031,7 +1047,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1063,7 +1079,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1095,7 +1111,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1127,7 +1143,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1159,7 +1175,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1191,7 +1207,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1223,7 +1239,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1255,7 +1271,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1287,7 +1303,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1319,7 +1335,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1351,7 +1367,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1383,7 +1399,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -1415,7 +1431,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -1447,7 +1463,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -1479,7 +1495,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -1511,7 +1527,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -1543,7 +1559,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -1575,7 +1591,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -1607,7 +1623,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -1639,7 +1655,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -1671,7 +1687,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -1703,7 +1719,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -1735,7 +1751,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -1767,7 +1783,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -1799,7 +1815,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -1831,7 +1847,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -1863,7 +1879,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -1895,7 +1911,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -1927,7 +1943,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>43</v>
       </c>

--- a/outputs/coded_findings.xlsx
+++ b/outputs/coded_findings.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecorys-my.sharepoint.com/personal/vincent_frippiat_ecorys_com/Documents/Documents/PnR/Sustainable Agriculture/PDF Processing Eleonora/lit_review/outputs/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_04E1C3EE2EA30B2A452D4CA58D6E0B5B78785B04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="145">
   <si>
     <t>snippet_id</t>
   </si>
@@ -52,36 +46,6 @@
     <t>finding_hash</t>
   </si>
   <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_EFFECTIVENESS__0001</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_EFFECTIVENESS__0002</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_EFFECTIVENESS__0003</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_EFFECTIVENESS__0004</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_EFFECTIVENESS__0005</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_EFFECTIVENESS__0006</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_EFFECTIVENESS__0007</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_EFFECTIVENESS__0008</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_EFFECTIVENESS__0009</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_EFFECTIVENESS__0010</t>
-  </si>
-  <si>
     <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_EFFECTIVENESS__0001</t>
   </si>
   <si>
@@ -130,31 +94,49 @@
     <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_EFFECTIVENESS__0016</t>
   </si>
   <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0001</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0002</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0003</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0004</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0005</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0006</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0007</t>
-  </si>
-  <si>
-    <t>AIPPI_position_paper_on_the_CPVO_CPVR_Ca__CPVR_LEGAL__0008</t>
-  </si>
-  <si>
-    <t>AIPPI position paper on the CPVO.CPVR Call for Evidence March 2025.pdf</t>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_EFFECTIVENESS__0017</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_EFFECTIVENESS__0018</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0001</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0002</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0003</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0004</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0005</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0006</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0007</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0008</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0009</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0010</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0011</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0012</t>
+  </si>
+  <si>
+    <t>Adelaiye__V_O___2024__Plant_Variety_Righ__CPVR_LEGAL__0013</t>
   </si>
   <si>
     <t>Adelaiye, V.O. (2024) Plant Variety Right and Intellectual Property Law in Nigeria A Review.pdf</t>
@@ -169,55 +151,43 @@
     <t>OBJECTIVES</t>
   </si>
   <si>
+    <t>INNOVATION_MARKET</t>
+  </si>
+  <si>
     <t>RIGHTS_BALANCE</t>
   </si>
   <si>
-    <t>INNOVATION_MARKET</t>
-  </si>
-  <si>
     <t>IP_FRAMEWORK</t>
   </si>
   <si>
     <t>IMPLEMENTATION_BARRIERS</t>
   </si>
   <si>
-    <t>Plant variety right protection is the most relevant form of intellectual property protection for plant varieties. To foster innovation in the field of plant breeding, the Basic Regulation should provide for strong and balanced IP protection for all stakeholders that invest in plant innovations, irrespective of how new plant varieties are developed, either by way of classic breeding and/or the use of new breeding technologies.</t>
-  </si>
-  <si>
-    <t>The interpretation given by the CJEU in its judgement of 19 December 2019 in the Nadorcott case (C-176 / 18) on unauthorized use of variety constituents in the context of provisional protection has a negative impact on the plant breeding industry in practice, especially in the field of ornamentals and fruit species.</t>
-  </si>
-  <si>
-    <t>The approach of the Court, that there is no unauthorized use of variety constituents if no authorization is required to propagate the material, limits the right to act against harvested material beyond the intentions of the UPOV legislator and has a chilling effect on the release of new plant varieties before the expiry of the provisional protection.</t>
-  </si>
-  <si>
-    <t>Holders of CPVR should have the same rights and remedies granted to other IP holders under the EU enforcement directive. To this end, the relation between the Basic Regulation and the EU enforcement directive should be clarified.</t>
-  </si>
-  <si>
-    <t>The definition of EDVs under Article 13(6), especially as regards the concepts of "predominantly derived" under Article 13(6)(a) and "conforms essentially to the initial variety in the expression of the characteristics …." under Article 13(6)(c), should be updated taking into account the guidance provided by the Explanatory Notes on Essentially Derived Varieties under the 1991 Act of the UPOV Convention, adopted by the Council at its fifty-seventh ordinary session on 27 October 2023 and further guidance should be provided on how to establish in practice if a variety is an EDV.</t>
-  </si>
-  <si>
-    <t>Article 95 provides that "Prior to the grant of Community plant variety rights, the holder may require reasonable compensation from any person who has, in the time between publication of the application for a Community plant variety right and grant thereof, effected an act that he would be prohibited from performing subsequent thereto". However, the concept of reasonable compensation is extremely vague and lends itself to different interpretations at the national level in the case of enforcement.</t>
-  </si>
-  <si>
-    <t>For provisional protection to be effective, it would be advisable to delineate the concept of "reasonable compensation" in its conceivable amount so as to provide reliable reference elements for (prospective) rights holders to prevent acts potentially adversely affecting their PVRs, where subsequently granted.</t>
-  </si>
-  <si>
-    <t>In Nigeria, the relationship between Plant Variety Protection (PVP) and traditional intellectual property rights (IPR) is evolving, especially with the recent enactment of the Plant Variety Protection Act in 2021 which aimed at: promoting increased staple crop productivity for smallholder farmers in Nigeria and encourage investment in plant breeding and crop variety development; promoting increased mutual accountability in the seed sector; and protecting new varieties of plants.</t>
+    <t>the recent enactment of the Plant Variety Protection Act in 2021 which aimed at: promoting increased staple crop productivity for smallholder farmers in Nigeria and encourage investment in plant breeding and crop variety development; promoting increased mutual accountability in the seed sector; and protecting new varieties of plants.</t>
   </si>
   <si>
     <t>Section 5 of the Plant Variety Protection Act 2021 established a Plant Variety Protection Office in Nigeria to grant breeders rights, facilitate transfer and licensing of plant breeder’s rights, collaborate with local and international bodies whose functions relate to plant breeding and perform other necessary functions.</t>
   </si>
   <si>
-    <t>PVR regimes, which are a part of larger IP regimes, seek to achieve a careful equilibrium between encouraging innovation and guaranteeing the preservation of genetic variation.</t>
-  </si>
-  <si>
-    <t>Fundamentally, PVR gives breeders an exclusive authority to commercially propagate, market, and distribute their registered plant varieties. PVR regimes encourage the generation of new varieties that are suited to address changing market needs and environmental issues by providing incentives for research and development.</t>
-  </si>
-  <si>
-    <t>However, the implementation of PVR regulations raises complex ethical, legal and socioeconomic considerations. Concerns about farmers' rights, benefit-sharing arrangements, and access to genetic resources are major problems that highlight the necessity of a comprehensive and inclusive approach to plant variety sustainability.</t>
-  </si>
-  <si>
-    <t>Nigeria was not a signatory to the International Union for the Protection of New Varieties of Plants (UPOV) Convention (Okonkwo, et al 2021) which to a large extent impeded the exploitation of such rights. It even deprived plant breeders in Nigeria access to high-quality new varieties of plant from foreign countries and also discourages foreign plant breeders since their new plant variety cannot be protected. These lacunae had surreptitiously deprived Nigeria of innovative opportunities in this sector unlike her counterparts – Uganda (Uganda Plant Variety Act2014), Kenya (Seed and Plant Varieties Act 2012) and South Africa (Plant Breeder’s Rights Act 1976).</t>
+    <t>This includes monitoring the market for potential infringements and taking legal action against unauthorized use of protected varieties. Breeders can also seek legal remedies through the courts if their rights are violated</t>
+  </si>
+  <si>
+    <t>The PVP Act grants registered plant breeders Intellectual Property rights, thereby providing incentives for the development of new crop varieties and encouraging more farmers to engage in plant breeding.</t>
+  </si>
+  <si>
+    <t>It is expected that the proper implementation of the provisions of the PVP will encourage research and development by breeders, thereby leading to higher agricultural productivity, and a boost in the agricultural sector would have a reverberating effect on Nigeria’s economy.</t>
+  </si>
+  <si>
+    <t>The Registrar should make effective guidelines for the effective implementation of the Act.</t>
+  </si>
+  <si>
+    <t>This will endeavour that NASC can handle applications, conduct examinations and enforce rights where necessary.</t>
+  </si>
+  <si>
+    <t>PVR regimes encourage the generation of new varieties that are suited to address changing market needs and environmental issues by providing incentives for research and development.</t>
+  </si>
+  <si>
+    <t>Nigeria was not a signatory to the International Union for the Protection of New Varieties of Plants (UPOV) Convention (Okonkwo, et al 2021) which to a large extent impeded the exploitation of such rights. It even deprived plant breeders in Nigeria access to high-quality new varieties of plant from foreign countries and also discourages foreign plant breeders since their new plant variety cannot be protected.</t>
   </si>
   <si>
     <t>Comparing plant variety systems in other countries, it's evident that regulatory frameworks and breeder rights are crucial for fully exploiting breeding activities, as new plant varieties require significant investment in skills, labor, resources, and time. Intellectual property (IP) protection is, therefore, necessary to serve as an incentive to plant breeders, for the development of new varieties to contribute to sustainable progress in agriculture.</t>
@@ -226,151 +196,154 @@
     <t>This system encourages investment in plant breeding and crop variety development, aiming to boost agricultural productivity and innovation.</t>
   </si>
   <si>
+    <t>Intellectual Property protection for plant breeders boosts investment in breeding and developing new plant varieties, as investors can now rely on a structured protection system.</t>
+  </si>
+  <si>
+    <t>The PVP Act will encourage non-resident or foreign plant breeder applications, enhancing access to foreign plant varieties by ensuring adequate protection of their varieties.</t>
+  </si>
+  <si>
+    <t>Concerns about farmers' rights, benefit-sharing arrangements, and access to genetic resources are major problems that highlight the necessity of a comprehensive and inclusive approach to plant variety sustainability.</t>
+  </si>
+  <si>
     <t>Breeders have the right to save seeds for the future use to the exclusion of other farmers within a reasonable limit and subject to the safeguarding of the interest of the breeders(Article 15(2) of UPOV).</t>
   </si>
   <si>
-    <t>A plant breeder has exclusive rights to propagate materials of a protected variety. Authorization must be obtained from such a breeder for the production and reproduction, conditioning for propagation; offering for sale; selling or marketing; exporting; importing and stocking in relation to any of the mentioned purposes. Any authorization given by the plant breeder may be subject to conditions and limitations. However, such exclusive rights of a plant breeder cannot impede the doing of the following acts by a third party without authorization: Private and non-commercial purposes; Experimental purposes; and for the purpose of breeding any other variety, except it is essentially derived from an initially protected variety.</t>
-  </si>
-  <si>
-    <t>1. The PVP Act grants registered plant breeders Intellectual Property rights, thereby providing incentives for the development of new crop varieties and encouraging more farmers to engage in plant breeding.</t>
-  </si>
-  <si>
-    <t>3. Intellectual Property protection for plant breeders boosts investment in breeding and developing new plant varieties, as investors can now rely on a structured protection system.</t>
-  </si>
-  <si>
-    <t>4. The PVP Act will encourage non-resident or foreign plant breeder applications, enhancing access to foreign plant varieties by ensuring adequate protection of their varieties.</t>
-  </si>
-  <si>
-    <t>5. It is expected that the proper implementation of the provisions of the PVP will encourage research and development by breeders, thereby leading to higher agricultural productivity, and a boost in the agricultural sector would have a reverberating effect on Nigeria’s economy.</t>
-  </si>
-  <si>
-    <t>The passing of the Plant Protection Variety Act heralded numerous opportunities in the agricultural sector as plant breeders can commercialize their intellectual property by assigning or authorizing any activity in relation to any registered plant variety. This also opens investment opportunities for investors seeking to explore this aspect of agriculture and further creates job opportunities for people skilled in agriculture.</t>
-  </si>
-  <si>
-    <t>To ensure breeders can benefit from the full scope of protection provided for under UPOV 1991 and to make the system future-proof in view of technical progress in plant breeding, the Basic Regulation and related regulations should be improved and clarified</t>
-  </si>
-  <si>
-    <t>Trigger exhaustion (Article 16 Basic Regulation). The wording of the trigger for exhaustion in Article 16 Basic Regulation (disposed of to others) deviates from the wording used in Article 16 UPOV 1991 (sold or otherwise marketed). The trigger for exhaustion should be clarified.</t>
-  </si>
-  <si>
-    <t>Enforcement. Holders of CPVR should have the same rights and remedies granted to other IP holders under the EU enforcement directive. To this end, the relation between the Basic Regulation and the EU enforcement directive should be clarified.</t>
-  </si>
-  <si>
-    <t>Furthermore, cost-efficient enforcement measures should be available for breeders to act against unauthorized use of protected plant material and harvested material.</t>
-  </si>
-  <si>
-    <t>Essentially Derived Varieties - EDVs (Article 13(6), Basic Regulation). The definition of EDVs under Article 13(6), especially as regards the concepts of "predominantly derived" under Article 13(6)(a) and "conforms essentially to the initial variety in the expression of the characteristics …." under Article 13(6)(c), should be updated taking into account the guidance provided by the Explanatory Notes on Essentially Derived Varieties under the 1991 Act of the UPOV Convention, adopted by the Council at its fifty-seventh ordinary session on 27 October 2023</t>
-  </si>
-  <si>
-    <t>Variety Denominations (Article 17, Basic Regulation). Under the terms of Article 17, the obligations relating to the use of the variety denominations contained in paragraphs 1 and 2 "shall apply even after the termination of the Community plant variety right". However, it is unclear who is entitled to enforce the related rights after the PVR expiry, and by which means.</t>
-  </si>
-  <si>
-    <t>Provisional protection (Article 95, Basic Regulation). Article 95 provides that "Prior to the grant of Community plant variety rights, the holder may require reasonable compensation from any person who has, in the time between publication of the application for a Community plant variety right and grant thereof, effected an act that he would be prohibited from performing subsequent thereto". However, the concept of reasonable compensation is extremely vague and lends itself to different interpretations at the national level in the case of enforcement.</t>
-  </si>
-  <si>
-    <t>A harmonization of terminology with the UPOV Convention might be advisable as well as the inclusion of a specific article providing for basic definitions.</t>
-  </si>
-  <si>
-    <t>This passage explicitly states policy goals for the Basic Regulation, including fostering innovation and providing balanced protection.</t>
-  </si>
-  <si>
-    <t>The phrase "strong and balanced IP protection for all stakeholders" directly concerns balancing rights within the CPVR framework.</t>
-  </si>
-  <si>
-    <t>This passage directly links CPVR to innovation in plant breeding and investment in plant innovations.</t>
-  </si>
-  <si>
-    <t>This passage discusses a concrete impact of CPVR interpretation on the plant breeding industry, relevant to innovation and competitiveness.</t>
-  </si>
-  <si>
-    <t>This passage concerns the scope of breeders' rights and limitations on enforcing those rights under CPVR.</t>
-  </si>
-  <si>
-    <t>The reference to a "chilling effect on the release of new plant varieties" directly concerns innovation outcomes and market introduction.</t>
-  </si>
-  <si>
-    <t>This passage directly addresses the rights and remedies available to CPVR holders within the legal regime.</t>
-  </si>
-  <si>
-    <t>This concerns the EDV framework, which is closely tied to breeding activity, varietal development, and competitive innovation conditions.</t>
-  </si>
-  <si>
-    <t>This passage addresses provisional protection and compensation, which are core elements of the balance and enforceability of breeders' rights.</t>
-  </si>
-  <si>
-    <t>This directly concerns strengthening and clarifying legal protections for rights holders under CPVR.</t>
-  </si>
-  <si>
-    <t>This passage explicitly states the aims of the 2021 Act, directly matching legislative and policy objectives.</t>
-  </si>
-  <si>
-    <t>This describes institutional functions under the Act, including oversight and administration relevant to CPVR-type objectives and implementation.</t>
-  </si>
-  <si>
-    <t>This directly links plant variety rights to encouraging innovation.</t>
-  </si>
-  <si>
-    <t>This passage addresses both innovation outcomes and market aspects, including commercialization and incentives for developing new varieties.</t>
-  </si>
-  <si>
-    <t>This explicitly discusses farmers' rights and related balancing considerations within the PVR framework.</t>
-  </si>
-  <si>
-    <t>This passage links plant variety protection to innovation opportunities, access to foreign varieties, and breeder participation in the market.</t>
-  </si>
-  <si>
-    <t>This directly discusses breeding activity, incentives, and development of new varieties as innovation outcomes.</t>
-  </si>
-  <si>
-    <t>This states intended outcomes of the protection system, aligning with legislative and policy objectives.</t>
-  </si>
-  <si>
-    <t>This passage clearly addresses innovation and breeding investment impacts.</t>
-  </si>
-  <si>
-    <t>This passage directly concerns the balance between breeders' interests and seed-saving/farmer-related exceptions under the legal framework.</t>
-  </si>
-  <si>
-    <t>This passage clearly sets out breeders' exclusive rights alongside exceptions, showing the legal balance of rights and limitations.</t>
-  </si>
-  <si>
-    <t>This directly links the Act to incentives for developing new varieties and increasing breeding activity.</t>
-  </si>
-  <si>
-    <t>This explicitly addresses investment and development of new varieties, central to innovation and market effects.</t>
-  </si>
-  <si>
-    <t>This passage is about market access and cross-border breeder participation resulting from protection.</t>
-  </si>
-  <si>
-    <t>This directly concerns R&amp;D by breeders and broader economic and innovation-related effects.</t>
-  </si>
-  <si>
-    <t>This passage discusses commercialization, investment opportunities, and sectoral economic effects, all relevant to innovation and market impact.</t>
-  </si>
-  <si>
-    <t>Directly references alignment of the Basic Regulation with UPOV 1991, which fits the international IP framework label.</t>
-  </si>
-  <si>
-    <t>Explicit comparison between the CPVR Basic Regulation and UPOV 1991 shows interaction with an international IP standard.</t>
-  </si>
-  <si>
-    <t>Directly addresses how CPVR interacts with the EU IP enforcement framework.</t>
-  </si>
-  <si>
-    <t>This points to enforcement availability as an implementation issue affecting operational effectiveness of CPVR.</t>
-  </si>
-  <si>
-    <t>References the UPOV Convention as guidance for updating CPVR rules, fitting international IP alignment.</t>
-  </si>
-  <si>
-    <t>Highlights ambiguity in enforcement responsibility and means, which is a barrier to implementation.</t>
-  </si>
-  <si>
-    <t>Describes vagueness and divergent national interpretations in enforcement, a clear implementation barrier.</t>
-  </si>
-  <si>
-    <t>Explicitly calls for harmonization with the UPOV Convention, directly matching the international IP framework label.</t>
+    <t>Any authorization given by the plant breeder may be subject to conditions and limitations. However, such exclusive rights of a plant breeder cannot impede the doing of the following acts by a third party without authorization: Private and non-commercial purposes; Experimental purposes; and for the purpose of breeding any other variety, except it is essentially derived from an initially protected variety.</t>
+  </si>
+  <si>
+    <t>The Plant Variety Protection Act 2021 established a Plant Variety Protection Office in Nigeria to grant breeders rights, facilitate transfer and licensing of plant breeder’s rights</t>
+  </si>
+  <si>
+    <t>The Plant Variety Protection Act 2021 makes provision for the holder of a plant breeder’s right to assign or authorize any activity in relation to a registered plant variety.</t>
+  </si>
+  <si>
+    <t>Recognizing the importance of Plant Variety Right and Intellectual Property Law in Nigeria: A Review harmonizing plant variety protection laws to facilitate international trade in plant germplasm and promote agricultural innovation, efforts were made to establish international agreements in this area. One of the most significant developments was the adoption of the International Union for the Protection of New Plant Varieties Convention (UPOV Convention) in 1961.</t>
+  </si>
+  <si>
+    <t>Nigeria was not a signatory to the International Union for the Protection of New Varieties of Plants (UPOV) Convention (Okonkwo, et al 2021) which to a large extent impeded the exploitation of such rights.</t>
+  </si>
+  <si>
+    <t>Meanwhile, the Trade-Related Aspects of Intellectual Property Rights Agreement (TRIPS), which Nigeria is a signatory to, recognizes and provides for the patentability of inventions in all fields of technology and specifically calls for the protection of plant varieties either by patent or by an effective sui generis system or by any combination thereof in line with the provisions of Article 27 of the TRIPS Agreement.</t>
+  </si>
+  <si>
+    <t>Some African countries have opted for the adoption of the International Convention for the Protection of New Varieties of Plants (UPOV Convention) while others have enacted a sui generis plant variety protection law.</t>
+  </si>
+  <si>
+    <t>The Act aligns with international standards, such as those set by the International Union for the Protection of New Varieties of Plants (UPOV).</t>
+  </si>
+  <si>
+    <t>In some jurisdictions like the United State and Australia, the subject matter of protection covered by a Traditional IP and by a plant breeder’s right might be the same, namely a plant variety while in several other jurisdictions like European Union and India, the subject matter of protection is different, and, in general, plant varieties are excluded from patentability.</t>
+  </si>
+  <si>
+    <t>As far as the International Union for the Protection of New Plant Varieties Convention (UPOV) is concerned, a member is free to protect plant varieties, in addition to the grant of a breeder’s right, by the grant of other titles, particularly patents.</t>
+  </si>
+  <si>
+    <t>TRIPS do not specify detailed criteria for plant variety protection but requires member countries to establish effective systems for the protection of plant varieties.</t>
+  </si>
+  <si>
+    <t>It allows flexibility for countries to determine their own criteria, which may include patent, or by an effective sui generis system (which could be UPOV standards) or by combination of both systems.</t>
+  </si>
+  <si>
+    <t>The National Agricultural Seeds Council (NASC) should be given adequate resources and trained personnel to effectively manage the PVP system. This will endeavour that NASC can handle applications, conduct examinations and enforce rights where necessary.</t>
+  </si>
+  <si>
+    <t>A well structured awareness program could be implemented at all level of the society to sensitize farmers, breeders, legislators and the general public on the intellectual property rights and plant variety rights and how they support innovation and food security.</t>
+  </si>
+  <si>
+    <t>Regular monitoring of the market for unauthorized use or infringement on plant varieties. Prompt action should be taken to enforce intellectual property rights through legal means such as sending cease-and-desist letters or pursuing litigation.</t>
+  </si>
+  <si>
+    <t>This passage explicitly states the legislative and policy objectives of Nigeria’s Plant Variety Protection Act.</t>
+  </si>
+  <si>
+    <t>This directly addresses the institutional framework and oversight functions established to implement the plant variety protection system.</t>
+  </si>
+  <si>
+    <t>The passage describes enforcement and monitoring activities supporting the legislative objective of protecting plant breeders’ rights.</t>
+  </si>
+  <si>
+    <t>This identifies an intended performance outcome of the Act: incentivising new variety development and broader breeding activity.</t>
+  </si>
+  <si>
+    <t>This links implementation of the plant variety protection framework to its intended objectives of research, productivity, and economic development.</t>
+  </si>
+  <si>
+    <t>This recommendation concerns effective implementation of the core plant variety protection legislation.</t>
+  </si>
+  <si>
+    <t>The passage directly addresses administrative oversight of applications, examination, and enforcement within the plant variety protection system.</t>
+  </si>
+  <si>
+    <t>This explicitly connects plant variety rights with breeding innovation and responsiveness to market needs.</t>
+  </si>
+  <si>
+    <t>This passage addresses the effects of the protection regime on access to varieties, foreign breeding activity, and exploitation of plant breeding rights.</t>
+  </si>
+  <si>
+    <t>The passage directly links plant variety protection to breeding investment, exploitation of breeding activities, and development of new varieties.</t>
+  </si>
+  <si>
+    <t>This explicitly describes the expected innovation and productivity effects of the plant variety protection system.</t>
+  </si>
+  <si>
+    <t>This passage addresses the relationship between plant variety protection, investment, and varietal innovation.</t>
+  </si>
+  <si>
+    <t>This directly concerns market access to foreign varieties and the effect of protection on international breeding activity.</t>
+  </si>
+  <si>
+    <t>This explicitly identifies farmers’ rights and benefit sharing as considerations that must be balanced within the plant variety protection system.</t>
+  </si>
+  <si>
+    <t>This directly addresses the relationship between breeders’ seed-saving rights and the interests of farmers.</t>
+  </si>
+  <si>
+    <t>This passage defines limitations and exceptions to breeders’ exclusive rights, including private, experimental, and further-breeding uses.</t>
+  </si>
+  <si>
+    <t>This directly addresses the licensing regime and administration of breeders’ rights under the plant variety protection framework.</t>
+  </si>
+  <si>
+    <t>This passage concerns the legal mechanisms for assignment and authorization of activities involving protected varieties.</t>
+  </si>
+  <si>
+    <t>This passage directly discusses the international harmonization of plant variety protection through the UPOV Convention.</t>
+  </si>
+  <si>
+    <t>The passage explicitly addresses Nigeria’s relationship with UPOV and the consequences of non-alignment with that international IP system.</t>
+  </si>
+  <si>
+    <t>This passage directly explains Nigeria’s obligations under TRIPS concerning plant variety protection.</t>
+  </si>
+  <si>
+    <t>The passage compares UPOV-based protection with national sui generis systems, directly addressing interaction between international and domestic IP frameworks.</t>
+  </si>
+  <si>
+    <t>This is a direct statement about alignment between Nigeria’s Plant Variety Protection Act and UPOV standards.</t>
+  </si>
+  <si>
+    <t>This passage explicitly references the European Union framework and compares plant variety rights with traditional IP protection.</t>
+  </si>
+  <si>
+    <t>The passage directly explains how UPOV interacts with other IP titles, particularly patents.</t>
+  </si>
+  <si>
+    <t>This passage describes the relationship between TRIPS obligations and national plant variety protection systems.</t>
+  </si>
+  <si>
+    <t>This directly addresses how TRIPS permits countries to implement plant variety protection through patents, sui generis systems, UPOV standards, or combinations thereof.</t>
+  </si>
+  <si>
+    <t>The passage identifies non-participation in UPOV and the resulting lack of protection and access as barriers to effective implementation and exploitation of plant variety rights.</t>
+  </si>
+  <si>
+    <t>This explicitly identifies inadequate resources and trained personnel as capacity barriers affecting administration, examination, and enforcement of the PVP system.</t>
+  </si>
+  <si>
+    <t>The recommendation indicates a knowledge and awareness gap among key stakeholders that may hinder compliance with and implementation of plant variety rights.</t>
+  </si>
+  <si>
+    <t>This passage addresses enforcement needs, including market monitoring and prompt action against unauthorized use or infringement.</t>
   </si>
   <si>
     <t>high</t>
@@ -379,119 +352,110 @@
     <t>medium</t>
   </si>
   <si>
-    <t>2026-07-09T13:57:31</t>
-  </si>
-  <si>
-    <t>2026-07-09T13:57:52</t>
-  </si>
-  <si>
-    <t>4885febfda356ba8</t>
-  </si>
-  <si>
-    <t>db560946c5a52cd1</t>
-  </si>
-  <si>
-    <t>0b0cda6ea456ae18</t>
-  </si>
-  <si>
-    <t>98bededa55afd02f</t>
-  </si>
-  <si>
-    <t>f0dd8fa3e5752042</t>
-  </si>
-  <si>
-    <t>72026d02c929d901</t>
-  </si>
-  <si>
-    <t>e1e2caa33ec59a34</t>
-  </si>
-  <si>
-    <t>b8687c2ff2bbad02</t>
-  </si>
-  <si>
-    <t>d975bc2534fd8579</t>
-  </si>
-  <si>
-    <t>1f3cc95cab3d84c6</t>
-  </si>
-  <si>
-    <t>a15be750d6e0dcbd</t>
+    <t>2026-07-13T10:46:49</t>
+  </si>
+  <si>
+    <t>2026-07-13T10:46:59</t>
+  </si>
+  <si>
+    <t>921c44f647cb8414</t>
   </si>
   <si>
     <t>0a0c5adc352ca23e</t>
   </si>
   <si>
-    <t>bdc4a4c520252ed4</t>
-  </si>
-  <si>
-    <t>27957cdc75878627</t>
-  </si>
-  <si>
-    <t>aa25b5fbb0c63bc9</t>
-  </si>
-  <si>
-    <t>62cf06fc8b087b12</t>
+    <t>15d08dae243bf0dd</t>
+  </si>
+  <si>
+    <t>e62fa8101dcbf495</t>
+  </si>
+  <si>
+    <t>8ab423e4f332419c</t>
+  </si>
+  <si>
+    <t>336157c31767af2e</t>
+  </si>
+  <si>
+    <t>c64f3b49bdbdbda6</t>
+  </si>
+  <si>
+    <t>60d3fa74711ddeff</t>
+  </si>
+  <si>
+    <t>0399a0f00984de28</t>
   </si>
   <si>
     <t>6d1276c2c269771d</t>
   </si>
   <si>
-    <t>a17bedcc73b313ea</t>
-  </si>
-  <si>
     <t>e25cc72fd7fe642d</t>
   </si>
   <si>
+    <t>0006dfdbe2556ca6</t>
+  </si>
+  <si>
+    <t>e26a5410d9566630</t>
+  </si>
+  <si>
+    <t>ea8f818b2d551ebe</t>
+  </si>
+  <si>
     <t>304d5e591be7ff7c</t>
   </si>
   <si>
-    <t>93ef8e4a617899b8</t>
-  </si>
-  <si>
-    <t>c385ada89e152b2a</t>
-  </si>
-  <si>
-    <t>3bdd9b777dc8ddd5</t>
-  </si>
-  <si>
-    <t>b49ca5012f68706e</t>
-  </si>
-  <si>
-    <t>388aa1a7a82d4eb6</t>
-  </si>
-  <si>
-    <t>12ce00b83501e378</t>
-  </si>
-  <si>
-    <t>78ca97f356748bd0</t>
-  </si>
-  <si>
-    <t>60826a686b8efa72</t>
-  </si>
-  <si>
-    <t>e5907597a32b23e5</t>
-  </si>
-  <si>
-    <t>4aeae4ca4140550c</t>
-  </si>
-  <si>
-    <t>3992db46e85ec29d</t>
-  </si>
-  <si>
-    <t>fb665a95cd9a7236</t>
-  </si>
-  <si>
-    <t>6216360d628f61d6</t>
-  </si>
-  <si>
-    <t>26bd3ff19bf9afcd</t>
+    <t>bed60198aa7d98d7</t>
+  </si>
+  <si>
+    <t>293bedc63ccac696</t>
+  </si>
+  <si>
+    <t>b8b95517fe0ec991</t>
+  </si>
+  <si>
+    <t>6e75c954be94e497</t>
+  </si>
+  <si>
+    <t>981ccf352303e94c</t>
+  </si>
+  <si>
+    <t>c610e80e31bf16e2</t>
+  </si>
+  <si>
+    <t>1241964aeb0d668a</t>
+  </si>
+  <si>
+    <t>f2a89608af05241d</t>
+  </si>
+  <si>
+    <t>b498bb48c3975e6e</t>
+  </si>
+  <si>
+    <t>d45207dcc9ebd233</t>
+  </si>
+  <si>
+    <t>81970ea37993455b</t>
+  </si>
+  <si>
+    <t>78836028559f5700</t>
+  </si>
+  <si>
+    <t>7dda530f2181d6e8</t>
+  </si>
+  <si>
+    <t>952879e5e9fdd222</t>
+  </si>
+  <si>
+    <t>7d12f70da1199b71</t>
+  </si>
+  <si>
+    <t>08fe648d8f55b74f</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -554,21 +518,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -606,7 +562,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -640,7 +596,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -675,10 +630,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -851,11 +805,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -887,1092 +841,996 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
         <v>44</v>
       </c>
-      <c r="C2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" t="s">
-        <v>48</v>
-      </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
         <v>44</v>
       </c>
-      <c r="C3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" t="s">
-        <v>49</v>
-      </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
         <v>44</v>
       </c>
-      <c r="C4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" t="s">
-        <v>50</v>
-      </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H4" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I4" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
         <v>44</v>
       </c>
-      <c r="C5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" t="s">
-        <v>50</v>
-      </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H5" t="s">
+        <v>110</v>
+      </c>
+      <c r="I5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J5" t="s">
         <v>117</v>
       </c>
-      <c r="I5" t="s">
-        <v>119</v>
-      </c>
-      <c r="J5" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
         <v>44</v>
       </c>
-      <c r="C6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" t="s">
-        <v>49</v>
-      </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H6" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I6" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>15</v>
       </c>
       <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
         <v>44</v>
       </c>
-      <c r="C7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" t="s">
-        <v>50</v>
-      </c>
       <c r="E7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I7" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" t="s">
         <v>119</v>
       </c>
-      <c r="J7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>16</v>
       </c>
       <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
         <v>44</v>
       </c>
-      <c r="C8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" t="s">
-        <v>49</v>
-      </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H8" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I8" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H9" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="I9" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J9" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I10" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H11" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I11" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J11" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>20</v>
       </c>
       <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
         <v>45</v>
       </c>
-      <c r="C12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" t="s">
-        <v>48</v>
-      </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F12">
         <v>4</v>
       </c>
       <c r="G12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H12" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I12" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J12" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>21</v>
       </c>
       <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
         <v>45</v>
       </c>
-      <c r="C13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" t="s">
-        <v>48</v>
-      </c>
       <c r="E13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I13" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J13" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>22</v>
       </c>
       <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" t="s">
         <v>45</v>
       </c>
-      <c r="C14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" t="s">
-        <v>50</v>
-      </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I14" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J14" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" t="s">
         <v>46</v>
       </c>
-      <c r="D15" t="s">
-        <v>50</v>
-      </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H15" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I15" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" t="s">
         <v>46</v>
       </c>
-      <c r="D16" t="s">
-        <v>49</v>
-      </c>
       <c r="E16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G16" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I16" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J16" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
         <v>46</v>
       </c>
-      <c r="D17" t="s">
-        <v>50</v>
-      </c>
       <c r="E17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H17" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I17" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" t="s">
         <v>46</v>
       </c>
-      <c r="D18" t="s">
-        <v>50</v>
-      </c>
       <c r="E18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G18" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H18" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I18" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" t="s">
         <v>46</v>
       </c>
-      <c r="D19" t="s">
-        <v>48</v>
-      </c>
       <c r="E19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H19" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I19" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J19" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E20" t="s">
         <v>67</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H20" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I20" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="J20" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G21" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H21" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="I21" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="J21" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D22" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E22" t="s">
         <v>69</v>
       </c>
       <c r="F22">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G22" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H22" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I22" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="J22" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E23" t="s">
         <v>70</v>
       </c>
       <c r="F23">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G23" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H23" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I23" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="J23" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D24" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s">
         <v>71</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G24" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H24" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I24" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="J24" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E25" t="s">
         <v>72</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G25" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H25" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I25" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="J25" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>34</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E26" t="s">
         <v>73</v>
       </c>
       <c r="F26">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G26" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H26" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I26" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="J26" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D27" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E27" t="s">
         <v>74</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G27" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H27" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I27" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="J27" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" t="s">
         <v>47</v>
-      </c>
-      <c r="D28" t="s">
-        <v>51</v>
       </c>
       <c r="E28" t="s">
         <v>75</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G28" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H28" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I28" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="J28" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C29" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H29" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I29" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="J29" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>38</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G30" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H30" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I30" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="J30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H31" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="I31" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="J31" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>40</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G32" t="s">
+        <v>109</v>
+      </c>
+      <c r="H32" t="s">
+        <v>110</v>
+      </c>
+      <c r="I32" t="s">
         <v>113</v>
       </c>
-      <c r="H32" t="s">
-        <v>117</v>
-      </c>
-      <c r="I32" t="s">
-        <v>120</v>
-      </c>
       <c r="J32" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" t="s">
-        <v>52</v>
-      </c>
-      <c r="E33" t="s">
-        <v>80</v>
-      </c>
-      <c r="F33">
-        <v>2</v>
-      </c>
-      <c r="G33" t="s">
-        <v>114</v>
-      </c>
-      <c r="H33" t="s">
-        <v>117</v>
-      </c>
-      <c r="I33" t="s">
-        <v>120</v>
-      </c>
-      <c r="J33" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" t="s">
-        <v>47</v>
-      </c>
-      <c r="D34" t="s">
-        <v>52</v>
-      </c>
-      <c r="E34" t="s">
-        <v>81</v>
-      </c>
-      <c r="F34">
-        <v>2</v>
-      </c>
-      <c r="G34" t="s">
-        <v>115</v>
-      </c>
-      <c r="H34" t="s">
-        <v>117</v>
-      </c>
-      <c r="I34" t="s">
-        <v>120</v>
-      </c>
-      <c r="J34" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" t="s">
-        <v>51</v>
-      </c>
-      <c r="E35" t="s">
-        <v>82</v>
-      </c>
-      <c r="F35">
-        <v>2</v>
-      </c>
-      <c r="G35" t="s">
-        <v>116</v>
-      </c>
-      <c r="H35" t="s">
-        <v>117</v>
-      </c>
-      <c r="I35" t="s">
-        <v>120</v>
-      </c>
-      <c r="J35" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
